--- a/sova-report/sova-report.xlsx
+++ b/sova-report/sova-report.xlsx
@@ -2285,15 +2285,15 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1)</f>
         <v/>
       </c>
       <c r="C7" s="11">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1)</f>
         <v/>
       </c>
       <c r="D7" s="11">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1)</f>
         <v/>
       </c>
       <c r="E7" s="12">
@@ -2305,7 +2305,7 @@
         <v/>
       </c>
       <c r="G7" s="11">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1)</f>
         <v/>
       </c>
       <c r="H7" s="13">
@@ -2332,15 +2332,15 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;="&amp;$K$8)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;"&amp;$K$8+1)</f>
         <v/>
       </c>
       <c r="C8" s="18">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;="&amp;$K$8)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;"&amp;$K$8+1)</f>
         <v/>
       </c>
       <c r="D8" s="18">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;="&amp;$K$8)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;"&amp;$K$8+1)</f>
         <v/>
       </c>
       <c r="E8" s="19">
@@ -2352,7 +2352,7 @@
         <v/>
       </c>
       <c r="G8" s="18">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;="&amp;$K$8)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;"&amp;$K$8+1)</f>
         <v/>
       </c>
       <c r="H8" s="20">
@@ -2478,15 +2478,15 @@
         <v/>
       </c>
       <c r="B13" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$A13)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$A13)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$A13)</f>
         <v/>
       </c>
       <c r="D13" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$A13)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$A13)</f>
         <v/>
       </c>
       <c r="E13" s="29">
@@ -2498,7 +2498,7 @@
         <v/>
       </c>
       <c r="G13" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$A13)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$A13)</f>
         <v/>
       </c>
       <c r="H13" s="30">
@@ -2520,15 +2520,15 @@
         <v/>
       </c>
       <c r="B14" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$A14)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$A14)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$A14)</f>
         <v/>
       </c>
       <c r="D14" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$A14)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$A14)</f>
         <v/>
       </c>
       <c r="E14" s="36">
@@ -2540,7 +2540,7 @@
         <v/>
       </c>
       <c r="G14" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$A14)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$A14)</f>
         <v/>
       </c>
       <c r="H14" s="37">
@@ -2562,15 +2562,15 @@
         <v/>
       </c>
       <c r="B15" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$A15)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$A15)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$A15)</f>
         <v/>
       </c>
       <c r="D15" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$A15)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$A15)</f>
         <v/>
       </c>
       <c r="E15" s="29">
@@ -2582,7 +2582,7 @@
         <v/>
       </c>
       <c r="G15" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$A15)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$A15)</f>
         <v/>
       </c>
       <c r="H15" s="30">
@@ -2697,15 +2697,15 @@
         <v/>
       </c>
       <c r="B20" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C20" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D20" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E20" s="49">
@@ -2720,15 +2720,15 @@
         <v/>
       </c>
       <c r="B21" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C21" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D21" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E21" s="51">
@@ -2746,15 +2746,15 @@
         <v/>
       </c>
       <c r="B22" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C22" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D22" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E22" s="49">
@@ -2772,15 +2772,15 @@
         <v/>
       </c>
       <c r="B23" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C23" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D23" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E23" s="51">
@@ -2798,15 +2798,15 @@
         <v/>
       </c>
       <c r="B24" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C24" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D24" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E24" s="49">
@@ -2824,15 +2824,15 @@
         <v/>
       </c>
       <c r="B25" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C25" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D25" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E25" s="51">
@@ -2850,15 +2850,15 @@
         <v/>
       </c>
       <c r="B26" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C26" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D26" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E26" s="49">
@@ -2876,15 +2876,15 @@
         <v/>
       </c>
       <c r="B27" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C27" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D27" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E27" s="51">
@@ -2902,15 +2902,15 @@
         <v/>
       </c>
       <c r="B28" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C28" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D28" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E28" s="49">
@@ -2928,15 +2928,15 @@
         <v/>
       </c>
       <c r="B29" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C29" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D29" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E29" s="51">
@@ -2954,15 +2954,15 @@
         <v/>
       </c>
       <c r="B30" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C30" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D30" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E30" s="49">
@@ -2980,15 +2980,15 @@
         <v/>
       </c>
       <c r="B31" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C31" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D31" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E31" s="51">
@@ -3006,15 +3006,15 @@
         <v/>
       </c>
       <c r="B32" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C32" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D32" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E32" s="49">
@@ -3032,15 +3032,15 @@
         <v/>
       </c>
       <c r="B33" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C33" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D33" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E33" s="51">
@@ -3058,15 +3058,15 @@
         <v/>
       </c>
       <c r="B34" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C34" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D34" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E34" s="49">
@@ -3084,15 +3084,15 @@
         <v/>
       </c>
       <c r="B35" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C35" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D35" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E35" s="51">
@@ -3110,15 +3110,15 @@
         <v/>
       </c>
       <c r="B36" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C36" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D36" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E36" s="49">
@@ -3136,15 +3136,15 @@
         <v/>
       </c>
       <c r="B37" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C37" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D37" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E37" s="51">
@@ -3162,15 +3162,15 @@
         <v/>
       </c>
       <c r="B38" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C38" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D38" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E38" s="49">
@@ -3188,15 +3188,15 @@
         <v/>
       </c>
       <c r="B39" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C39" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D39" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E39" s="51">
@@ -3214,15 +3214,15 @@
         <v/>
       </c>
       <c r="B40" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C40" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D40" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E40" s="49">
@@ -3240,15 +3240,15 @@
         <v/>
       </c>
       <c r="B41" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C41" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D41" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E41" s="51">
@@ -3266,15 +3266,15 @@
         <v/>
       </c>
       <c r="B42" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C42" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D42" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E42" s="49">
@@ -3292,15 +3292,15 @@
         <v/>
       </c>
       <c r="B43" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C43" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D43" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E43" s="51">
@@ -3318,15 +3318,15 @@
         <v/>
       </c>
       <c r="B44" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C44" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D44" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E44" s="49">
@@ -3344,15 +3344,15 @@
         <v/>
       </c>
       <c r="B45" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6),'Данные'!$B:$B,B$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6)+1,'Данные'!$B:$B,B$19)</f>
         <v/>
       </c>
       <c r="C45" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6),'Данные'!$B:$B,C$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6)+1,'Данные'!$B:$B,C$19)</f>
         <v/>
       </c>
       <c r="D45" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6),'Данные'!$B:$B,D$19)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6)+1,'Данные'!$B:$B,D$19)</f>
         <v/>
       </c>
       <c r="E45" s="51">
@@ -4004,15 +4004,15 @@
         <v/>
       </c>
       <c r="B78" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C78" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D78" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E78" s="55">
@@ -4026,15 +4026,15 @@
         <v/>
       </c>
       <c r="B79" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C79" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D79" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E79" s="56">
@@ -4048,15 +4048,15 @@
         <v/>
       </c>
       <c r="B80" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C80" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D80" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E80" s="55">
@@ -4070,15 +4070,15 @@
         <v/>
       </c>
       <c r="B81" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C81" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D81" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E81" s="56">
@@ -4092,15 +4092,15 @@
         <v/>
       </c>
       <c r="B82" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C82" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D82" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E82" s="55">
@@ -4114,15 +4114,15 @@
         <v/>
       </c>
       <c r="B83" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C83" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D83" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E83" s="56">
@@ -4136,15 +4136,15 @@
         <v/>
       </c>
       <c r="B84" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C84" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D84" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E84" s="55">
@@ -4158,15 +4158,15 @@
         <v/>
       </c>
       <c r="B85" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C85" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D85" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E85" s="56">
@@ -4180,15 +4180,15 @@
         <v/>
       </c>
       <c r="B86" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C86" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D86" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E86" s="55">
@@ -4202,15 +4202,15 @@
         <v/>
       </c>
       <c r="B87" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C87" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D87" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E87" s="56">
@@ -4224,15 +4224,15 @@
         <v/>
       </c>
       <c r="B88" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C88" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D88" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E88" s="55">
@@ -4246,15 +4246,15 @@
         <v/>
       </c>
       <c r="B89" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C89" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D89" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E89" s="56">
@@ -4268,15 +4268,15 @@
         <v/>
       </c>
       <c r="B90" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C90" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D90" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E90" s="55">
@@ -4290,15 +4290,15 @@
         <v/>
       </c>
       <c r="B91" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C91" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D91" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E91" s="56">
@@ -4312,15 +4312,15 @@
         <v/>
       </c>
       <c r="B92" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C92" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D92" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E92" s="55">
@@ -4334,15 +4334,15 @@
         <v/>
       </c>
       <c r="B93" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C93" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D93" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E93" s="56">
@@ -4356,15 +4356,15 @@
         <v/>
       </c>
       <c r="B94" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C94" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D94" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E94" s="55">
@@ -4378,15 +4378,15 @@
         <v/>
       </c>
       <c r="B95" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C95" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D95" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E95" s="56">
@@ -4400,15 +4400,15 @@
         <v/>
       </c>
       <c r="B96" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C96" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D96" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E96" s="55">
@@ -4422,15 +4422,15 @@
         <v/>
       </c>
       <c r="B97" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C97" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D97" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E97" s="56">
@@ -4444,15 +4444,15 @@
         <v/>
       </c>
       <c r="B98" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C98" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D98" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E98" s="55">
@@ -4466,15 +4466,15 @@
         <v/>
       </c>
       <c r="B99" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C99" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D99" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E99" s="56">
@@ -4488,15 +4488,15 @@
         <v/>
       </c>
       <c r="B100" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C100" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D100" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E100" s="55">
@@ -4510,15 +4510,15 @@
         <v/>
       </c>
       <c r="B101" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C101" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D101" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E101" s="56">
@@ -4532,15 +4532,15 @@
         <v/>
       </c>
       <c r="B102" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C102" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D102" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E102" s="55">
@@ -4554,15 +4554,15 @@
         <v/>
       </c>
       <c r="B103" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6),'Данные'!$B:$B,B$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6)+1,'Данные'!$B:$B,B$77)</f>
         <v/>
       </c>
       <c r="C103" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6),'Данные'!$B:$B,C$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6)+1,'Данные'!$B:$B,C$77)</f>
         <v/>
       </c>
       <c r="D103" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),'Данные'!$A:$A,"&lt;="&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6),'Данные'!$B:$B,D$77)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;(($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),'Данные'!$A:$A,"&lt;"&amp;((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6)+1,'Данные'!$B:$B,D$77)</f>
         <v/>
       </c>
       <c r="E103" s="56">
@@ -4626,15 +4626,15 @@
         <v/>
       </c>
       <c r="B107" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),0),'Данные'!$B:$B,B$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),0)+1,'Данные'!$B:$B,B$106)</f>
         <v/>
       </c>
       <c r="C107" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),0),'Данные'!$B:$B,C$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),0)+1,'Данные'!$B:$B,C$106)</f>
         <v/>
       </c>
       <c r="D107" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),0),'Данные'!$B:$B,D$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),0)+1,'Данные'!$B:$B,D$106)</f>
         <v/>
       </c>
       <c r="E107" s="49">
@@ -4649,15 +4649,15 @@
         <v/>
       </c>
       <c r="B108" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),0),'Данные'!$B:$B,B$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),0)+1,'Данные'!$B:$B,B$106)</f>
         <v/>
       </c>
       <c r="C108" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),0),'Данные'!$B:$B,C$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),0)+1,'Данные'!$B:$B,C$106)</f>
         <v/>
       </c>
       <c r="D108" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),0),'Данные'!$B:$B,D$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),0)+1,'Данные'!$B:$B,D$106)</f>
         <v/>
       </c>
       <c r="E108" s="51">
@@ -4675,15 +4675,15 @@
         <v/>
       </c>
       <c r="B109" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),0),'Данные'!$B:$B,B$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),0)+1,'Данные'!$B:$B,B$106)</f>
         <v/>
       </c>
       <c r="C109" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),0),'Данные'!$B:$B,C$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),0)+1,'Данные'!$B:$B,C$106)</f>
         <v/>
       </c>
       <c r="D109" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),0),'Данные'!$B:$B,D$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),0)+1,'Данные'!$B:$B,D$106)</f>
         <v/>
       </c>
       <c r="E109" s="49">
@@ -4701,15 +4701,15 @@
         <v/>
       </c>
       <c r="B110" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),0),'Данные'!$B:$B,B$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),0)+1,'Данные'!$B:$B,B$106)</f>
         <v/>
       </c>
       <c r="C110" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),0),'Данные'!$B:$B,C$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),0)+1,'Данные'!$B:$B,C$106)</f>
         <v/>
       </c>
       <c r="D110" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),0),'Данные'!$B:$B,D$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),0)+1,'Данные'!$B:$B,D$106)</f>
         <v/>
       </c>
       <c r="E110" s="51">
@@ -4727,15 +4727,15 @@
         <v/>
       </c>
       <c r="B111" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),0),'Данные'!$B:$B,B$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),0)+1,'Данные'!$B:$B,B$106)</f>
         <v/>
       </c>
       <c r="C111" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),0),'Данные'!$B:$B,C$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),0)+1,'Данные'!$B:$B,C$106)</f>
         <v/>
       </c>
       <c r="D111" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),0),'Данные'!$B:$B,D$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),0)+1,'Данные'!$B:$B,D$106)</f>
         <v/>
       </c>
       <c r="E111" s="49">
@@ -4753,15 +4753,15 @@
         <v/>
       </c>
       <c r="B112" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),0),'Данные'!$B:$B,B$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),0)+1,'Данные'!$B:$B,B$106)</f>
         <v/>
       </c>
       <c r="C112" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),0),'Данные'!$B:$B,C$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),0)+1,'Данные'!$B:$B,C$106)</f>
         <v/>
       </c>
       <c r="D112" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),0),'Данные'!$B:$B,D$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),0)+1,'Данные'!$B:$B,D$106)</f>
         <v/>
       </c>
       <c r="E112" s="51">
@@ -4779,15 +4779,15 @@
         <v/>
       </c>
       <c r="B113" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),0),'Данные'!$B:$B,B$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),0)+1,'Данные'!$B:$B,B$106)</f>
         <v/>
       </c>
       <c r="C113" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),0),'Данные'!$B:$B,C$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),0)+1,'Данные'!$B:$B,C$106)</f>
         <v/>
       </c>
       <c r="D113" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),0),'Данные'!$B:$B,D$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),0)+1,'Данные'!$B:$B,D$106)</f>
         <v/>
       </c>
       <c r="E113" s="49">
@@ -4805,15 +4805,15 @@
         <v/>
       </c>
       <c r="B114" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),0),'Данные'!$B:$B,B$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),0)+1,'Данные'!$B:$B,B$106)</f>
         <v/>
       </c>
       <c r="C114" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),0),'Данные'!$B:$B,C$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),0)+1,'Данные'!$B:$B,C$106)</f>
         <v/>
       </c>
       <c r="D114" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),0),'Данные'!$B:$B,D$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),0)+1,'Данные'!$B:$B,D$106)</f>
         <v/>
       </c>
       <c r="E114" s="51">
@@ -4831,15 +4831,15 @@
         <v/>
       </c>
       <c r="B115" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),0),'Данные'!$B:$B,B$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),0)+1,'Данные'!$B:$B,B$106)</f>
         <v/>
       </c>
       <c r="C115" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),0),'Данные'!$B:$B,C$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),0)+1,'Данные'!$B:$B,C$106)</f>
         <v/>
       </c>
       <c r="D115" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),0),'Данные'!$B:$B,D$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),0)+1,'Данные'!$B:$B,D$106)</f>
         <v/>
       </c>
       <c r="E115" s="49">
@@ -4857,15 +4857,15 @@
         <v/>
       </c>
       <c r="B116" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),0),'Данные'!$B:$B,B$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),0)+1,'Данные'!$B:$B,B$106)</f>
         <v/>
       </c>
       <c r="C116" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),0),'Данные'!$B:$B,C$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),0)+1,'Данные'!$B:$B,C$106)</f>
         <v/>
       </c>
       <c r="D116" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),0),'Данные'!$B:$B,D$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),0)+1,'Данные'!$B:$B,D$106)</f>
         <v/>
       </c>
       <c r="E116" s="51">
@@ -4883,15 +4883,15 @@
         <v/>
       </c>
       <c r="B117" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),0),'Данные'!$B:$B,B$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),0)+1,'Данные'!$B:$B,B$106)</f>
         <v/>
       </c>
       <c r="C117" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),0),'Данные'!$B:$B,C$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),0)+1,'Данные'!$B:$B,C$106)</f>
         <v/>
       </c>
       <c r="D117" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),0),'Данные'!$B:$B,D$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),0)+1,'Данные'!$B:$B,D$106)</f>
         <v/>
       </c>
       <c r="E117" s="49">
@@ -4909,15 +4909,15 @@
         <v/>
       </c>
       <c r="B118" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),0),'Данные'!$B:$B,B$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),0)+1,'Данные'!$B:$B,B$106)</f>
         <v/>
       </c>
       <c r="C118" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),0),'Данные'!$B:$B,C$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),0)+1,'Данные'!$B:$B,C$106)</f>
         <v/>
       </c>
       <c r="D118" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),0),'Данные'!$B:$B,D$106)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),0)+1,'Данные'!$B:$B,D$106)</f>
         <v/>
       </c>
       <c r="E118" s="51">
@@ -5261,15 +5261,15 @@
         <v/>
       </c>
       <c r="B137" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),0),'Данные'!$B:$B,B$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),0)+1,'Данные'!$B:$B,B$136)</f>
         <v/>
       </c>
       <c r="C137" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),0),'Данные'!$B:$B,C$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),0)+1,'Данные'!$B:$B,C$136)</f>
         <v/>
       </c>
       <c r="D137" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),0),'Данные'!$B:$B,D$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11),0)+1,'Данные'!$B:$B,D$136)</f>
         <v/>
       </c>
       <c r="E137" s="55">
@@ -5283,15 +5283,15 @@
         <v/>
       </c>
       <c r="B138" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),0),'Данные'!$B:$B,B$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),0)+1,'Данные'!$B:$B,B$136)</f>
         <v/>
       </c>
       <c r="C138" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),0),'Данные'!$B:$B,C$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),0)+1,'Данные'!$B:$B,C$136)</f>
         <v/>
       </c>
       <c r="D138" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),0),'Данные'!$B:$B,D$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10),0)+1,'Данные'!$B:$B,D$136)</f>
         <v/>
       </c>
       <c r="E138" s="56">
@@ -5305,15 +5305,15 @@
         <v/>
       </c>
       <c r="B139" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),0),'Данные'!$B:$B,B$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),0)+1,'Данные'!$B:$B,B$136)</f>
         <v/>
       </c>
       <c r="C139" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),0),'Данные'!$B:$B,C$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),0)+1,'Данные'!$B:$B,C$136)</f>
         <v/>
       </c>
       <c r="D139" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),0),'Данные'!$B:$B,D$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9),0)+1,'Данные'!$B:$B,D$136)</f>
         <v/>
       </c>
       <c r="E139" s="55">
@@ -5327,15 +5327,15 @@
         <v/>
       </c>
       <c r="B140" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),0),'Данные'!$B:$B,B$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),0)+1,'Данные'!$B:$B,B$136)</f>
         <v/>
       </c>
       <c r="C140" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),0),'Данные'!$B:$B,C$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),0)+1,'Данные'!$B:$B,C$136)</f>
         <v/>
       </c>
       <c r="D140" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),0),'Данные'!$B:$B,D$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8),0)+1,'Данные'!$B:$B,D$136)</f>
         <v/>
       </c>
       <c r="E140" s="56">
@@ -5349,15 +5349,15 @@
         <v/>
       </c>
       <c r="B141" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),0),'Данные'!$B:$B,B$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),0)+1,'Данные'!$B:$B,B$136)</f>
         <v/>
       </c>
       <c r="C141" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),0),'Данные'!$B:$B,C$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),0)+1,'Данные'!$B:$B,C$136)</f>
         <v/>
       </c>
       <c r="D141" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),0),'Данные'!$B:$B,D$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7),0)+1,'Данные'!$B:$B,D$136)</f>
         <v/>
       </c>
       <c r="E141" s="55">
@@ -5371,15 +5371,15 @@
         <v/>
       </c>
       <c r="B142" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),0),'Данные'!$B:$B,B$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),0)+1,'Данные'!$B:$B,B$136)</f>
         <v/>
       </c>
       <c r="C142" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),0),'Данные'!$B:$B,C$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),0)+1,'Данные'!$B:$B,C$136)</f>
         <v/>
       </c>
       <c r="D142" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),0),'Данные'!$B:$B,D$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6),0)+1,'Данные'!$B:$B,D$136)</f>
         <v/>
       </c>
       <c r="E142" s="56">
@@ -5393,15 +5393,15 @@
         <v/>
       </c>
       <c r="B143" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),0),'Данные'!$B:$B,B$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),0)+1,'Данные'!$B:$B,B$136)</f>
         <v/>
       </c>
       <c r="C143" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),0),'Данные'!$B:$B,C$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),0)+1,'Данные'!$B:$B,C$136)</f>
         <v/>
       </c>
       <c r="D143" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),0),'Данные'!$B:$B,D$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5),0)+1,'Данные'!$B:$B,D$136)</f>
         <v/>
       </c>
       <c r="E143" s="55">
@@ -5415,15 +5415,15 @@
         <v/>
       </c>
       <c r="B144" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),0),'Данные'!$B:$B,B$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),0)+1,'Данные'!$B:$B,B$136)</f>
         <v/>
       </c>
       <c r="C144" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),0),'Данные'!$B:$B,C$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),0)+1,'Данные'!$B:$B,C$136)</f>
         <v/>
       </c>
       <c r="D144" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),0),'Данные'!$B:$B,D$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4),0)+1,'Данные'!$B:$B,D$136)</f>
         <v/>
       </c>
       <c r="E144" s="56">
@@ -5437,15 +5437,15 @@
         <v/>
       </c>
       <c r="B145" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),0),'Данные'!$B:$B,B$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),0)+1,'Данные'!$B:$B,B$136)</f>
         <v/>
       </c>
       <c r="C145" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),0),'Данные'!$B:$B,C$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),0)+1,'Данные'!$B:$B,C$136)</f>
         <v/>
       </c>
       <c r="D145" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),0),'Данные'!$B:$B,D$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3),0)+1,'Данные'!$B:$B,D$136)</f>
         <v/>
       </c>
       <c r="E145" s="55">
@@ -5459,15 +5459,15 @@
         <v/>
       </c>
       <c r="B146" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),0),'Данные'!$B:$B,B$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),0)+1,'Данные'!$B:$B,B$136)</f>
         <v/>
       </c>
       <c r="C146" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),0),'Данные'!$B:$B,C$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),0)+1,'Данные'!$B:$B,C$136)</f>
         <v/>
       </c>
       <c r="D146" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),0),'Данные'!$B:$B,D$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2),0)+1,'Данные'!$B:$B,D$136)</f>
         <v/>
       </c>
       <c r="E146" s="56">
@@ -5481,15 +5481,15 @@
         <v/>
       </c>
       <c r="B147" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),0),'Данные'!$B:$B,B$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),0)+1,'Данные'!$B:$B,B$136)</f>
         <v/>
       </c>
       <c r="C147" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),0),'Данные'!$B:$B,C$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),0)+1,'Данные'!$B:$B,C$136)</f>
         <v/>
       </c>
       <c r="D147" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),0),'Данные'!$B:$B,D$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1),0)+1,'Данные'!$B:$B,D$136)</f>
         <v/>
       </c>
       <c r="E147" s="55">
@@ -5503,15 +5503,15 @@
         <v/>
       </c>
       <c r="B148" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),0),'Данные'!$B:$B,B$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),0)+1,'Данные'!$B:$B,B$136)</f>
         <v/>
       </c>
       <c r="C148" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),0),'Данные'!$B:$B,C$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),0)+1,'Данные'!$B:$B,C$136)</f>
         <v/>
       </c>
       <c r="D148" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),'Данные'!$A:$A,"&lt;="&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),0),'Данные'!$B:$B,D$136)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),'Данные'!$A:$A,"&lt;"&amp;EOMONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0),0)+1,'Данные'!$B:$B,D$136)</f>
         <v/>
       </c>
       <c r="E148" s="56">
@@ -5845,15 +5845,15 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C7" s="11">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D7" s="11">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E7" s="12">
@@ -5865,7 +5865,7 @@
         <v/>
       </c>
       <c r="G7" s="11">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H7" s="13">
@@ -5892,15 +5892,15 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;="&amp;$K$8,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;"&amp;$K$8+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C8" s="18">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;="&amp;$K$8,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;"&amp;$K$8+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D8" s="18">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;="&amp;$K$8,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;"&amp;$K$8+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E8" s="19">
@@ -5912,7 +5912,7 @@
         <v/>
       </c>
       <c r="G8" s="18">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;="&amp;$K$8,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;"&amp;$K$8+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H8" s="20">
@@ -6033,15 +6033,15 @@
         <v/>
       </c>
       <c r="B13" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;="&amp;($E$3-89),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;"&amp;($E$3-89)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C13" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;="&amp;($E$3-89),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;"&amp;($E$3-89)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D13" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;="&amp;($E$3-89),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;"&amp;($E$3-89)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E13" s="29">
@@ -6053,7 +6053,7 @@
         <v/>
       </c>
       <c r="G13" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;="&amp;($E$3-89),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;"&amp;($E$3-89)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H13" s="30">
@@ -6071,15 +6071,15 @@
         <v/>
       </c>
       <c r="B14" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;="&amp;($E$3-88),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;"&amp;($E$3-88)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C14" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;="&amp;($E$3-88),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;"&amp;($E$3-88)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D14" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;="&amp;($E$3-88),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;"&amp;($E$3-88)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E14" s="36">
@@ -6091,7 +6091,7 @@
         <v/>
       </c>
       <c r="G14" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;="&amp;($E$3-88),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;"&amp;($E$3-88)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H14" s="37">
@@ -6109,15 +6109,15 @@
         <v/>
       </c>
       <c r="B15" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;="&amp;($E$3-87),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;"&amp;($E$3-87)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C15" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;="&amp;($E$3-87),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;"&amp;($E$3-87)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D15" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;="&amp;($E$3-87),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;"&amp;($E$3-87)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E15" s="29">
@@ -6129,7 +6129,7 @@
         <v/>
       </c>
       <c r="G15" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;="&amp;($E$3-87),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;"&amp;($E$3-87)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H15" s="30">
@@ -6147,15 +6147,15 @@
         <v/>
       </c>
       <c r="B16" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;="&amp;($E$3-86),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;"&amp;($E$3-86)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C16" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;="&amp;($E$3-86),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;"&amp;($E$3-86)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D16" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;="&amp;($E$3-86),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;"&amp;($E$3-86)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E16" s="36">
@@ -6167,7 +6167,7 @@
         <v/>
       </c>
       <c r="G16" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;="&amp;($E$3-86),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;"&amp;($E$3-86)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H16" s="37">
@@ -6185,15 +6185,15 @@
         <v/>
       </c>
       <c r="B17" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;="&amp;($E$3-85),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;"&amp;($E$3-85)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C17" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;="&amp;($E$3-85),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;"&amp;($E$3-85)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D17" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;="&amp;($E$3-85),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;"&amp;($E$3-85)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E17" s="29">
@@ -6205,7 +6205,7 @@
         <v/>
       </c>
       <c r="G17" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;="&amp;($E$3-85),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;"&amp;($E$3-85)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H17" s="30">
@@ -6223,15 +6223,15 @@
         <v/>
       </c>
       <c r="B18" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;="&amp;($E$3-84),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;"&amp;($E$3-84)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C18" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;="&amp;($E$3-84),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;"&amp;($E$3-84)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D18" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;="&amp;($E$3-84),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;"&amp;($E$3-84)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E18" s="36">
@@ -6243,7 +6243,7 @@
         <v/>
       </c>
       <c r="G18" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;="&amp;($E$3-84),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;"&amp;($E$3-84)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H18" s="37">
@@ -6261,15 +6261,15 @@
         <v/>
       </c>
       <c r="B19" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;="&amp;($E$3-83),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;"&amp;($E$3-83)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C19" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;="&amp;($E$3-83),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;"&amp;($E$3-83)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D19" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;="&amp;($E$3-83),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;"&amp;($E$3-83)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E19" s="29">
@@ -6281,7 +6281,7 @@
         <v/>
       </c>
       <c r="G19" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;="&amp;($E$3-83),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;"&amp;($E$3-83)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H19" s="30">
@@ -6299,15 +6299,15 @@
         <v/>
       </c>
       <c r="B20" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;="&amp;($E$3-82),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;"&amp;($E$3-82)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C20" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;="&amp;($E$3-82),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;"&amp;($E$3-82)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D20" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;="&amp;($E$3-82),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;"&amp;($E$3-82)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E20" s="36">
@@ -6319,7 +6319,7 @@
         <v/>
       </c>
       <c r="G20" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;="&amp;($E$3-82),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;"&amp;($E$3-82)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H20" s="37">
@@ -6337,15 +6337,15 @@
         <v/>
       </c>
       <c r="B21" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;="&amp;($E$3-81),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;"&amp;($E$3-81)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C21" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;="&amp;($E$3-81),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;"&amp;($E$3-81)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D21" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;="&amp;($E$3-81),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;"&amp;($E$3-81)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E21" s="29">
@@ -6357,7 +6357,7 @@
         <v/>
       </c>
       <c r="G21" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;="&amp;($E$3-81),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;"&amp;($E$3-81)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H21" s="30">
@@ -6375,15 +6375,15 @@
         <v/>
       </c>
       <c r="B22" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;="&amp;($E$3-80),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;"&amp;($E$3-80)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C22" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;="&amp;($E$3-80),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;"&amp;($E$3-80)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D22" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;="&amp;($E$3-80),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;"&amp;($E$3-80)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E22" s="36">
@@ -6395,7 +6395,7 @@
         <v/>
       </c>
       <c r="G22" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;="&amp;($E$3-80),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;"&amp;($E$3-80)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H22" s="37">
@@ -6413,15 +6413,15 @@
         <v/>
       </c>
       <c r="B23" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;="&amp;($E$3-79),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;"&amp;($E$3-79)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C23" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;="&amp;($E$3-79),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;"&amp;($E$3-79)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D23" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;="&amp;($E$3-79),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;"&amp;($E$3-79)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E23" s="29">
@@ -6433,7 +6433,7 @@
         <v/>
       </c>
       <c r="G23" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;="&amp;($E$3-79),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;"&amp;($E$3-79)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H23" s="30">
@@ -6451,15 +6451,15 @@
         <v/>
       </c>
       <c r="B24" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;="&amp;($E$3-78),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;"&amp;($E$3-78)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C24" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;="&amp;($E$3-78),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;"&amp;($E$3-78)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D24" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;="&amp;($E$3-78),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;"&amp;($E$3-78)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E24" s="36">
@@ -6471,7 +6471,7 @@
         <v/>
       </c>
       <c r="G24" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;="&amp;($E$3-78),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;"&amp;($E$3-78)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H24" s="37">
@@ -6489,15 +6489,15 @@
         <v/>
       </c>
       <c r="B25" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;="&amp;($E$3-77),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;"&amp;($E$3-77)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C25" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;="&amp;($E$3-77),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;"&amp;($E$3-77)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D25" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;="&amp;($E$3-77),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;"&amp;($E$3-77)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E25" s="29">
@@ -6509,7 +6509,7 @@
         <v/>
       </c>
       <c r="G25" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;="&amp;($E$3-77),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;"&amp;($E$3-77)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H25" s="30">
@@ -6527,15 +6527,15 @@
         <v/>
       </c>
       <c r="B26" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;="&amp;($E$3-76),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;"&amp;($E$3-76)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C26" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;="&amp;($E$3-76),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;"&amp;($E$3-76)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D26" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;="&amp;($E$3-76),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;"&amp;($E$3-76)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E26" s="36">
@@ -6547,7 +6547,7 @@
         <v/>
       </c>
       <c r="G26" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;="&amp;($E$3-76),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;"&amp;($E$3-76)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H26" s="37">
@@ -6565,15 +6565,15 @@
         <v/>
       </c>
       <c r="B27" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;="&amp;($E$3-75),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;"&amp;($E$3-75)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C27" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;="&amp;($E$3-75),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;"&amp;($E$3-75)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D27" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;="&amp;($E$3-75),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;"&amp;($E$3-75)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E27" s="29">
@@ -6585,7 +6585,7 @@
         <v/>
       </c>
       <c r="G27" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;="&amp;($E$3-75),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;"&amp;($E$3-75)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H27" s="30">
@@ -6603,15 +6603,15 @@
         <v/>
       </c>
       <c r="B28" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;="&amp;($E$3-74),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;"&amp;($E$3-74)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C28" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;="&amp;($E$3-74),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;"&amp;($E$3-74)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D28" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;="&amp;($E$3-74),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;"&amp;($E$3-74)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E28" s="36">
@@ -6623,7 +6623,7 @@
         <v/>
       </c>
       <c r="G28" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;="&amp;($E$3-74),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;"&amp;($E$3-74)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H28" s="37">
@@ -6641,15 +6641,15 @@
         <v/>
       </c>
       <c r="B29" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;="&amp;($E$3-73),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;"&amp;($E$3-73)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C29" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;="&amp;($E$3-73),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;"&amp;($E$3-73)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D29" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;="&amp;($E$3-73),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;"&amp;($E$3-73)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E29" s="29">
@@ -6661,7 +6661,7 @@
         <v/>
       </c>
       <c r="G29" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;="&amp;($E$3-73),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;"&amp;($E$3-73)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H29" s="30">
@@ -6679,15 +6679,15 @@
         <v/>
       </c>
       <c r="B30" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;="&amp;($E$3-72),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;"&amp;($E$3-72)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C30" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;="&amp;($E$3-72),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;"&amp;($E$3-72)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D30" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;="&amp;($E$3-72),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;"&amp;($E$3-72)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E30" s="36">
@@ -6699,7 +6699,7 @@
         <v/>
       </c>
       <c r="G30" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;="&amp;($E$3-72),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;"&amp;($E$3-72)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H30" s="37">
@@ -6717,15 +6717,15 @@
         <v/>
       </c>
       <c r="B31" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;="&amp;($E$3-71),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;"&amp;($E$3-71)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C31" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;="&amp;($E$3-71),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;"&amp;($E$3-71)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D31" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;="&amp;($E$3-71),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;"&amp;($E$3-71)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E31" s="29">
@@ -6737,7 +6737,7 @@
         <v/>
       </c>
       <c r="G31" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;="&amp;($E$3-71),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;"&amp;($E$3-71)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H31" s="30">
@@ -6755,15 +6755,15 @@
         <v/>
       </c>
       <c r="B32" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;="&amp;($E$3-70),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;"&amp;($E$3-70)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C32" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;="&amp;($E$3-70),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;"&amp;($E$3-70)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D32" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;="&amp;($E$3-70),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;"&amp;($E$3-70)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E32" s="36">
@@ -6775,7 +6775,7 @@
         <v/>
       </c>
       <c r="G32" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;="&amp;($E$3-70),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;"&amp;($E$3-70)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H32" s="37">
@@ -6793,15 +6793,15 @@
         <v/>
       </c>
       <c r="B33" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;="&amp;($E$3-69),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;"&amp;($E$3-69)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C33" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;="&amp;($E$3-69),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;"&amp;($E$3-69)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D33" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;="&amp;($E$3-69),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;"&amp;($E$3-69)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E33" s="29">
@@ -6813,7 +6813,7 @@
         <v/>
       </c>
       <c r="G33" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;="&amp;($E$3-69),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;"&amp;($E$3-69)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H33" s="30">
@@ -6831,15 +6831,15 @@
         <v/>
       </c>
       <c r="B34" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;="&amp;($E$3-68),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;"&amp;($E$3-68)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C34" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;="&amp;($E$3-68),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;"&amp;($E$3-68)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D34" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;="&amp;($E$3-68),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;"&amp;($E$3-68)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E34" s="36">
@@ -6851,7 +6851,7 @@
         <v/>
       </c>
       <c r="G34" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;="&amp;($E$3-68),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;"&amp;($E$3-68)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H34" s="37">
@@ -6869,15 +6869,15 @@
         <v/>
       </c>
       <c r="B35" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;="&amp;($E$3-67),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;"&amp;($E$3-67)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C35" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;="&amp;($E$3-67),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;"&amp;($E$3-67)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D35" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;="&amp;($E$3-67),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;"&amp;($E$3-67)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E35" s="29">
@@ -6889,7 +6889,7 @@
         <v/>
       </c>
       <c r="G35" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;="&amp;($E$3-67),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;"&amp;($E$3-67)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H35" s="30">
@@ -6907,15 +6907,15 @@
         <v/>
       </c>
       <c r="B36" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;="&amp;($E$3-66),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;"&amp;($E$3-66)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C36" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;="&amp;($E$3-66),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;"&amp;($E$3-66)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D36" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;="&amp;($E$3-66),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;"&amp;($E$3-66)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E36" s="36">
@@ -6927,7 +6927,7 @@
         <v/>
       </c>
       <c r="G36" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;="&amp;($E$3-66),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;"&amp;($E$3-66)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H36" s="37">
@@ -6945,15 +6945,15 @@
         <v/>
       </c>
       <c r="B37" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;="&amp;($E$3-65),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;"&amp;($E$3-65)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C37" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;="&amp;($E$3-65),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;"&amp;($E$3-65)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D37" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;="&amp;($E$3-65),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;"&amp;($E$3-65)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E37" s="29">
@@ -6965,7 +6965,7 @@
         <v/>
       </c>
       <c r="G37" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;="&amp;($E$3-65),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;"&amp;($E$3-65)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H37" s="30">
@@ -6983,15 +6983,15 @@
         <v/>
       </c>
       <c r="B38" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;="&amp;($E$3-64),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;"&amp;($E$3-64)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C38" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;="&amp;($E$3-64),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;"&amp;($E$3-64)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D38" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;="&amp;($E$3-64),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;"&amp;($E$3-64)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E38" s="36">
@@ -7003,7 +7003,7 @@
         <v/>
       </c>
       <c r="G38" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;="&amp;($E$3-64),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;"&amp;($E$3-64)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H38" s="37">
@@ -7021,15 +7021,15 @@
         <v/>
       </c>
       <c r="B39" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;="&amp;($E$3-63),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;"&amp;($E$3-63)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C39" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;="&amp;($E$3-63),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;"&amp;($E$3-63)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D39" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;="&amp;($E$3-63),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;"&amp;($E$3-63)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E39" s="29">
@@ -7041,7 +7041,7 @@
         <v/>
       </c>
       <c r="G39" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;="&amp;($E$3-63),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;"&amp;($E$3-63)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H39" s="30">
@@ -7059,15 +7059,15 @@
         <v/>
       </c>
       <c r="B40" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;="&amp;($E$3-62),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;"&amp;($E$3-62)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C40" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;="&amp;($E$3-62),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;"&amp;($E$3-62)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D40" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;="&amp;($E$3-62),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;"&amp;($E$3-62)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E40" s="36">
@@ -7079,7 +7079,7 @@
         <v/>
       </c>
       <c r="G40" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;="&amp;($E$3-62),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;"&amp;($E$3-62)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H40" s="37">
@@ -7097,15 +7097,15 @@
         <v/>
       </c>
       <c r="B41" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;="&amp;($E$3-61),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;"&amp;($E$3-61)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C41" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;="&amp;($E$3-61),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;"&amp;($E$3-61)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D41" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;="&amp;($E$3-61),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;"&amp;($E$3-61)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E41" s="29">
@@ -7117,7 +7117,7 @@
         <v/>
       </c>
       <c r="G41" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;="&amp;($E$3-61),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;"&amp;($E$3-61)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H41" s="30">
@@ -7135,15 +7135,15 @@
         <v/>
       </c>
       <c r="B42" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;="&amp;($E$3-60),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;"&amp;($E$3-60)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C42" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;="&amp;($E$3-60),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;"&amp;($E$3-60)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D42" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;="&amp;($E$3-60),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;"&amp;($E$3-60)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E42" s="36">
@@ -7155,7 +7155,7 @@
         <v/>
       </c>
       <c r="G42" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;="&amp;($E$3-60),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;"&amp;($E$3-60)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H42" s="37">
@@ -7173,15 +7173,15 @@
         <v/>
       </c>
       <c r="B43" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;="&amp;($E$3-59),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;"&amp;($E$3-59)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C43" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;="&amp;($E$3-59),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;"&amp;($E$3-59)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D43" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;="&amp;($E$3-59),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;"&amp;($E$3-59)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E43" s="29">
@@ -7193,7 +7193,7 @@
         <v/>
       </c>
       <c r="G43" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;="&amp;($E$3-59),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;"&amp;($E$3-59)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H43" s="30">
@@ -7211,15 +7211,15 @@
         <v/>
       </c>
       <c r="B44" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;="&amp;($E$3-58),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;"&amp;($E$3-58)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C44" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;="&amp;($E$3-58),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;"&amp;($E$3-58)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D44" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;="&amp;($E$3-58),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;"&amp;($E$3-58)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E44" s="36">
@@ -7231,7 +7231,7 @@
         <v/>
       </c>
       <c r="G44" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;="&amp;($E$3-58),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;"&amp;($E$3-58)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H44" s="37">
@@ -7249,15 +7249,15 @@
         <v/>
       </c>
       <c r="B45" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;="&amp;($E$3-57),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;"&amp;($E$3-57)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C45" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;="&amp;($E$3-57),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;"&amp;($E$3-57)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D45" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;="&amp;($E$3-57),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;"&amp;($E$3-57)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E45" s="29">
@@ -7269,7 +7269,7 @@
         <v/>
       </c>
       <c r="G45" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;="&amp;($E$3-57),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;"&amp;($E$3-57)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H45" s="30">
@@ -7287,15 +7287,15 @@
         <v/>
       </c>
       <c r="B46" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;="&amp;($E$3-56),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;"&amp;($E$3-56)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C46" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;="&amp;($E$3-56),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;"&amp;($E$3-56)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D46" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;="&amp;($E$3-56),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;"&amp;($E$3-56)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E46" s="36">
@@ -7307,7 +7307,7 @@
         <v/>
       </c>
       <c r="G46" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;="&amp;($E$3-56),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;"&amp;($E$3-56)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H46" s="37">
@@ -7325,15 +7325,15 @@
         <v/>
       </c>
       <c r="B47" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;="&amp;($E$3-55),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;"&amp;($E$3-55)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C47" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;="&amp;($E$3-55),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;"&amp;($E$3-55)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D47" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;="&amp;($E$3-55),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;"&amp;($E$3-55)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E47" s="29">
@@ -7345,7 +7345,7 @@
         <v/>
       </c>
       <c r="G47" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;="&amp;($E$3-55),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;"&amp;($E$3-55)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H47" s="30">
@@ -7363,15 +7363,15 @@
         <v/>
       </c>
       <c r="B48" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;="&amp;($E$3-54),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;"&amp;($E$3-54)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C48" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;="&amp;($E$3-54),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;"&amp;($E$3-54)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D48" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;="&amp;($E$3-54),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;"&amp;($E$3-54)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E48" s="36">
@@ -7383,7 +7383,7 @@
         <v/>
       </c>
       <c r="G48" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;="&amp;($E$3-54),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;"&amp;($E$3-54)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H48" s="37">
@@ -7401,15 +7401,15 @@
         <v/>
       </c>
       <c r="B49" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;="&amp;($E$3-53),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;"&amp;($E$3-53)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C49" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;="&amp;($E$3-53),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;"&amp;($E$3-53)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D49" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;="&amp;($E$3-53),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;"&amp;($E$3-53)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E49" s="29">
@@ -7421,7 +7421,7 @@
         <v/>
       </c>
       <c r="G49" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;="&amp;($E$3-53),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;"&amp;($E$3-53)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H49" s="30">
@@ -7439,15 +7439,15 @@
         <v/>
       </c>
       <c r="B50" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;="&amp;($E$3-52),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;"&amp;($E$3-52)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C50" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;="&amp;($E$3-52),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;"&amp;($E$3-52)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D50" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;="&amp;($E$3-52),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;"&amp;($E$3-52)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E50" s="36">
@@ -7459,7 +7459,7 @@
         <v/>
       </c>
       <c r="G50" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;="&amp;($E$3-52),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;"&amp;($E$3-52)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H50" s="37">
@@ -7477,15 +7477,15 @@
         <v/>
       </c>
       <c r="B51" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;="&amp;($E$3-51),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;"&amp;($E$3-51)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C51" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;="&amp;($E$3-51),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;"&amp;($E$3-51)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D51" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;="&amp;($E$3-51),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;"&amp;($E$3-51)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E51" s="29">
@@ -7497,7 +7497,7 @@
         <v/>
       </c>
       <c r="G51" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;="&amp;($E$3-51),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;"&amp;($E$3-51)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H51" s="30">
@@ -7515,15 +7515,15 @@
         <v/>
       </c>
       <c r="B52" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;="&amp;($E$3-50),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;"&amp;($E$3-50)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C52" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;="&amp;($E$3-50),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;"&amp;($E$3-50)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D52" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;="&amp;($E$3-50),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;"&amp;($E$3-50)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E52" s="36">
@@ -7535,7 +7535,7 @@
         <v/>
       </c>
       <c r="G52" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;="&amp;($E$3-50),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;"&amp;($E$3-50)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H52" s="37">
@@ -7553,15 +7553,15 @@
         <v/>
       </c>
       <c r="B53" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;="&amp;($E$3-49),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;"&amp;($E$3-49)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C53" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;="&amp;($E$3-49),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;"&amp;($E$3-49)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D53" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;="&amp;($E$3-49),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;"&amp;($E$3-49)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E53" s="29">
@@ -7573,7 +7573,7 @@
         <v/>
       </c>
       <c r="G53" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;="&amp;($E$3-49),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;"&amp;($E$3-49)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H53" s="30">
@@ -7591,15 +7591,15 @@
         <v/>
       </c>
       <c r="B54" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;="&amp;($E$3-48),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;"&amp;($E$3-48)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C54" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;="&amp;($E$3-48),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;"&amp;($E$3-48)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D54" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;="&amp;($E$3-48),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;"&amp;($E$3-48)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E54" s="36">
@@ -7611,7 +7611,7 @@
         <v/>
       </c>
       <c r="G54" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;="&amp;($E$3-48),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;"&amp;($E$3-48)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H54" s="37">
@@ -7629,15 +7629,15 @@
         <v/>
       </c>
       <c r="B55" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;="&amp;($E$3-47),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;"&amp;($E$3-47)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C55" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;="&amp;($E$3-47),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;"&amp;($E$3-47)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D55" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;="&amp;($E$3-47),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;"&amp;($E$3-47)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E55" s="29">
@@ -7649,7 +7649,7 @@
         <v/>
       </c>
       <c r="G55" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;="&amp;($E$3-47),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;"&amp;($E$3-47)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H55" s="30">
@@ -7667,15 +7667,15 @@
         <v/>
       </c>
       <c r="B56" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;="&amp;($E$3-46),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;"&amp;($E$3-46)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C56" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;="&amp;($E$3-46),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;"&amp;($E$3-46)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D56" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;="&amp;($E$3-46),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;"&amp;($E$3-46)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E56" s="36">
@@ -7687,7 +7687,7 @@
         <v/>
       </c>
       <c r="G56" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;="&amp;($E$3-46),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;"&amp;($E$3-46)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H56" s="37">
@@ -7705,15 +7705,15 @@
         <v/>
       </c>
       <c r="B57" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;="&amp;($E$3-45),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;"&amp;($E$3-45)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C57" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;="&amp;($E$3-45),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;"&amp;($E$3-45)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D57" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;="&amp;($E$3-45),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;"&amp;($E$3-45)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E57" s="29">
@@ -7725,7 +7725,7 @@
         <v/>
       </c>
       <c r="G57" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;="&amp;($E$3-45),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;"&amp;($E$3-45)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H57" s="30">
@@ -7743,15 +7743,15 @@
         <v/>
       </c>
       <c r="B58" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;="&amp;($E$3-44),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;"&amp;($E$3-44)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C58" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;="&amp;($E$3-44),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;"&amp;($E$3-44)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D58" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;="&amp;($E$3-44),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;"&amp;($E$3-44)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E58" s="36">
@@ -7763,7 +7763,7 @@
         <v/>
       </c>
       <c r="G58" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;="&amp;($E$3-44),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;"&amp;($E$3-44)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H58" s="37">
@@ -7781,15 +7781,15 @@
         <v/>
       </c>
       <c r="B59" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;="&amp;($E$3-43),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;"&amp;($E$3-43)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C59" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;="&amp;($E$3-43),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;"&amp;($E$3-43)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D59" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;="&amp;($E$3-43),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;"&amp;($E$3-43)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E59" s="29">
@@ -7801,7 +7801,7 @@
         <v/>
       </c>
       <c r="G59" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;="&amp;($E$3-43),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;"&amp;($E$3-43)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H59" s="30">
@@ -7819,15 +7819,15 @@
         <v/>
       </c>
       <c r="B60" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;="&amp;($E$3-42),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;"&amp;($E$3-42)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C60" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;="&amp;($E$3-42),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;"&amp;($E$3-42)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D60" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;="&amp;($E$3-42),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;"&amp;($E$3-42)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E60" s="36">
@@ -7839,7 +7839,7 @@
         <v/>
       </c>
       <c r="G60" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;="&amp;($E$3-42),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;"&amp;($E$3-42)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H60" s="37">
@@ -7857,15 +7857,15 @@
         <v/>
       </c>
       <c r="B61" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;="&amp;($E$3-41),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;"&amp;($E$3-41)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C61" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;="&amp;($E$3-41),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;"&amp;($E$3-41)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D61" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;="&amp;($E$3-41),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;"&amp;($E$3-41)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E61" s="29">
@@ -7877,7 +7877,7 @@
         <v/>
       </c>
       <c r="G61" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;="&amp;($E$3-41),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;"&amp;($E$3-41)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H61" s="30">
@@ -7895,15 +7895,15 @@
         <v/>
       </c>
       <c r="B62" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;="&amp;($E$3-40),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;"&amp;($E$3-40)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C62" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;="&amp;($E$3-40),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;"&amp;($E$3-40)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D62" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;="&amp;($E$3-40),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;"&amp;($E$3-40)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E62" s="36">
@@ -7915,7 +7915,7 @@
         <v/>
       </c>
       <c r="G62" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;="&amp;($E$3-40),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;"&amp;($E$3-40)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H62" s="37">
@@ -7933,15 +7933,15 @@
         <v/>
       </c>
       <c r="B63" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;="&amp;($E$3-39),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;"&amp;($E$3-39)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C63" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;="&amp;($E$3-39),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;"&amp;($E$3-39)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D63" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;="&amp;($E$3-39),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;"&amp;($E$3-39)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E63" s="29">
@@ -7953,7 +7953,7 @@
         <v/>
       </c>
       <c r="G63" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;="&amp;($E$3-39),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;"&amp;($E$3-39)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H63" s="30">
@@ -7971,15 +7971,15 @@
         <v/>
       </c>
       <c r="B64" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;="&amp;($E$3-38),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;"&amp;($E$3-38)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C64" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;="&amp;($E$3-38),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;"&amp;($E$3-38)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D64" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;="&amp;($E$3-38),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;"&amp;($E$3-38)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E64" s="36">
@@ -7991,7 +7991,7 @@
         <v/>
       </c>
       <c r="G64" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;="&amp;($E$3-38),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;"&amp;($E$3-38)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H64" s="37">
@@ -8009,15 +8009,15 @@
         <v/>
       </c>
       <c r="B65" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;="&amp;($E$3-37),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;"&amp;($E$3-37)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C65" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;="&amp;($E$3-37),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;"&amp;($E$3-37)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D65" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;="&amp;($E$3-37),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;"&amp;($E$3-37)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E65" s="29">
@@ -8029,7 +8029,7 @@
         <v/>
       </c>
       <c r="G65" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;="&amp;($E$3-37),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;"&amp;($E$3-37)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H65" s="30">
@@ -8047,15 +8047,15 @@
         <v/>
       </c>
       <c r="B66" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;="&amp;($E$3-36),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;"&amp;($E$3-36)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C66" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;="&amp;($E$3-36),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;"&amp;($E$3-36)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D66" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;="&amp;($E$3-36),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;"&amp;($E$3-36)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E66" s="36">
@@ -8067,7 +8067,7 @@
         <v/>
       </c>
       <c r="G66" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;="&amp;($E$3-36),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;"&amp;($E$3-36)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H66" s="37">
@@ -8085,15 +8085,15 @@
         <v/>
       </c>
       <c r="B67" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;="&amp;($E$3-35),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;"&amp;($E$3-35)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C67" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;="&amp;($E$3-35),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;"&amp;($E$3-35)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D67" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;="&amp;($E$3-35),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;"&amp;($E$3-35)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E67" s="29">
@@ -8105,7 +8105,7 @@
         <v/>
       </c>
       <c r="G67" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;="&amp;($E$3-35),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;"&amp;($E$3-35)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H67" s="30">
@@ -8123,15 +8123,15 @@
         <v/>
       </c>
       <c r="B68" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;="&amp;($E$3-34),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;"&amp;($E$3-34)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C68" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;="&amp;($E$3-34),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;"&amp;($E$3-34)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D68" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;="&amp;($E$3-34),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;"&amp;($E$3-34)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E68" s="36">
@@ -8143,7 +8143,7 @@
         <v/>
       </c>
       <c r="G68" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;="&amp;($E$3-34),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;"&amp;($E$3-34)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H68" s="37">
@@ -8161,15 +8161,15 @@
         <v/>
       </c>
       <c r="B69" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;="&amp;($E$3-33),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;"&amp;($E$3-33)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C69" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;="&amp;($E$3-33),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;"&amp;($E$3-33)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D69" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;="&amp;($E$3-33),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;"&amp;($E$3-33)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E69" s="29">
@@ -8181,7 +8181,7 @@
         <v/>
       </c>
       <c r="G69" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;="&amp;($E$3-33),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;"&amp;($E$3-33)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H69" s="30">
@@ -8199,15 +8199,15 @@
         <v/>
       </c>
       <c r="B70" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;="&amp;($E$3-32),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;"&amp;($E$3-32)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C70" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;="&amp;($E$3-32),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;"&amp;($E$3-32)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D70" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;="&amp;($E$3-32),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;"&amp;($E$3-32)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E70" s="36">
@@ -8219,7 +8219,7 @@
         <v/>
       </c>
       <c r="G70" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;="&amp;($E$3-32),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;"&amp;($E$3-32)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H70" s="37">
@@ -8237,15 +8237,15 @@
         <v/>
       </c>
       <c r="B71" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;="&amp;($E$3-31),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;"&amp;($E$3-31)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C71" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;="&amp;($E$3-31),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;"&amp;($E$3-31)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D71" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;="&amp;($E$3-31),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;"&amp;($E$3-31)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E71" s="29">
@@ -8257,7 +8257,7 @@
         <v/>
       </c>
       <c r="G71" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;="&amp;($E$3-31),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;"&amp;($E$3-31)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H71" s="30">
@@ -8275,15 +8275,15 @@
         <v/>
       </c>
       <c r="B72" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;="&amp;($E$3-30),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;"&amp;($E$3-30)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C72" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;="&amp;($E$3-30),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;"&amp;($E$3-30)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D72" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;="&amp;($E$3-30),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;"&amp;($E$3-30)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E72" s="36">
@@ -8295,7 +8295,7 @@
         <v/>
       </c>
       <c r="G72" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;="&amp;($E$3-30),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;"&amp;($E$3-30)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H72" s="37">
@@ -8313,15 +8313,15 @@
         <v/>
       </c>
       <c r="B73" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;="&amp;($E$3-29),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;"&amp;($E$3-29)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C73" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;="&amp;($E$3-29),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;"&amp;($E$3-29)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D73" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;="&amp;($E$3-29),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;"&amp;($E$3-29)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E73" s="29">
@@ -8333,7 +8333,7 @@
         <v/>
       </c>
       <c r="G73" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;="&amp;($E$3-29),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;"&amp;($E$3-29)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H73" s="30">
@@ -8351,15 +8351,15 @@
         <v/>
       </c>
       <c r="B74" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;="&amp;($E$3-28),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;"&amp;($E$3-28)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C74" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;="&amp;($E$3-28),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;"&amp;($E$3-28)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D74" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;="&amp;($E$3-28),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;"&amp;($E$3-28)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E74" s="36">
@@ -8371,7 +8371,7 @@
         <v/>
       </c>
       <c r="G74" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;="&amp;($E$3-28),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;"&amp;($E$3-28)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H74" s="37">
@@ -8389,15 +8389,15 @@
         <v/>
       </c>
       <c r="B75" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;="&amp;($E$3-27),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;"&amp;($E$3-27)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C75" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;="&amp;($E$3-27),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;"&amp;($E$3-27)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D75" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;="&amp;($E$3-27),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;"&amp;($E$3-27)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E75" s="29">
@@ -8409,7 +8409,7 @@
         <v/>
       </c>
       <c r="G75" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;="&amp;($E$3-27),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;"&amp;($E$3-27)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H75" s="30">
@@ -8427,15 +8427,15 @@
         <v/>
       </c>
       <c r="B76" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;="&amp;($E$3-26),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;"&amp;($E$3-26)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C76" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;="&amp;($E$3-26),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;"&amp;($E$3-26)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D76" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;="&amp;($E$3-26),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;"&amp;($E$3-26)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E76" s="36">
@@ -8447,7 +8447,7 @@
         <v/>
       </c>
       <c r="G76" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;="&amp;($E$3-26),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;"&amp;($E$3-26)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H76" s="37">
@@ -8465,15 +8465,15 @@
         <v/>
       </c>
       <c r="B77" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;="&amp;($E$3-25),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;"&amp;($E$3-25)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C77" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;="&amp;($E$3-25),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;"&amp;($E$3-25)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D77" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;="&amp;($E$3-25),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;"&amp;($E$3-25)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E77" s="29">
@@ -8485,7 +8485,7 @@
         <v/>
       </c>
       <c r="G77" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;="&amp;($E$3-25),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;"&amp;($E$3-25)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H77" s="30">
@@ -8503,15 +8503,15 @@
         <v/>
       </c>
       <c r="B78" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;="&amp;($E$3-24),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;"&amp;($E$3-24)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C78" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;="&amp;($E$3-24),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;"&amp;($E$3-24)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D78" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;="&amp;($E$3-24),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;"&amp;($E$3-24)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E78" s="36">
@@ -8523,7 +8523,7 @@
         <v/>
       </c>
       <c r="G78" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;="&amp;($E$3-24),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;"&amp;($E$3-24)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H78" s="37">
@@ -8541,15 +8541,15 @@
         <v/>
       </c>
       <c r="B79" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;="&amp;($E$3-23),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;"&amp;($E$3-23)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C79" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;="&amp;($E$3-23),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;"&amp;($E$3-23)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D79" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;="&amp;($E$3-23),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;"&amp;($E$3-23)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E79" s="29">
@@ -8561,7 +8561,7 @@
         <v/>
       </c>
       <c r="G79" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;="&amp;($E$3-23),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;"&amp;($E$3-23)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H79" s="30">
@@ -8579,15 +8579,15 @@
         <v/>
       </c>
       <c r="B80" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;="&amp;($E$3-22),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;"&amp;($E$3-22)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C80" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;="&amp;($E$3-22),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;"&amp;($E$3-22)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D80" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;="&amp;($E$3-22),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;"&amp;($E$3-22)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E80" s="36">
@@ -8599,7 +8599,7 @@
         <v/>
       </c>
       <c r="G80" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;="&amp;($E$3-22),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;"&amp;($E$3-22)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H80" s="37">
@@ -8617,15 +8617,15 @@
         <v/>
       </c>
       <c r="B81" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;="&amp;($E$3-21),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;"&amp;($E$3-21)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C81" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;="&amp;($E$3-21),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;"&amp;($E$3-21)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D81" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;="&amp;($E$3-21),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;"&amp;($E$3-21)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E81" s="29">
@@ -8637,7 +8637,7 @@
         <v/>
       </c>
       <c r="G81" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;="&amp;($E$3-21),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;"&amp;($E$3-21)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H81" s="30">
@@ -8655,15 +8655,15 @@
         <v/>
       </c>
       <c r="B82" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;="&amp;($E$3-20),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;"&amp;($E$3-20)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C82" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;="&amp;($E$3-20),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;"&amp;($E$3-20)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D82" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;="&amp;($E$3-20),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;"&amp;($E$3-20)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E82" s="36">
@@ -8675,7 +8675,7 @@
         <v/>
       </c>
       <c r="G82" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;="&amp;($E$3-20),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;"&amp;($E$3-20)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H82" s="37">
@@ -8693,15 +8693,15 @@
         <v/>
       </c>
       <c r="B83" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;="&amp;($E$3-19),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;"&amp;($E$3-19)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C83" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;="&amp;($E$3-19),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;"&amp;($E$3-19)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D83" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;="&amp;($E$3-19),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;"&amp;($E$3-19)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E83" s="29">
@@ -8713,7 +8713,7 @@
         <v/>
       </c>
       <c r="G83" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;="&amp;($E$3-19),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;"&amp;($E$3-19)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H83" s="30">
@@ -8731,15 +8731,15 @@
         <v/>
       </c>
       <c r="B84" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;="&amp;($E$3-18),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;"&amp;($E$3-18)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C84" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;="&amp;($E$3-18),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;"&amp;($E$3-18)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D84" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;="&amp;($E$3-18),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;"&amp;($E$3-18)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E84" s="36">
@@ -8751,7 +8751,7 @@
         <v/>
       </c>
       <c r="G84" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;="&amp;($E$3-18),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;"&amp;($E$3-18)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H84" s="37">
@@ -8769,15 +8769,15 @@
         <v/>
       </c>
       <c r="B85" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;="&amp;($E$3-17),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;"&amp;($E$3-17)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C85" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;="&amp;($E$3-17),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;"&amp;($E$3-17)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D85" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;="&amp;($E$3-17),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;"&amp;($E$3-17)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E85" s="29">
@@ -8789,7 +8789,7 @@
         <v/>
       </c>
       <c r="G85" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;="&amp;($E$3-17),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;"&amp;($E$3-17)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H85" s="30">
@@ -8807,15 +8807,15 @@
         <v/>
       </c>
       <c r="B86" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;="&amp;($E$3-16),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;"&amp;($E$3-16)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C86" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;="&amp;($E$3-16),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;"&amp;($E$3-16)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D86" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;="&amp;($E$3-16),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;"&amp;($E$3-16)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E86" s="36">
@@ -8827,7 +8827,7 @@
         <v/>
       </c>
       <c r="G86" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;="&amp;($E$3-16),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;"&amp;($E$3-16)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H86" s="37">
@@ -8845,15 +8845,15 @@
         <v/>
       </c>
       <c r="B87" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;="&amp;($E$3-15),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;"&amp;($E$3-15)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C87" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;="&amp;($E$3-15),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;"&amp;($E$3-15)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D87" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;="&amp;($E$3-15),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;"&amp;($E$3-15)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E87" s="29">
@@ -8865,7 +8865,7 @@
         <v/>
       </c>
       <c r="G87" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;="&amp;($E$3-15),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;"&amp;($E$3-15)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H87" s="30">
@@ -8883,15 +8883,15 @@
         <v/>
       </c>
       <c r="B88" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;="&amp;($E$3-14),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;"&amp;($E$3-14)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C88" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;="&amp;($E$3-14),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;"&amp;($E$3-14)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D88" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;="&amp;($E$3-14),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;"&amp;($E$3-14)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E88" s="36">
@@ -8903,7 +8903,7 @@
         <v/>
       </c>
       <c r="G88" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;="&amp;($E$3-14),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;"&amp;($E$3-14)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H88" s="37">
@@ -8921,15 +8921,15 @@
         <v/>
       </c>
       <c r="B89" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;="&amp;($E$3-13),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;"&amp;($E$3-13)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C89" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;="&amp;($E$3-13),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;"&amp;($E$3-13)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D89" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;="&amp;($E$3-13),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;"&amp;($E$3-13)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E89" s="29">
@@ -8941,7 +8941,7 @@
         <v/>
       </c>
       <c r="G89" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;="&amp;($E$3-13),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;"&amp;($E$3-13)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H89" s="30">
@@ -8959,15 +8959,15 @@
         <v/>
       </c>
       <c r="B90" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;="&amp;($E$3-12),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;"&amp;($E$3-12)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C90" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;="&amp;($E$3-12),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;"&amp;($E$3-12)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D90" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;="&amp;($E$3-12),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;"&amp;($E$3-12)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E90" s="36">
@@ -8979,7 +8979,7 @@
         <v/>
       </c>
       <c r="G90" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;="&amp;($E$3-12),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;"&amp;($E$3-12)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H90" s="37">
@@ -8997,15 +8997,15 @@
         <v/>
       </c>
       <c r="B91" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;="&amp;($E$3-11),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;"&amp;($E$3-11)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C91" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;="&amp;($E$3-11),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;"&amp;($E$3-11)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D91" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;="&amp;($E$3-11),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;"&amp;($E$3-11)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E91" s="29">
@@ -9017,7 +9017,7 @@
         <v/>
       </c>
       <c r="G91" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;="&amp;($E$3-11),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;"&amp;($E$3-11)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H91" s="30">
@@ -9035,15 +9035,15 @@
         <v/>
       </c>
       <c r="B92" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;="&amp;($E$3-10),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;"&amp;($E$3-10)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C92" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;="&amp;($E$3-10),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;"&amp;($E$3-10)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D92" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;="&amp;($E$3-10),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;"&amp;($E$3-10)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E92" s="36">
@@ -9055,7 +9055,7 @@
         <v/>
       </c>
       <c r="G92" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;="&amp;($E$3-10),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;"&amp;($E$3-10)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H92" s="37">
@@ -9073,15 +9073,15 @@
         <v/>
       </c>
       <c r="B93" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;="&amp;($E$3-9),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;"&amp;($E$3-9)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C93" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;="&amp;($E$3-9),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;"&amp;($E$3-9)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D93" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;="&amp;($E$3-9),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;"&amp;($E$3-9)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E93" s="29">
@@ -9093,7 +9093,7 @@
         <v/>
       </c>
       <c r="G93" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;="&amp;($E$3-9),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;"&amp;($E$3-9)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H93" s="30">
@@ -9111,15 +9111,15 @@
         <v/>
       </c>
       <c r="B94" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;="&amp;($E$3-8),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;"&amp;($E$3-8)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C94" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;="&amp;($E$3-8),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;"&amp;($E$3-8)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D94" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;="&amp;($E$3-8),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;"&amp;($E$3-8)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E94" s="36">
@@ -9131,7 +9131,7 @@
         <v/>
       </c>
       <c r="G94" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;="&amp;($E$3-8),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;"&amp;($E$3-8)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H94" s="37">
@@ -9149,15 +9149,15 @@
         <v/>
       </c>
       <c r="B95" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;="&amp;($E$3-7),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;"&amp;($E$3-7)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C95" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;="&amp;($E$3-7),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;"&amp;($E$3-7)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D95" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;="&amp;($E$3-7),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;"&amp;($E$3-7)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E95" s="29">
@@ -9169,7 +9169,7 @@
         <v/>
       </c>
       <c r="G95" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;="&amp;($E$3-7),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;"&amp;($E$3-7)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H95" s="30">
@@ -9187,15 +9187,15 @@
         <v/>
       </c>
       <c r="B96" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;="&amp;($E$3-6),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;"&amp;($E$3-6)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C96" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;="&amp;($E$3-6),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;"&amp;($E$3-6)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D96" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;="&amp;($E$3-6),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;"&amp;($E$3-6)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E96" s="36">
@@ -9207,7 +9207,7 @@
         <v/>
       </c>
       <c r="G96" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;="&amp;($E$3-6),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;"&amp;($E$3-6)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H96" s="37">
@@ -9225,15 +9225,15 @@
         <v/>
       </c>
       <c r="B97" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;="&amp;($E$3-5),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;"&amp;($E$3-5)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C97" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;="&amp;($E$3-5),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;"&amp;($E$3-5)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D97" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;="&amp;($E$3-5),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;"&amp;($E$3-5)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E97" s="29">
@@ -9245,7 +9245,7 @@
         <v/>
       </c>
       <c r="G97" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;="&amp;($E$3-5),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;"&amp;($E$3-5)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H97" s="30">
@@ -9263,15 +9263,15 @@
         <v/>
       </c>
       <c r="B98" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;="&amp;($E$3-4),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;"&amp;($E$3-4)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C98" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;="&amp;($E$3-4),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;"&amp;($E$3-4)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D98" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;="&amp;($E$3-4),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;"&amp;($E$3-4)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E98" s="36">
@@ -9283,7 +9283,7 @@
         <v/>
       </c>
       <c r="G98" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;="&amp;($E$3-4),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;"&amp;($E$3-4)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H98" s="37">
@@ -9301,15 +9301,15 @@
         <v/>
       </c>
       <c r="B99" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;="&amp;($E$3-3),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;"&amp;($E$3-3)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C99" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;="&amp;($E$3-3),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;"&amp;($E$3-3)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D99" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;="&amp;($E$3-3),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;"&amp;($E$3-3)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E99" s="29">
@@ -9321,7 +9321,7 @@
         <v/>
       </c>
       <c r="G99" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;="&amp;($E$3-3),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;"&amp;($E$3-3)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H99" s="30">
@@ -9339,15 +9339,15 @@
         <v/>
       </c>
       <c r="B100" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;="&amp;($E$3-2),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;"&amp;($E$3-2)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C100" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;="&amp;($E$3-2),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;"&amp;($E$3-2)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D100" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;="&amp;($E$3-2),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;"&amp;($E$3-2)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E100" s="36">
@@ -9359,7 +9359,7 @@
         <v/>
       </c>
       <c r="G100" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;="&amp;($E$3-2),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;"&amp;($E$3-2)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H100" s="37">
@@ -9377,15 +9377,15 @@
         <v/>
       </c>
       <c r="B101" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;="&amp;($E$3-1),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;"&amp;($E$3-1)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C101" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;="&amp;($E$3-1),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;"&amp;($E$3-1)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D101" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;="&amp;($E$3-1),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;"&amp;($E$3-1)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E101" s="29">
@@ -9397,7 +9397,7 @@
         <v/>
       </c>
       <c r="G101" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;="&amp;($E$3-1),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;"&amp;($E$3-1)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H101" s="30">
@@ -9415,15 +9415,15 @@
         <v/>
       </c>
       <c r="B102" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;="&amp;($E$3-0),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;"&amp;($E$3-0)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C102" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;="&amp;($E$3-0),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;"&amp;($E$3-0)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D102" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;="&amp;($E$3-0),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;"&amp;($E$3-0)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E102" s="36">
@@ -9435,7 +9435,7 @@
         <v/>
       </c>
       <c r="G102" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;="&amp;($E$3-0),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;"&amp;($E$3-0)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H102" s="37">
@@ -9729,15 +9729,15 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C7" s="11">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D7" s="11">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E7" s="12">
@@ -9749,7 +9749,7 @@
         <v/>
       </c>
       <c r="G7" s="11">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H7" s="13">
@@ -9776,15 +9776,15 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;="&amp;$K$8,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;"&amp;$K$8+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C8" s="18">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;="&amp;$K$8,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;"&amp;$K$8+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D8" s="18">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;="&amp;$K$8,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;"&amp;$K$8+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E8" s="19">
@@ -9796,7 +9796,7 @@
         <v/>
       </c>
       <c r="G8" s="18">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;="&amp;$K$8,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;"&amp;$K$8+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H8" s="20">
@@ -9917,15 +9917,15 @@
         <v/>
       </c>
       <c r="B13" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;="&amp;($E$3-89),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;"&amp;($E$3-89)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C13" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;="&amp;($E$3-89),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;"&amp;($E$3-89)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D13" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;="&amp;($E$3-89),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;"&amp;($E$3-89)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E13" s="29">
@@ -9937,7 +9937,7 @@
         <v/>
       </c>
       <c r="G13" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;="&amp;($E$3-89),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;"&amp;($E$3-89)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H13" s="30">
@@ -9955,15 +9955,15 @@
         <v/>
       </c>
       <c r="B14" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;="&amp;($E$3-88),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;"&amp;($E$3-88)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C14" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;="&amp;($E$3-88),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;"&amp;($E$3-88)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D14" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;="&amp;($E$3-88),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;"&amp;($E$3-88)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E14" s="36">
@@ -9975,7 +9975,7 @@
         <v/>
       </c>
       <c r="G14" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;="&amp;($E$3-88),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;"&amp;($E$3-88)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H14" s="37">
@@ -9993,15 +9993,15 @@
         <v/>
       </c>
       <c r="B15" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;="&amp;($E$3-87),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;"&amp;($E$3-87)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C15" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;="&amp;($E$3-87),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;"&amp;($E$3-87)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D15" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;="&amp;($E$3-87),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;"&amp;($E$3-87)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E15" s="29">
@@ -10013,7 +10013,7 @@
         <v/>
       </c>
       <c r="G15" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;="&amp;($E$3-87),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;"&amp;($E$3-87)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H15" s="30">
@@ -10031,15 +10031,15 @@
         <v/>
       </c>
       <c r="B16" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;="&amp;($E$3-86),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;"&amp;($E$3-86)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C16" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;="&amp;($E$3-86),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;"&amp;($E$3-86)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D16" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;="&amp;($E$3-86),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;"&amp;($E$3-86)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E16" s="36">
@@ -10051,7 +10051,7 @@
         <v/>
       </c>
       <c r="G16" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;="&amp;($E$3-86),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;"&amp;($E$3-86)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H16" s="37">
@@ -10069,15 +10069,15 @@
         <v/>
       </c>
       <c r="B17" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;="&amp;($E$3-85),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;"&amp;($E$3-85)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C17" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;="&amp;($E$3-85),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;"&amp;($E$3-85)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D17" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;="&amp;($E$3-85),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;"&amp;($E$3-85)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E17" s="29">
@@ -10089,7 +10089,7 @@
         <v/>
       </c>
       <c r="G17" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;="&amp;($E$3-85),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;"&amp;($E$3-85)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H17" s="30">
@@ -10107,15 +10107,15 @@
         <v/>
       </c>
       <c r="B18" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;="&amp;($E$3-84),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;"&amp;($E$3-84)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C18" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;="&amp;($E$3-84),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;"&amp;($E$3-84)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D18" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;="&amp;($E$3-84),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;"&amp;($E$3-84)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E18" s="36">
@@ -10127,7 +10127,7 @@
         <v/>
       </c>
       <c r="G18" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;="&amp;($E$3-84),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;"&amp;($E$3-84)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H18" s="37">
@@ -10145,15 +10145,15 @@
         <v/>
       </c>
       <c r="B19" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;="&amp;($E$3-83),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;"&amp;($E$3-83)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C19" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;="&amp;($E$3-83),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;"&amp;($E$3-83)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D19" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;="&amp;($E$3-83),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;"&amp;($E$3-83)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E19" s="29">
@@ -10165,7 +10165,7 @@
         <v/>
       </c>
       <c r="G19" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;="&amp;($E$3-83),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;"&amp;($E$3-83)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H19" s="30">
@@ -10183,15 +10183,15 @@
         <v/>
       </c>
       <c r="B20" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;="&amp;($E$3-82),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;"&amp;($E$3-82)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C20" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;="&amp;($E$3-82),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;"&amp;($E$3-82)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D20" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;="&amp;($E$3-82),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;"&amp;($E$3-82)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E20" s="36">
@@ -10203,7 +10203,7 @@
         <v/>
       </c>
       <c r="G20" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;="&amp;($E$3-82),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;"&amp;($E$3-82)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H20" s="37">
@@ -10221,15 +10221,15 @@
         <v/>
       </c>
       <c r="B21" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;="&amp;($E$3-81),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;"&amp;($E$3-81)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C21" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;="&amp;($E$3-81),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;"&amp;($E$3-81)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D21" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;="&amp;($E$3-81),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;"&amp;($E$3-81)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E21" s="29">
@@ -10241,7 +10241,7 @@
         <v/>
       </c>
       <c r="G21" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;="&amp;($E$3-81),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;"&amp;($E$3-81)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H21" s="30">
@@ -10259,15 +10259,15 @@
         <v/>
       </c>
       <c r="B22" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;="&amp;($E$3-80),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;"&amp;($E$3-80)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C22" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;="&amp;($E$3-80),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;"&amp;($E$3-80)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D22" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;="&amp;($E$3-80),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;"&amp;($E$3-80)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E22" s="36">
@@ -10279,7 +10279,7 @@
         <v/>
       </c>
       <c r="G22" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;="&amp;($E$3-80),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;"&amp;($E$3-80)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H22" s="37">
@@ -10297,15 +10297,15 @@
         <v/>
       </c>
       <c r="B23" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;="&amp;($E$3-79),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;"&amp;($E$3-79)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C23" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;="&amp;($E$3-79),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;"&amp;($E$3-79)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D23" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;="&amp;($E$3-79),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;"&amp;($E$3-79)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E23" s="29">
@@ -10317,7 +10317,7 @@
         <v/>
       </c>
       <c r="G23" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;="&amp;($E$3-79),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;"&amp;($E$3-79)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H23" s="30">
@@ -10335,15 +10335,15 @@
         <v/>
       </c>
       <c r="B24" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;="&amp;($E$3-78),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;"&amp;($E$3-78)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C24" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;="&amp;($E$3-78),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;"&amp;($E$3-78)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D24" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;="&amp;($E$3-78),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;"&amp;($E$3-78)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E24" s="36">
@@ -10355,7 +10355,7 @@
         <v/>
       </c>
       <c r="G24" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;="&amp;($E$3-78),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;"&amp;($E$3-78)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H24" s="37">
@@ -10373,15 +10373,15 @@
         <v/>
       </c>
       <c r="B25" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;="&amp;($E$3-77),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;"&amp;($E$3-77)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C25" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;="&amp;($E$3-77),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;"&amp;($E$3-77)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D25" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;="&amp;($E$3-77),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;"&amp;($E$3-77)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E25" s="29">
@@ -10393,7 +10393,7 @@
         <v/>
       </c>
       <c r="G25" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;="&amp;($E$3-77),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;"&amp;($E$3-77)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H25" s="30">
@@ -10411,15 +10411,15 @@
         <v/>
       </c>
       <c r="B26" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;="&amp;($E$3-76),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;"&amp;($E$3-76)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C26" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;="&amp;($E$3-76),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;"&amp;($E$3-76)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D26" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;="&amp;($E$3-76),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;"&amp;($E$3-76)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E26" s="36">
@@ -10431,7 +10431,7 @@
         <v/>
       </c>
       <c r="G26" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;="&amp;($E$3-76),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;"&amp;($E$3-76)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H26" s="37">
@@ -10449,15 +10449,15 @@
         <v/>
       </c>
       <c r="B27" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;="&amp;($E$3-75),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;"&amp;($E$3-75)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C27" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;="&amp;($E$3-75),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;"&amp;($E$3-75)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D27" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;="&amp;($E$3-75),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;"&amp;($E$3-75)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E27" s="29">
@@ -10469,7 +10469,7 @@
         <v/>
       </c>
       <c r="G27" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;="&amp;($E$3-75),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;"&amp;($E$3-75)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H27" s="30">
@@ -10487,15 +10487,15 @@
         <v/>
       </c>
       <c r="B28" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;="&amp;($E$3-74),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;"&amp;($E$3-74)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C28" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;="&amp;($E$3-74),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;"&amp;($E$3-74)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D28" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;="&amp;($E$3-74),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;"&amp;($E$3-74)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E28" s="36">
@@ -10507,7 +10507,7 @@
         <v/>
       </c>
       <c r="G28" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;="&amp;($E$3-74),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;"&amp;($E$3-74)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H28" s="37">
@@ -10525,15 +10525,15 @@
         <v/>
       </c>
       <c r="B29" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;="&amp;($E$3-73),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;"&amp;($E$3-73)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C29" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;="&amp;($E$3-73),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;"&amp;($E$3-73)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D29" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;="&amp;($E$3-73),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;"&amp;($E$3-73)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E29" s="29">
@@ -10545,7 +10545,7 @@
         <v/>
       </c>
       <c r="G29" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;="&amp;($E$3-73),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;"&amp;($E$3-73)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H29" s="30">
@@ -10563,15 +10563,15 @@
         <v/>
       </c>
       <c r="B30" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;="&amp;($E$3-72),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;"&amp;($E$3-72)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C30" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;="&amp;($E$3-72),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;"&amp;($E$3-72)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D30" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;="&amp;($E$3-72),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;"&amp;($E$3-72)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E30" s="36">
@@ -10583,7 +10583,7 @@
         <v/>
       </c>
       <c r="G30" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;="&amp;($E$3-72),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;"&amp;($E$3-72)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H30" s="37">
@@ -10601,15 +10601,15 @@
         <v/>
       </c>
       <c r="B31" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;="&amp;($E$3-71),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;"&amp;($E$3-71)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C31" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;="&amp;($E$3-71),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;"&amp;($E$3-71)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D31" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;="&amp;($E$3-71),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;"&amp;($E$3-71)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E31" s="29">
@@ -10621,7 +10621,7 @@
         <v/>
       </c>
       <c r="G31" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;="&amp;($E$3-71),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;"&amp;($E$3-71)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H31" s="30">
@@ -10639,15 +10639,15 @@
         <v/>
       </c>
       <c r="B32" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;="&amp;($E$3-70),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;"&amp;($E$3-70)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C32" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;="&amp;($E$3-70),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;"&amp;($E$3-70)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D32" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;="&amp;($E$3-70),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;"&amp;($E$3-70)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E32" s="36">
@@ -10659,7 +10659,7 @@
         <v/>
       </c>
       <c r="G32" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;="&amp;($E$3-70),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;"&amp;($E$3-70)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H32" s="37">
@@ -10677,15 +10677,15 @@
         <v/>
       </c>
       <c r="B33" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;="&amp;($E$3-69),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;"&amp;($E$3-69)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C33" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;="&amp;($E$3-69),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;"&amp;($E$3-69)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D33" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;="&amp;($E$3-69),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;"&amp;($E$3-69)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E33" s="29">
@@ -10697,7 +10697,7 @@
         <v/>
       </c>
       <c r="G33" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;="&amp;($E$3-69),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;"&amp;($E$3-69)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H33" s="30">
@@ -10715,15 +10715,15 @@
         <v/>
       </c>
       <c r="B34" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;="&amp;($E$3-68),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;"&amp;($E$3-68)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C34" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;="&amp;($E$3-68),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;"&amp;($E$3-68)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D34" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;="&amp;($E$3-68),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;"&amp;($E$3-68)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E34" s="36">
@@ -10735,7 +10735,7 @@
         <v/>
       </c>
       <c r="G34" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;="&amp;($E$3-68),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;"&amp;($E$3-68)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H34" s="37">
@@ -10753,15 +10753,15 @@
         <v/>
       </c>
       <c r="B35" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;="&amp;($E$3-67),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;"&amp;($E$3-67)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C35" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;="&amp;($E$3-67),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;"&amp;($E$3-67)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D35" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;="&amp;($E$3-67),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;"&amp;($E$3-67)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E35" s="29">
@@ -10773,7 +10773,7 @@
         <v/>
       </c>
       <c r="G35" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;="&amp;($E$3-67),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;"&amp;($E$3-67)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H35" s="30">
@@ -10791,15 +10791,15 @@
         <v/>
       </c>
       <c r="B36" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;="&amp;($E$3-66),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;"&amp;($E$3-66)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C36" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;="&amp;($E$3-66),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;"&amp;($E$3-66)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D36" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;="&amp;($E$3-66),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;"&amp;($E$3-66)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E36" s="36">
@@ -10811,7 +10811,7 @@
         <v/>
       </c>
       <c r="G36" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;="&amp;($E$3-66),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;"&amp;($E$3-66)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H36" s="37">
@@ -10829,15 +10829,15 @@
         <v/>
       </c>
       <c r="B37" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;="&amp;($E$3-65),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;"&amp;($E$3-65)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C37" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;="&amp;($E$3-65),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;"&amp;($E$3-65)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D37" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;="&amp;($E$3-65),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;"&amp;($E$3-65)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E37" s="29">
@@ -10849,7 +10849,7 @@
         <v/>
       </c>
       <c r="G37" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;="&amp;($E$3-65),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;"&amp;($E$3-65)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H37" s="30">
@@ -10867,15 +10867,15 @@
         <v/>
       </c>
       <c r="B38" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;="&amp;($E$3-64),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;"&amp;($E$3-64)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C38" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;="&amp;($E$3-64),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;"&amp;($E$3-64)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D38" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;="&amp;($E$3-64),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;"&amp;($E$3-64)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E38" s="36">
@@ -10887,7 +10887,7 @@
         <v/>
       </c>
       <c r="G38" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;="&amp;($E$3-64),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;"&amp;($E$3-64)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H38" s="37">
@@ -10905,15 +10905,15 @@
         <v/>
       </c>
       <c r="B39" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;="&amp;($E$3-63),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;"&amp;($E$3-63)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C39" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;="&amp;($E$3-63),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;"&amp;($E$3-63)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D39" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;="&amp;($E$3-63),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;"&amp;($E$3-63)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E39" s="29">
@@ -10925,7 +10925,7 @@
         <v/>
       </c>
       <c r="G39" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;="&amp;($E$3-63),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;"&amp;($E$3-63)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H39" s="30">
@@ -10943,15 +10943,15 @@
         <v/>
       </c>
       <c r="B40" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;="&amp;($E$3-62),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;"&amp;($E$3-62)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C40" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;="&amp;($E$3-62),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;"&amp;($E$3-62)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D40" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;="&amp;($E$3-62),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;"&amp;($E$3-62)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E40" s="36">
@@ -10963,7 +10963,7 @@
         <v/>
       </c>
       <c r="G40" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;="&amp;($E$3-62),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;"&amp;($E$3-62)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H40" s="37">
@@ -10981,15 +10981,15 @@
         <v/>
       </c>
       <c r="B41" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;="&amp;($E$3-61),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;"&amp;($E$3-61)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C41" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;="&amp;($E$3-61),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;"&amp;($E$3-61)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D41" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;="&amp;($E$3-61),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;"&amp;($E$3-61)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E41" s="29">
@@ -11001,7 +11001,7 @@
         <v/>
       </c>
       <c r="G41" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;="&amp;($E$3-61),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;"&amp;($E$3-61)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H41" s="30">
@@ -11019,15 +11019,15 @@
         <v/>
       </c>
       <c r="B42" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;="&amp;($E$3-60),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;"&amp;($E$3-60)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C42" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;="&amp;($E$3-60),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;"&amp;($E$3-60)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D42" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;="&amp;($E$3-60),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;"&amp;($E$3-60)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E42" s="36">
@@ -11039,7 +11039,7 @@
         <v/>
       </c>
       <c r="G42" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;="&amp;($E$3-60),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;"&amp;($E$3-60)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H42" s="37">
@@ -11057,15 +11057,15 @@
         <v/>
       </c>
       <c r="B43" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;="&amp;($E$3-59),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;"&amp;($E$3-59)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C43" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;="&amp;($E$3-59),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;"&amp;($E$3-59)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D43" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;="&amp;($E$3-59),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;"&amp;($E$3-59)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E43" s="29">
@@ -11077,7 +11077,7 @@
         <v/>
       </c>
       <c r="G43" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;="&amp;($E$3-59),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;"&amp;($E$3-59)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H43" s="30">
@@ -11095,15 +11095,15 @@
         <v/>
       </c>
       <c r="B44" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;="&amp;($E$3-58),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;"&amp;($E$3-58)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C44" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;="&amp;($E$3-58),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;"&amp;($E$3-58)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D44" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;="&amp;($E$3-58),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;"&amp;($E$3-58)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E44" s="36">
@@ -11115,7 +11115,7 @@
         <v/>
       </c>
       <c r="G44" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;="&amp;($E$3-58),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;"&amp;($E$3-58)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H44" s="37">
@@ -11133,15 +11133,15 @@
         <v/>
       </c>
       <c r="B45" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;="&amp;($E$3-57),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;"&amp;($E$3-57)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C45" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;="&amp;($E$3-57),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;"&amp;($E$3-57)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D45" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;="&amp;($E$3-57),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;"&amp;($E$3-57)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E45" s="29">
@@ -11153,7 +11153,7 @@
         <v/>
       </c>
       <c r="G45" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;="&amp;($E$3-57),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;"&amp;($E$3-57)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H45" s="30">
@@ -11171,15 +11171,15 @@
         <v/>
       </c>
       <c r="B46" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;="&amp;($E$3-56),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;"&amp;($E$3-56)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C46" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;="&amp;($E$3-56),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;"&amp;($E$3-56)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D46" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;="&amp;($E$3-56),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;"&amp;($E$3-56)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E46" s="36">
@@ -11191,7 +11191,7 @@
         <v/>
       </c>
       <c r="G46" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;="&amp;($E$3-56),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;"&amp;($E$3-56)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H46" s="37">
@@ -11209,15 +11209,15 @@
         <v/>
       </c>
       <c r="B47" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;="&amp;($E$3-55),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;"&amp;($E$3-55)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C47" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;="&amp;($E$3-55),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;"&amp;($E$3-55)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D47" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;="&amp;($E$3-55),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;"&amp;($E$3-55)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E47" s="29">
@@ -11229,7 +11229,7 @@
         <v/>
       </c>
       <c r="G47" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;="&amp;($E$3-55),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;"&amp;($E$3-55)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H47" s="30">
@@ -11247,15 +11247,15 @@
         <v/>
       </c>
       <c r="B48" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;="&amp;($E$3-54),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;"&amp;($E$3-54)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C48" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;="&amp;($E$3-54),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;"&amp;($E$3-54)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D48" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;="&amp;($E$3-54),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;"&amp;($E$3-54)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E48" s="36">
@@ -11267,7 +11267,7 @@
         <v/>
       </c>
       <c r="G48" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;="&amp;($E$3-54),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;"&amp;($E$3-54)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H48" s="37">
@@ -11285,15 +11285,15 @@
         <v/>
       </c>
       <c r="B49" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;="&amp;($E$3-53),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;"&amp;($E$3-53)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C49" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;="&amp;($E$3-53),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;"&amp;($E$3-53)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D49" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;="&amp;($E$3-53),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;"&amp;($E$3-53)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E49" s="29">
@@ -11305,7 +11305,7 @@
         <v/>
       </c>
       <c r="G49" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;="&amp;($E$3-53),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;"&amp;($E$3-53)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H49" s="30">
@@ -11323,15 +11323,15 @@
         <v/>
       </c>
       <c r="B50" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;="&amp;($E$3-52),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;"&amp;($E$3-52)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C50" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;="&amp;($E$3-52),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;"&amp;($E$3-52)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D50" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;="&amp;($E$3-52),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;"&amp;($E$3-52)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E50" s="36">
@@ -11343,7 +11343,7 @@
         <v/>
       </c>
       <c r="G50" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;="&amp;($E$3-52),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;"&amp;($E$3-52)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H50" s="37">
@@ -11361,15 +11361,15 @@
         <v/>
       </c>
       <c r="B51" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;="&amp;($E$3-51),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;"&amp;($E$3-51)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C51" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;="&amp;($E$3-51),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;"&amp;($E$3-51)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D51" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;="&amp;($E$3-51),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;"&amp;($E$3-51)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E51" s="29">
@@ -11381,7 +11381,7 @@
         <v/>
       </c>
       <c r="G51" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;="&amp;($E$3-51),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;"&amp;($E$3-51)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H51" s="30">
@@ -11399,15 +11399,15 @@
         <v/>
       </c>
       <c r="B52" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;="&amp;($E$3-50),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;"&amp;($E$3-50)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C52" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;="&amp;($E$3-50),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;"&amp;($E$3-50)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D52" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;="&amp;($E$3-50),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;"&amp;($E$3-50)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E52" s="36">
@@ -11419,7 +11419,7 @@
         <v/>
       </c>
       <c r="G52" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;="&amp;($E$3-50),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;"&amp;($E$3-50)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H52" s="37">
@@ -11437,15 +11437,15 @@
         <v/>
       </c>
       <c r="B53" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;="&amp;($E$3-49),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;"&amp;($E$3-49)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C53" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;="&amp;($E$3-49),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;"&amp;($E$3-49)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D53" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;="&amp;($E$3-49),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;"&amp;($E$3-49)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E53" s="29">
@@ -11457,7 +11457,7 @@
         <v/>
       </c>
       <c r="G53" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;="&amp;($E$3-49),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;"&amp;($E$3-49)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H53" s="30">
@@ -11475,15 +11475,15 @@
         <v/>
       </c>
       <c r="B54" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;="&amp;($E$3-48),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;"&amp;($E$3-48)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C54" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;="&amp;($E$3-48),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;"&amp;($E$3-48)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D54" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;="&amp;($E$3-48),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;"&amp;($E$3-48)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E54" s="36">
@@ -11495,7 +11495,7 @@
         <v/>
       </c>
       <c r="G54" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;="&amp;($E$3-48),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;"&amp;($E$3-48)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H54" s="37">
@@ -11513,15 +11513,15 @@
         <v/>
       </c>
       <c r="B55" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;="&amp;($E$3-47),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;"&amp;($E$3-47)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C55" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;="&amp;($E$3-47),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;"&amp;($E$3-47)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D55" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;="&amp;($E$3-47),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;"&amp;($E$3-47)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E55" s="29">
@@ -11533,7 +11533,7 @@
         <v/>
       </c>
       <c r="G55" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;="&amp;($E$3-47),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;"&amp;($E$3-47)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H55" s="30">
@@ -11551,15 +11551,15 @@
         <v/>
       </c>
       <c r="B56" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;="&amp;($E$3-46),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;"&amp;($E$3-46)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C56" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;="&amp;($E$3-46),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;"&amp;($E$3-46)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D56" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;="&amp;($E$3-46),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;"&amp;($E$3-46)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E56" s="36">
@@ -11571,7 +11571,7 @@
         <v/>
       </c>
       <c r="G56" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;="&amp;($E$3-46),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;"&amp;($E$3-46)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H56" s="37">
@@ -11589,15 +11589,15 @@
         <v/>
       </c>
       <c r="B57" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;="&amp;($E$3-45),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;"&amp;($E$3-45)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C57" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;="&amp;($E$3-45),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;"&amp;($E$3-45)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D57" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;="&amp;($E$3-45),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;"&amp;($E$3-45)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E57" s="29">
@@ -11609,7 +11609,7 @@
         <v/>
       </c>
       <c r="G57" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;="&amp;($E$3-45),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;"&amp;($E$3-45)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H57" s="30">
@@ -11627,15 +11627,15 @@
         <v/>
       </c>
       <c r="B58" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;="&amp;($E$3-44),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;"&amp;($E$3-44)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C58" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;="&amp;($E$3-44),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;"&amp;($E$3-44)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D58" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;="&amp;($E$3-44),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;"&amp;($E$3-44)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E58" s="36">
@@ -11647,7 +11647,7 @@
         <v/>
       </c>
       <c r="G58" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;="&amp;($E$3-44),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;"&amp;($E$3-44)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H58" s="37">
@@ -11665,15 +11665,15 @@
         <v/>
       </c>
       <c r="B59" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;="&amp;($E$3-43),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;"&amp;($E$3-43)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C59" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;="&amp;($E$3-43),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;"&amp;($E$3-43)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D59" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;="&amp;($E$3-43),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;"&amp;($E$3-43)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E59" s="29">
@@ -11685,7 +11685,7 @@
         <v/>
       </c>
       <c r="G59" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;="&amp;($E$3-43),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;"&amp;($E$3-43)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H59" s="30">
@@ -11703,15 +11703,15 @@
         <v/>
       </c>
       <c r="B60" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;="&amp;($E$3-42),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;"&amp;($E$3-42)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C60" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;="&amp;($E$3-42),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;"&amp;($E$3-42)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D60" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;="&amp;($E$3-42),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;"&amp;($E$3-42)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E60" s="36">
@@ -11723,7 +11723,7 @@
         <v/>
       </c>
       <c r="G60" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;="&amp;($E$3-42),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;"&amp;($E$3-42)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H60" s="37">
@@ -11741,15 +11741,15 @@
         <v/>
       </c>
       <c r="B61" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;="&amp;($E$3-41),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;"&amp;($E$3-41)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C61" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;="&amp;($E$3-41),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;"&amp;($E$3-41)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D61" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;="&amp;($E$3-41),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;"&amp;($E$3-41)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E61" s="29">
@@ -11761,7 +11761,7 @@
         <v/>
       </c>
       <c r="G61" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;="&amp;($E$3-41),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;"&amp;($E$3-41)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H61" s="30">
@@ -11779,15 +11779,15 @@
         <v/>
       </c>
       <c r="B62" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;="&amp;($E$3-40),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;"&amp;($E$3-40)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C62" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;="&amp;($E$3-40),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;"&amp;($E$3-40)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D62" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;="&amp;($E$3-40),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;"&amp;($E$3-40)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E62" s="36">
@@ -11799,7 +11799,7 @@
         <v/>
       </c>
       <c r="G62" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;="&amp;($E$3-40),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;"&amp;($E$3-40)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H62" s="37">
@@ -11817,15 +11817,15 @@
         <v/>
       </c>
       <c r="B63" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;="&amp;($E$3-39),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;"&amp;($E$3-39)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C63" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;="&amp;($E$3-39),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;"&amp;($E$3-39)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D63" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;="&amp;($E$3-39),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;"&amp;($E$3-39)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E63" s="29">
@@ -11837,7 +11837,7 @@
         <v/>
       </c>
       <c r="G63" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;="&amp;($E$3-39),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;"&amp;($E$3-39)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H63" s="30">
@@ -11855,15 +11855,15 @@
         <v/>
       </c>
       <c r="B64" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;="&amp;($E$3-38),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;"&amp;($E$3-38)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C64" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;="&amp;($E$3-38),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;"&amp;($E$3-38)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D64" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;="&amp;($E$3-38),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;"&amp;($E$3-38)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E64" s="36">
@@ -11875,7 +11875,7 @@
         <v/>
       </c>
       <c r="G64" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;="&amp;($E$3-38),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;"&amp;($E$3-38)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H64" s="37">
@@ -11893,15 +11893,15 @@
         <v/>
       </c>
       <c r="B65" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;="&amp;($E$3-37),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;"&amp;($E$3-37)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C65" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;="&amp;($E$3-37),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;"&amp;($E$3-37)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D65" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;="&amp;($E$3-37),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;"&amp;($E$3-37)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E65" s="29">
@@ -11913,7 +11913,7 @@
         <v/>
       </c>
       <c r="G65" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;="&amp;($E$3-37),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;"&amp;($E$3-37)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H65" s="30">
@@ -11931,15 +11931,15 @@
         <v/>
       </c>
       <c r="B66" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;="&amp;($E$3-36),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;"&amp;($E$3-36)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C66" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;="&amp;($E$3-36),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;"&amp;($E$3-36)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D66" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;="&amp;($E$3-36),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;"&amp;($E$3-36)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E66" s="36">
@@ -11951,7 +11951,7 @@
         <v/>
       </c>
       <c r="G66" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;="&amp;($E$3-36),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;"&amp;($E$3-36)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H66" s="37">
@@ -11969,15 +11969,15 @@
         <v/>
       </c>
       <c r="B67" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;="&amp;($E$3-35),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;"&amp;($E$3-35)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C67" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;="&amp;($E$3-35),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;"&amp;($E$3-35)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D67" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;="&amp;($E$3-35),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;"&amp;($E$3-35)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E67" s="29">
@@ -11989,7 +11989,7 @@
         <v/>
       </c>
       <c r="G67" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;="&amp;($E$3-35),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;"&amp;($E$3-35)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H67" s="30">
@@ -12007,15 +12007,15 @@
         <v/>
       </c>
       <c r="B68" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;="&amp;($E$3-34),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;"&amp;($E$3-34)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C68" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;="&amp;($E$3-34),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;"&amp;($E$3-34)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D68" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;="&amp;($E$3-34),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;"&amp;($E$3-34)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E68" s="36">
@@ -12027,7 +12027,7 @@
         <v/>
       </c>
       <c r="G68" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;="&amp;($E$3-34),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;"&amp;($E$3-34)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H68" s="37">
@@ -12045,15 +12045,15 @@
         <v/>
       </c>
       <c r="B69" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;="&amp;($E$3-33),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;"&amp;($E$3-33)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C69" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;="&amp;($E$3-33),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;"&amp;($E$3-33)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D69" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;="&amp;($E$3-33),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;"&amp;($E$3-33)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E69" s="29">
@@ -12065,7 +12065,7 @@
         <v/>
       </c>
       <c r="G69" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;="&amp;($E$3-33),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;"&amp;($E$3-33)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H69" s="30">
@@ -12083,15 +12083,15 @@
         <v/>
       </c>
       <c r="B70" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;="&amp;($E$3-32),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;"&amp;($E$3-32)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C70" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;="&amp;($E$3-32),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;"&amp;($E$3-32)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D70" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;="&amp;($E$3-32),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;"&amp;($E$3-32)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E70" s="36">
@@ -12103,7 +12103,7 @@
         <v/>
       </c>
       <c r="G70" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;="&amp;($E$3-32),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;"&amp;($E$3-32)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H70" s="37">
@@ -12121,15 +12121,15 @@
         <v/>
       </c>
       <c r="B71" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;="&amp;($E$3-31),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;"&amp;($E$3-31)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C71" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;="&amp;($E$3-31),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;"&amp;($E$3-31)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D71" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;="&amp;($E$3-31),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;"&amp;($E$3-31)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E71" s="29">
@@ -12141,7 +12141,7 @@
         <v/>
       </c>
       <c r="G71" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;="&amp;($E$3-31),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;"&amp;($E$3-31)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H71" s="30">
@@ -12159,15 +12159,15 @@
         <v/>
       </c>
       <c r="B72" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;="&amp;($E$3-30),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;"&amp;($E$3-30)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C72" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;="&amp;($E$3-30),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;"&amp;($E$3-30)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D72" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;="&amp;($E$3-30),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;"&amp;($E$3-30)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E72" s="36">
@@ -12179,7 +12179,7 @@
         <v/>
       </c>
       <c r="G72" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;="&amp;($E$3-30),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;"&amp;($E$3-30)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H72" s="37">
@@ -12197,15 +12197,15 @@
         <v/>
       </c>
       <c r="B73" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;="&amp;($E$3-29),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;"&amp;($E$3-29)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C73" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;="&amp;($E$3-29),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;"&amp;($E$3-29)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D73" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;="&amp;($E$3-29),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;"&amp;($E$3-29)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E73" s="29">
@@ -12217,7 +12217,7 @@
         <v/>
       </c>
       <c r="G73" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;="&amp;($E$3-29),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;"&amp;($E$3-29)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H73" s="30">
@@ -12235,15 +12235,15 @@
         <v/>
       </c>
       <c r="B74" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;="&amp;($E$3-28),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;"&amp;($E$3-28)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C74" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;="&amp;($E$3-28),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;"&amp;($E$3-28)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D74" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;="&amp;($E$3-28),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;"&amp;($E$3-28)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E74" s="36">
@@ -12255,7 +12255,7 @@
         <v/>
       </c>
       <c r="G74" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;="&amp;($E$3-28),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;"&amp;($E$3-28)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H74" s="37">
@@ -12273,15 +12273,15 @@
         <v/>
       </c>
       <c r="B75" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;="&amp;($E$3-27),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;"&amp;($E$3-27)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C75" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;="&amp;($E$3-27),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;"&amp;($E$3-27)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D75" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;="&amp;($E$3-27),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;"&amp;($E$3-27)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E75" s="29">
@@ -12293,7 +12293,7 @@
         <v/>
       </c>
       <c r="G75" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;="&amp;($E$3-27),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;"&amp;($E$3-27)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H75" s="30">
@@ -12311,15 +12311,15 @@
         <v/>
       </c>
       <c r="B76" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;="&amp;($E$3-26),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;"&amp;($E$3-26)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C76" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;="&amp;($E$3-26),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;"&amp;($E$3-26)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D76" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;="&amp;($E$3-26),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;"&amp;($E$3-26)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E76" s="36">
@@ -12331,7 +12331,7 @@
         <v/>
       </c>
       <c r="G76" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;="&amp;($E$3-26),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;"&amp;($E$3-26)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H76" s="37">
@@ -12349,15 +12349,15 @@
         <v/>
       </c>
       <c r="B77" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;="&amp;($E$3-25),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;"&amp;($E$3-25)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C77" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;="&amp;($E$3-25),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;"&amp;($E$3-25)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D77" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;="&amp;($E$3-25),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;"&amp;($E$3-25)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E77" s="29">
@@ -12369,7 +12369,7 @@
         <v/>
       </c>
       <c r="G77" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;="&amp;($E$3-25),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;"&amp;($E$3-25)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H77" s="30">
@@ -12387,15 +12387,15 @@
         <v/>
       </c>
       <c r="B78" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;="&amp;($E$3-24),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;"&amp;($E$3-24)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C78" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;="&amp;($E$3-24),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;"&amp;($E$3-24)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D78" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;="&amp;($E$3-24),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;"&amp;($E$3-24)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E78" s="36">
@@ -12407,7 +12407,7 @@
         <v/>
       </c>
       <c r="G78" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;="&amp;($E$3-24),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;"&amp;($E$3-24)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H78" s="37">
@@ -12425,15 +12425,15 @@
         <v/>
       </c>
       <c r="B79" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;="&amp;($E$3-23),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;"&amp;($E$3-23)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C79" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;="&amp;($E$3-23),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;"&amp;($E$3-23)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D79" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;="&amp;($E$3-23),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;"&amp;($E$3-23)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E79" s="29">
@@ -12445,7 +12445,7 @@
         <v/>
       </c>
       <c r="G79" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;="&amp;($E$3-23),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;"&amp;($E$3-23)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H79" s="30">
@@ -12463,15 +12463,15 @@
         <v/>
       </c>
       <c r="B80" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;="&amp;($E$3-22),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;"&amp;($E$3-22)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C80" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;="&amp;($E$3-22),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;"&amp;($E$3-22)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D80" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;="&amp;($E$3-22),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;"&amp;($E$3-22)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E80" s="36">
@@ -12483,7 +12483,7 @@
         <v/>
       </c>
       <c r="G80" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;="&amp;($E$3-22),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;"&amp;($E$3-22)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H80" s="37">
@@ -12501,15 +12501,15 @@
         <v/>
       </c>
       <c r="B81" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;="&amp;($E$3-21),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;"&amp;($E$3-21)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C81" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;="&amp;($E$3-21),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;"&amp;($E$3-21)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D81" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;="&amp;($E$3-21),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;"&amp;($E$3-21)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E81" s="29">
@@ -12521,7 +12521,7 @@
         <v/>
       </c>
       <c r="G81" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;="&amp;($E$3-21),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;"&amp;($E$3-21)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H81" s="30">
@@ -12539,15 +12539,15 @@
         <v/>
       </c>
       <c r="B82" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;="&amp;($E$3-20),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;"&amp;($E$3-20)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C82" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;="&amp;($E$3-20),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;"&amp;($E$3-20)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D82" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;="&amp;($E$3-20),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;"&amp;($E$3-20)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E82" s="36">
@@ -12559,7 +12559,7 @@
         <v/>
       </c>
       <c r="G82" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;="&amp;($E$3-20),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;"&amp;($E$3-20)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H82" s="37">
@@ -12577,15 +12577,15 @@
         <v/>
       </c>
       <c r="B83" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;="&amp;($E$3-19),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;"&amp;($E$3-19)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C83" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;="&amp;($E$3-19),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;"&amp;($E$3-19)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D83" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;="&amp;($E$3-19),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;"&amp;($E$3-19)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E83" s="29">
@@ -12597,7 +12597,7 @@
         <v/>
       </c>
       <c r="G83" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;="&amp;($E$3-19),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;"&amp;($E$3-19)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H83" s="30">
@@ -12615,15 +12615,15 @@
         <v/>
       </c>
       <c r="B84" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;="&amp;($E$3-18),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;"&amp;($E$3-18)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C84" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;="&amp;($E$3-18),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;"&amp;($E$3-18)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D84" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;="&amp;($E$3-18),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;"&amp;($E$3-18)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E84" s="36">
@@ -12635,7 +12635,7 @@
         <v/>
       </c>
       <c r="G84" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;="&amp;($E$3-18),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;"&amp;($E$3-18)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H84" s="37">
@@ -12653,15 +12653,15 @@
         <v/>
       </c>
       <c r="B85" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;="&amp;($E$3-17),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;"&amp;($E$3-17)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C85" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;="&amp;($E$3-17),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;"&amp;($E$3-17)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D85" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;="&amp;($E$3-17),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;"&amp;($E$3-17)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E85" s="29">
@@ -12673,7 +12673,7 @@
         <v/>
       </c>
       <c r="G85" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;="&amp;($E$3-17),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;"&amp;($E$3-17)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H85" s="30">
@@ -12691,15 +12691,15 @@
         <v/>
       </c>
       <c r="B86" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;="&amp;($E$3-16),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;"&amp;($E$3-16)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C86" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;="&amp;($E$3-16),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;"&amp;($E$3-16)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D86" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;="&amp;($E$3-16),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;"&amp;($E$3-16)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E86" s="36">
@@ -12711,7 +12711,7 @@
         <v/>
       </c>
       <c r="G86" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;="&amp;($E$3-16),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;"&amp;($E$3-16)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H86" s="37">
@@ -12729,15 +12729,15 @@
         <v/>
       </c>
       <c r="B87" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;="&amp;($E$3-15),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;"&amp;($E$3-15)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C87" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;="&amp;($E$3-15),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;"&amp;($E$3-15)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D87" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;="&amp;($E$3-15),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;"&amp;($E$3-15)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E87" s="29">
@@ -12749,7 +12749,7 @@
         <v/>
       </c>
       <c r="G87" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;="&amp;($E$3-15),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;"&amp;($E$3-15)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H87" s="30">
@@ -12767,15 +12767,15 @@
         <v/>
       </c>
       <c r="B88" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;="&amp;($E$3-14),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;"&amp;($E$3-14)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C88" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;="&amp;($E$3-14),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;"&amp;($E$3-14)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D88" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;="&amp;($E$3-14),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;"&amp;($E$3-14)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E88" s="36">
@@ -12787,7 +12787,7 @@
         <v/>
       </c>
       <c r="G88" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;="&amp;($E$3-14),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;"&amp;($E$3-14)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H88" s="37">
@@ -12805,15 +12805,15 @@
         <v/>
       </c>
       <c r="B89" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;="&amp;($E$3-13),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;"&amp;($E$3-13)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C89" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;="&amp;($E$3-13),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;"&amp;($E$3-13)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D89" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;="&amp;($E$3-13),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;"&amp;($E$3-13)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E89" s="29">
@@ -12825,7 +12825,7 @@
         <v/>
       </c>
       <c r="G89" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;="&amp;($E$3-13),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;"&amp;($E$3-13)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H89" s="30">
@@ -12843,15 +12843,15 @@
         <v/>
       </c>
       <c r="B90" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;="&amp;($E$3-12),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;"&amp;($E$3-12)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C90" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;="&amp;($E$3-12),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;"&amp;($E$3-12)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D90" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;="&amp;($E$3-12),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;"&amp;($E$3-12)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E90" s="36">
@@ -12863,7 +12863,7 @@
         <v/>
       </c>
       <c r="G90" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;="&amp;($E$3-12),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;"&amp;($E$3-12)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H90" s="37">
@@ -12881,15 +12881,15 @@
         <v/>
       </c>
       <c r="B91" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;="&amp;($E$3-11),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;"&amp;($E$3-11)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C91" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;="&amp;($E$3-11),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;"&amp;($E$3-11)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D91" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;="&amp;($E$3-11),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;"&amp;($E$3-11)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E91" s="29">
@@ -12901,7 +12901,7 @@
         <v/>
       </c>
       <c r="G91" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;="&amp;($E$3-11),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;"&amp;($E$3-11)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H91" s="30">
@@ -12919,15 +12919,15 @@
         <v/>
       </c>
       <c r="B92" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;="&amp;($E$3-10),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;"&amp;($E$3-10)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C92" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;="&amp;($E$3-10),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;"&amp;($E$3-10)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D92" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;="&amp;($E$3-10),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;"&amp;($E$3-10)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E92" s="36">
@@ -12939,7 +12939,7 @@
         <v/>
       </c>
       <c r="G92" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;="&amp;($E$3-10),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;"&amp;($E$3-10)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H92" s="37">
@@ -12957,15 +12957,15 @@
         <v/>
       </c>
       <c r="B93" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;="&amp;($E$3-9),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;"&amp;($E$3-9)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C93" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;="&amp;($E$3-9),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;"&amp;($E$3-9)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D93" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;="&amp;($E$3-9),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;"&amp;($E$3-9)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E93" s="29">
@@ -12977,7 +12977,7 @@
         <v/>
       </c>
       <c r="G93" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;="&amp;($E$3-9),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;"&amp;($E$3-9)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H93" s="30">
@@ -12995,15 +12995,15 @@
         <v/>
       </c>
       <c r="B94" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;="&amp;($E$3-8),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;"&amp;($E$3-8)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C94" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;="&amp;($E$3-8),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;"&amp;($E$3-8)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D94" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;="&amp;($E$3-8),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;"&amp;($E$3-8)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E94" s="36">
@@ -13015,7 +13015,7 @@
         <v/>
       </c>
       <c r="G94" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;="&amp;($E$3-8),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;"&amp;($E$3-8)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H94" s="37">
@@ -13033,15 +13033,15 @@
         <v/>
       </c>
       <c r="B95" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;="&amp;($E$3-7),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;"&amp;($E$3-7)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C95" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;="&amp;($E$3-7),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;"&amp;($E$3-7)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D95" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;="&amp;($E$3-7),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;"&amp;($E$3-7)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E95" s="29">
@@ -13053,7 +13053,7 @@
         <v/>
       </c>
       <c r="G95" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;="&amp;($E$3-7),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;"&amp;($E$3-7)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H95" s="30">
@@ -13071,15 +13071,15 @@
         <v/>
       </c>
       <c r="B96" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;="&amp;($E$3-6),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;"&amp;($E$3-6)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C96" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;="&amp;($E$3-6),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;"&amp;($E$3-6)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D96" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;="&amp;($E$3-6),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;"&amp;($E$3-6)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E96" s="36">
@@ -13091,7 +13091,7 @@
         <v/>
       </c>
       <c r="G96" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;="&amp;($E$3-6),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;"&amp;($E$3-6)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H96" s="37">
@@ -13109,15 +13109,15 @@
         <v/>
       </c>
       <c r="B97" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;="&amp;($E$3-5),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;"&amp;($E$3-5)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C97" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;="&amp;($E$3-5),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;"&amp;($E$3-5)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D97" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;="&amp;($E$3-5),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;"&amp;($E$3-5)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E97" s="29">
@@ -13129,7 +13129,7 @@
         <v/>
       </c>
       <c r="G97" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;="&amp;($E$3-5),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;"&amp;($E$3-5)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H97" s="30">
@@ -13147,15 +13147,15 @@
         <v/>
       </c>
       <c r="B98" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;="&amp;($E$3-4),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;"&amp;($E$3-4)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C98" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;="&amp;($E$3-4),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;"&amp;($E$3-4)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D98" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;="&amp;($E$3-4),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;"&amp;($E$3-4)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E98" s="36">
@@ -13167,7 +13167,7 @@
         <v/>
       </c>
       <c r="G98" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;="&amp;($E$3-4),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;"&amp;($E$3-4)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H98" s="37">
@@ -13185,15 +13185,15 @@
         <v/>
       </c>
       <c r="B99" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;="&amp;($E$3-3),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;"&amp;($E$3-3)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C99" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;="&amp;($E$3-3),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;"&amp;($E$3-3)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D99" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;="&amp;($E$3-3),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;"&amp;($E$3-3)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E99" s="29">
@@ -13205,7 +13205,7 @@
         <v/>
       </c>
       <c r="G99" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;="&amp;($E$3-3),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;"&amp;($E$3-3)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H99" s="30">
@@ -13223,15 +13223,15 @@
         <v/>
       </c>
       <c r="B100" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;="&amp;($E$3-2),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;"&amp;($E$3-2)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C100" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;="&amp;($E$3-2),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;"&amp;($E$3-2)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D100" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;="&amp;($E$3-2),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;"&amp;($E$3-2)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E100" s="36">
@@ -13243,7 +13243,7 @@
         <v/>
       </c>
       <c r="G100" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;="&amp;($E$3-2),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;"&amp;($E$3-2)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H100" s="37">
@@ -13261,15 +13261,15 @@
         <v/>
       </c>
       <c r="B101" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;="&amp;($E$3-1),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;"&amp;($E$3-1)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C101" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;="&amp;($E$3-1),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;"&amp;($E$3-1)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D101" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;="&amp;($E$3-1),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;"&amp;($E$3-1)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E101" s="29">
@@ -13281,7 +13281,7 @@
         <v/>
       </c>
       <c r="G101" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;="&amp;($E$3-1),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;"&amp;($E$3-1)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H101" s="30">
@@ -13299,15 +13299,15 @@
         <v/>
       </c>
       <c r="B102" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;="&amp;($E$3-0),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;"&amp;($E$3-0)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C102" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;="&amp;($E$3-0),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;"&amp;($E$3-0)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D102" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;="&amp;($E$3-0),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;"&amp;($E$3-0)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E102" s="36">
@@ -13319,7 +13319,7 @@
         <v/>
       </c>
       <c r="G102" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;="&amp;($E$3-0),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;"&amp;($E$3-0)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H102" s="37">
@@ -13613,15 +13613,15 @@
         </is>
       </c>
       <c r="B7" s="10">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C7" s="11">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D7" s="11">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E7" s="12">
@@ -13633,7 +13633,7 @@
         <v/>
       </c>
       <c r="G7" s="11">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;="&amp;$K$7,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H7" s="13">
@@ -13660,15 +13660,15 @@
         </is>
       </c>
       <c r="B8" s="17">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;="&amp;$K$8,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;"&amp;$K$8+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C8" s="18">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;="&amp;$K$8,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;"&amp;$K$8+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D8" s="18">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;="&amp;$K$8,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;"&amp;$K$8+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E8" s="19">
@@ -13680,7 +13680,7 @@
         <v/>
       </c>
       <c r="G8" s="18">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;="&amp;$K$8,'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;"&amp;$K$8+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H8" s="20">
@@ -13801,15 +13801,15 @@
         <v/>
       </c>
       <c r="B13" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;="&amp;($E$3-89),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;"&amp;($E$3-89)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C13" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;="&amp;($E$3-89),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;"&amp;($E$3-89)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D13" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;="&amp;($E$3-89),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;"&amp;($E$3-89)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E13" s="29">
@@ -13821,7 +13821,7 @@
         <v/>
       </c>
       <c r="G13" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;="&amp;($E$3-89),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-89),'Данные'!$A:$A,"&lt;"&amp;($E$3-89)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H13" s="30">
@@ -13839,15 +13839,15 @@
         <v/>
       </c>
       <c r="B14" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;="&amp;($E$3-88),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;"&amp;($E$3-88)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C14" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;="&amp;($E$3-88),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;"&amp;($E$3-88)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D14" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;="&amp;($E$3-88),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;"&amp;($E$3-88)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E14" s="36">
@@ -13859,7 +13859,7 @@
         <v/>
       </c>
       <c r="G14" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;="&amp;($E$3-88),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-88),'Данные'!$A:$A,"&lt;"&amp;($E$3-88)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H14" s="37">
@@ -13877,15 +13877,15 @@
         <v/>
       </c>
       <c r="B15" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;="&amp;($E$3-87),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;"&amp;($E$3-87)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C15" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;="&amp;($E$3-87),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;"&amp;($E$3-87)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D15" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;="&amp;($E$3-87),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;"&amp;($E$3-87)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E15" s="29">
@@ -13897,7 +13897,7 @@
         <v/>
       </c>
       <c r="G15" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;="&amp;($E$3-87),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-87),'Данные'!$A:$A,"&lt;"&amp;($E$3-87)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H15" s="30">
@@ -13915,15 +13915,15 @@
         <v/>
       </c>
       <c r="B16" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;="&amp;($E$3-86),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;"&amp;($E$3-86)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C16" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;="&amp;($E$3-86),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;"&amp;($E$3-86)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D16" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;="&amp;($E$3-86),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;"&amp;($E$3-86)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E16" s="36">
@@ -13935,7 +13935,7 @@
         <v/>
       </c>
       <c r="G16" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;="&amp;($E$3-86),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-86),'Данные'!$A:$A,"&lt;"&amp;($E$3-86)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H16" s="37">
@@ -13953,15 +13953,15 @@
         <v/>
       </c>
       <c r="B17" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;="&amp;($E$3-85),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;"&amp;($E$3-85)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C17" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;="&amp;($E$3-85),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;"&amp;($E$3-85)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D17" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;="&amp;($E$3-85),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;"&amp;($E$3-85)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E17" s="29">
@@ -13973,7 +13973,7 @@
         <v/>
       </c>
       <c r="G17" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;="&amp;($E$3-85),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-85),'Данные'!$A:$A,"&lt;"&amp;($E$3-85)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H17" s="30">
@@ -13991,15 +13991,15 @@
         <v/>
       </c>
       <c r="B18" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;="&amp;($E$3-84),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;"&amp;($E$3-84)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C18" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;="&amp;($E$3-84),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;"&amp;($E$3-84)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D18" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;="&amp;($E$3-84),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;"&amp;($E$3-84)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E18" s="36">
@@ -14011,7 +14011,7 @@
         <v/>
       </c>
       <c r="G18" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;="&amp;($E$3-84),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-84),'Данные'!$A:$A,"&lt;"&amp;($E$3-84)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H18" s="37">
@@ -14029,15 +14029,15 @@
         <v/>
       </c>
       <c r="B19" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;="&amp;($E$3-83),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;"&amp;($E$3-83)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C19" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;="&amp;($E$3-83),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;"&amp;($E$3-83)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D19" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;="&amp;($E$3-83),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;"&amp;($E$3-83)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E19" s="29">
@@ -14049,7 +14049,7 @@
         <v/>
       </c>
       <c r="G19" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;="&amp;($E$3-83),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-83),'Данные'!$A:$A,"&lt;"&amp;($E$3-83)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H19" s="30">
@@ -14067,15 +14067,15 @@
         <v/>
       </c>
       <c r="B20" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;="&amp;($E$3-82),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;"&amp;($E$3-82)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C20" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;="&amp;($E$3-82),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;"&amp;($E$3-82)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D20" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;="&amp;($E$3-82),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;"&amp;($E$3-82)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E20" s="36">
@@ -14087,7 +14087,7 @@
         <v/>
       </c>
       <c r="G20" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;="&amp;($E$3-82),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-82),'Данные'!$A:$A,"&lt;"&amp;($E$3-82)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H20" s="37">
@@ -14105,15 +14105,15 @@
         <v/>
       </c>
       <c r="B21" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;="&amp;($E$3-81),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;"&amp;($E$3-81)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C21" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;="&amp;($E$3-81),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;"&amp;($E$3-81)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D21" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;="&amp;($E$3-81),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;"&amp;($E$3-81)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E21" s="29">
@@ -14125,7 +14125,7 @@
         <v/>
       </c>
       <c r="G21" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;="&amp;($E$3-81),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-81),'Данные'!$A:$A,"&lt;"&amp;($E$3-81)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H21" s="30">
@@ -14143,15 +14143,15 @@
         <v/>
       </c>
       <c r="B22" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;="&amp;($E$3-80),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;"&amp;($E$3-80)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C22" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;="&amp;($E$3-80),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;"&amp;($E$3-80)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D22" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;="&amp;($E$3-80),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;"&amp;($E$3-80)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E22" s="36">
@@ -14163,7 +14163,7 @@
         <v/>
       </c>
       <c r="G22" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;="&amp;($E$3-80),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-80),'Данные'!$A:$A,"&lt;"&amp;($E$3-80)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H22" s="37">
@@ -14181,15 +14181,15 @@
         <v/>
       </c>
       <c r="B23" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;="&amp;($E$3-79),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;"&amp;($E$3-79)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C23" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;="&amp;($E$3-79),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;"&amp;($E$3-79)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D23" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;="&amp;($E$3-79),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;"&amp;($E$3-79)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E23" s="29">
@@ -14201,7 +14201,7 @@
         <v/>
       </c>
       <c r="G23" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;="&amp;($E$3-79),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-79),'Данные'!$A:$A,"&lt;"&amp;($E$3-79)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H23" s="30">
@@ -14219,15 +14219,15 @@
         <v/>
       </c>
       <c r="B24" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;="&amp;($E$3-78),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;"&amp;($E$3-78)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C24" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;="&amp;($E$3-78),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;"&amp;($E$3-78)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D24" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;="&amp;($E$3-78),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;"&amp;($E$3-78)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E24" s="36">
@@ -14239,7 +14239,7 @@
         <v/>
       </c>
       <c r="G24" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;="&amp;($E$3-78),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-78),'Данные'!$A:$A,"&lt;"&amp;($E$3-78)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H24" s="37">
@@ -14257,15 +14257,15 @@
         <v/>
       </c>
       <c r="B25" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;="&amp;($E$3-77),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;"&amp;($E$3-77)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C25" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;="&amp;($E$3-77),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;"&amp;($E$3-77)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D25" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;="&amp;($E$3-77),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;"&amp;($E$3-77)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E25" s="29">
@@ -14277,7 +14277,7 @@
         <v/>
       </c>
       <c r="G25" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;="&amp;($E$3-77),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-77),'Данные'!$A:$A,"&lt;"&amp;($E$3-77)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H25" s="30">
@@ -14295,15 +14295,15 @@
         <v/>
       </c>
       <c r="B26" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;="&amp;($E$3-76),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;"&amp;($E$3-76)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C26" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;="&amp;($E$3-76),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;"&amp;($E$3-76)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D26" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;="&amp;($E$3-76),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;"&amp;($E$3-76)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E26" s="36">
@@ -14315,7 +14315,7 @@
         <v/>
       </c>
       <c r="G26" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;="&amp;($E$3-76),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-76),'Данные'!$A:$A,"&lt;"&amp;($E$3-76)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H26" s="37">
@@ -14333,15 +14333,15 @@
         <v/>
       </c>
       <c r="B27" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;="&amp;($E$3-75),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;"&amp;($E$3-75)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C27" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;="&amp;($E$3-75),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;"&amp;($E$3-75)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D27" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;="&amp;($E$3-75),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;"&amp;($E$3-75)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E27" s="29">
@@ -14353,7 +14353,7 @@
         <v/>
       </c>
       <c r="G27" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;="&amp;($E$3-75),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-75),'Данные'!$A:$A,"&lt;"&amp;($E$3-75)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H27" s="30">
@@ -14371,15 +14371,15 @@
         <v/>
       </c>
       <c r="B28" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;="&amp;($E$3-74),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;"&amp;($E$3-74)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C28" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;="&amp;($E$3-74),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;"&amp;($E$3-74)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D28" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;="&amp;($E$3-74),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;"&amp;($E$3-74)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E28" s="36">
@@ -14391,7 +14391,7 @@
         <v/>
       </c>
       <c r="G28" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;="&amp;($E$3-74),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-74),'Данные'!$A:$A,"&lt;"&amp;($E$3-74)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H28" s="37">
@@ -14409,15 +14409,15 @@
         <v/>
       </c>
       <c r="B29" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;="&amp;($E$3-73),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;"&amp;($E$3-73)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C29" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;="&amp;($E$3-73),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;"&amp;($E$3-73)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D29" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;="&amp;($E$3-73),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;"&amp;($E$3-73)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E29" s="29">
@@ -14429,7 +14429,7 @@
         <v/>
       </c>
       <c r="G29" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;="&amp;($E$3-73),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-73),'Данные'!$A:$A,"&lt;"&amp;($E$3-73)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H29" s="30">
@@ -14447,15 +14447,15 @@
         <v/>
       </c>
       <c r="B30" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;="&amp;($E$3-72),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;"&amp;($E$3-72)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C30" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;="&amp;($E$3-72),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;"&amp;($E$3-72)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D30" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;="&amp;($E$3-72),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;"&amp;($E$3-72)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E30" s="36">
@@ -14467,7 +14467,7 @@
         <v/>
       </c>
       <c r="G30" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;="&amp;($E$3-72),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-72),'Данные'!$A:$A,"&lt;"&amp;($E$3-72)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H30" s="37">
@@ -14485,15 +14485,15 @@
         <v/>
       </c>
       <c r="B31" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;="&amp;($E$3-71),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;"&amp;($E$3-71)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C31" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;="&amp;($E$3-71),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;"&amp;($E$3-71)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D31" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;="&amp;($E$3-71),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;"&amp;($E$3-71)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E31" s="29">
@@ -14505,7 +14505,7 @@
         <v/>
       </c>
       <c r="G31" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;="&amp;($E$3-71),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-71),'Данные'!$A:$A,"&lt;"&amp;($E$3-71)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H31" s="30">
@@ -14523,15 +14523,15 @@
         <v/>
       </c>
       <c r="B32" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;="&amp;($E$3-70),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;"&amp;($E$3-70)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C32" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;="&amp;($E$3-70),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;"&amp;($E$3-70)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D32" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;="&amp;($E$3-70),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;"&amp;($E$3-70)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E32" s="36">
@@ -14543,7 +14543,7 @@
         <v/>
       </c>
       <c r="G32" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;="&amp;($E$3-70),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-70),'Данные'!$A:$A,"&lt;"&amp;($E$3-70)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H32" s="37">
@@ -14561,15 +14561,15 @@
         <v/>
       </c>
       <c r="B33" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;="&amp;($E$3-69),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;"&amp;($E$3-69)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C33" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;="&amp;($E$3-69),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;"&amp;($E$3-69)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D33" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;="&amp;($E$3-69),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;"&amp;($E$3-69)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E33" s="29">
@@ -14581,7 +14581,7 @@
         <v/>
       </c>
       <c r="G33" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;="&amp;($E$3-69),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-69),'Данные'!$A:$A,"&lt;"&amp;($E$3-69)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H33" s="30">
@@ -14599,15 +14599,15 @@
         <v/>
       </c>
       <c r="B34" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;="&amp;($E$3-68),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;"&amp;($E$3-68)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C34" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;="&amp;($E$3-68),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;"&amp;($E$3-68)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D34" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;="&amp;($E$3-68),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;"&amp;($E$3-68)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E34" s="36">
@@ -14619,7 +14619,7 @@
         <v/>
       </c>
       <c r="G34" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;="&amp;($E$3-68),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-68),'Данные'!$A:$A,"&lt;"&amp;($E$3-68)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H34" s="37">
@@ -14637,15 +14637,15 @@
         <v/>
       </c>
       <c r="B35" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;="&amp;($E$3-67),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;"&amp;($E$3-67)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C35" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;="&amp;($E$3-67),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;"&amp;($E$3-67)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D35" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;="&amp;($E$3-67),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;"&amp;($E$3-67)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E35" s="29">
@@ -14657,7 +14657,7 @@
         <v/>
       </c>
       <c r="G35" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;="&amp;($E$3-67),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-67),'Данные'!$A:$A,"&lt;"&amp;($E$3-67)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H35" s="30">
@@ -14675,15 +14675,15 @@
         <v/>
       </c>
       <c r="B36" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;="&amp;($E$3-66),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;"&amp;($E$3-66)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C36" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;="&amp;($E$3-66),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;"&amp;($E$3-66)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D36" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;="&amp;($E$3-66),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;"&amp;($E$3-66)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E36" s="36">
@@ -14695,7 +14695,7 @@
         <v/>
       </c>
       <c r="G36" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;="&amp;($E$3-66),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-66),'Данные'!$A:$A,"&lt;"&amp;($E$3-66)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H36" s="37">
@@ -14713,15 +14713,15 @@
         <v/>
       </c>
       <c r="B37" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;="&amp;($E$3-65),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;"&amp;($E$3-65)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C37" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;="&amp;($E$3-65),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;"&amp;($E$3-65)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D37" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;="&amp;($E$3-65),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;"&amp;($E$3-65)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E37" s="29">
@@ -14733,7 +14733,7 @@
         <v/>
       </c>
       <c r="G37" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;="&amp;($E$3-65),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-65),'Данные'!$A:$A,"&lt;"&amp;($E$3-65)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H37" s="30">
@@ -14751,15 +14751,15 @@
         <v/>
       </c>
       <c r="B38" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;="&amp;($E$3-64),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;"&amp;($E$3-64)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C38" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;="&amp;($E$3-64),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;"&amp;($E$3-64)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D38" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;="&amp;($E$3-64),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;"&amp;($E$3-64)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E38" s="36">
@@ -14771,7 +14771,7 @@
         <v/>
       </c>
       <c r="G38" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;="&amp;($E$3-64),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-64),'Данные'!$A:$A,"&lt;"&amp;($E$3-64)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H38" s="37">
@@ -14789,15 +14789,15 @@
         <v/>
       </c>
       <c r="B39" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;="&amp;($E$3-63),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;"&amp;($E$3-63)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C39" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;="&amp;($E$3-63),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;"&amp;($E$3-63)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D39" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;="&amp;($E$3-63),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;"&amp;($E$3-63)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E39" s="29">
@@ -14809,7 +14809,7 @@
         <v/>
       </c>
       <c r="G39" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;="&amp;($E$3-63),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-63),'Данные'!$A:$A,"&lt;"&amp;($E$3-63)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H39" s="30">
@@ -14827,15 +14827,15 @@
         <v/>
       </c>
       <c r="B40" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;="&amp;($E$3-62),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;"&amp;($E$3-62)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C40" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;="&amp;($E$3-62),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;"&amp;($E$3-62)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D40" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;="&amp;($E$3-62),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;"&amp;($E$3-62)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E40" s="36">
@@ -14847,7 +14847,7 @@
         <v/>
       </c>
       <c r="G40" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;="&amp;($E$3-62),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-62),'Данные'!$A:$A,"&lt;"&amp;($E$3-62)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H40" s="37">
@@ -14865,15 +14865,15 @@
         <v/>
       </c>
       <c r="B41" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;="&amp;($E$3-61),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;"&amp;($E$3-61)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C41" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;="&amp;($E$3-61),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;"&amp;($E$3-61)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D41" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;="&amp;($E$3-61),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;"&amp;($E$3-61)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E41" s="29">
@@ -14885,7 +14885,7 @@
         <v/>
       </c>
       <c r="G41" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;="&amp;($E$3-61),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-61),'Данные'!$A:$A,"&lt;"&amp;($E$3-61)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H41" s="30">
@@ -14903,15 +14903,15 @@
         <v/>
       </c>
       <c r="B42" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;="&amp;($E$3-60),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;"&amp;($E$3-60)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C42" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;="&amp;($E$3-60),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;"&amp;($E$3-60)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D42" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;="&amp;($E$3-60),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;"&amp;($E$3-60)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E42" s="36">
@@ -14923,7 +14923,7 @@
         <v/>
       </c>
       <c r="G42" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;="&amp;($E$3-60),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-60),'Данные'!$A:$A,"&lt;"&amp;($E$3-60)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H42" s="37">
@@ -14941,15 +14941,15 @@
         <v/>
       </c>
       <c r="B43" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;="&amp;($E$3-59),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;"&amp;($E$3-59)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C43" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;="&amp;($E$3-59),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;"&amp;($E$3-59)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D43" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;="&amp;($E$3-59),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;"&amp;($E$3-59)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E43" s="29">
@@ -14961,7 +14961,7 @@
         <v/>
       </c>
       <c r="G43" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;="&amp;($E$3-59),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-59),'Данные'!$A:$A,"&lt;"&amp;($E$3-59)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H43" s="30">
@@ -14979,15 +14979,15 @@
         <v/>
       </c>
       <c r="B44" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;="&amp;($E$3-58),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;"&amp;($E$3-58)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C44" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;="&amp;($E$3-58),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;"&amp;($E$3-58)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D44" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;="&amp;($E$3-58),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;"&amp;($E$3-58)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E44" s="36">
@@ -14999,7 +14999,7 @@
         <v/>
       </c>
       <c r="G44" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;="&amp;($E$3-58),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-58),'Данные'!$A:$A,"&lt;"&amp;($E$3-58)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H44" s="37">
@@ -15017,15 +15017,15 @@
         <v/>
       </c>
       <c r="B45" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;="&amp;($E$3-57),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;"&amp;($E$3-57)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C45" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;="&amp;($E$3-57),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;"&amp;($E$3-57)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D45" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;="&amp;($E$3-57),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;"&amp;($E$3-57)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E45" s="29">
@@ -15037,7 +15037,7 @@
         <v/>
       </c>
       <c r="G45" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;="&amp;($E$3-57),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-57),'Данные'!$A:$A,"&lt;"&amp;($E$3-57)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H45" s="30">
@@ -15055,15 +15055,15 @@
         <v/>
       </c>
       <c r="B46" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;="&amp;($E$3-56),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;"&amp;($E$3-56)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C46" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;="&amp;($E$3-56),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;"&amp;($E$3-56)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D46" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;="&amp;($E$3-56),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;"&amp;($E$3-56)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E46" s="36">
@@ -15075,7 +15075,7 @@
         <v/>
       </c>
       <c r="G46" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;="&amp;($E$3-56),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-56),'Данные'!$A:$A,"&lt;"&amp;($E$3-56)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H46" s="37">
@@ -15093,15 +15093,15 @@
         <v/>
       </c>
       <c r="B47" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;="&amp;($E$3-55),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;"&amp;($E$3-55)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C47" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;="&amp;($E$3-55),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;"&amp;($E$3-55)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D47" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;="&amp;($E$3-55),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;"&amp;($E$3-55)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E47" s="29">
@@ -15113,7 +15113,7 @@
         <v/>
       </c>
       <c r="G47" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;="&amp;($E$3-55),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-55),'Данные'!$A:$A,"&lt;"&amp;($E$3-55)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H47" s="30">
@@ -15131,15 +15131,15 @@
         <v/>
       </c>
       <c r="B48" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;="&amp;($E$3-54),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;"&amp;($E$3-54)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C48" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;="&amp;($E$3-54),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;"&amp;($E$3-54)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D48" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;="&amp;($E$3-54),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;"&amp;($E$3-54)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E48" s="36">
@@ -15151,7 +15151,7 @@
         <v/>
       </c>
       <c r="G48" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;="&amp;($E$3-54),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-54),'Данные'!$A:$A,"&lt;"&amp;($E$3-54)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H48" s="37">
@@ -15169,15 +15169,15 @@
         <v/>
       </c>
       <c r="B49" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;="&amp;($E$3-53),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;"&amp;($E$3-53)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C49" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;="&amp;($E$3-53),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;"&amp;($E$3-53)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D49" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;="&amp;($E$3-53),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;"&amp;($E$3-53)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E49" s="29">
@@ -15189,7 +15189,7 @@
         <v/>
       </c>
       <c r="G49" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;="&amp;($E$3-53),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-53),'Данные'!$A:$A,"&lt;"&amp;($E$3-53)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H49" s="30">
@@ -15207,15 +15207,15 @@
         <v/>
       </c>
       <c r="B50" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;="&amp;($E$3-52),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;"&amp;($E$3-52)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C50" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;="&amp;($E$3-52),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;"&amp;($E$3-52)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D50" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;="&amp;($E$3-52),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;"&amp;($E$3-52)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E50" s="36">
@@ -15227,7 +15227,7 @@
         <v/>
       </c>
       <c r="G50" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;="&amp;($E$3-52),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-52),'Данные'!$A:$A,"&lt;"&amp;($E$3-52)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H50" s="37">
@@ -15245,15 +15245,15 @@
         <v/>
       </c>
       <c r="B51" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;="&amp;($E$3-51),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;"&amp;($E$3-51)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C51" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;="&amp;($E$3-51),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;"&amp;($E$3-51)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D51" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;="&amp;($E$3-51),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;"&amp;($E$3-51)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E51" s="29">
@@ -15265,7 +15265,7 @@
         <v/>
       </c>
       <c r="G51" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;="&amp;($E$3-51),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-51),'Данные'!$A:$A,"&lt;"&amp;($E$3-51)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H51" s="30">
@@ -15283,15 +15283,15 @@
         <v/>
       </c>
       <c r="B52" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;="&amp;($E$3-50),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;"&amp;($E$3-50)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C52" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;="&amp;($E$3-50),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;"&amp;($E$3-50)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D52" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;="&amp;($E$3-50),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;"&amp;($E$3-50)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E52" s="36">
@@ -15303,7 +15303,7 @@
         <v/>
       </c>
       <c r="G52" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;="&amp;($E$3-50),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-50),'Данные'!$A:$A,"&lt;"&amp;($E$3-50)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H52" s="37">
@@ -15321,15 +15321,15 @@
         <v/>
       </c>
       <c r="B53" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;="&amp;($E$3-49),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;"&amp;($E$3-49)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C53" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;="&amp;($E$3-49),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;"&amp;($E$3-49)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D53" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;="&amp;($E$3-49),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;"&amp;($E$3-49)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E53" s="29">
@@ -15341,7 +15341,7 @@
         <v/>
       </c>
       <c r="G53" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;="&amp;($E$3-49),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-49),'Данные'!$A:$A,"&lt;"&amp;($E$3-49)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H53" s="30">
@@ -15359,15 +15359,15 @@
         <v/>
       </c>
       <c r="B54" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;="&amp;($E$3-48),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;"&amp;($E$3-48)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C54" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;="&amp;($E$3-48),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;"&amp;($E$3-48)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D54" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;="&amp;($E$3-48),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;"&amp;($E$3-48)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E54" s="36">
@@ -15379,7 +15379,7 @@
         <v/>
       </c>
       <c r="G54" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;="&amp;($E$3-48),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-48),'Данные'!$A:$A,"&lt;"&amp;($E$3-48)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H54" s="37">
@@ -15397,15 +15397,15 @@
         <v/>
       </c>
       <c r="B55" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;="&amp;($E$3-47),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;"&amp;($E$3-47)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C55" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;="&amp;($E$3-47),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;"&amp;($E$3-47)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D55" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;="&amp;($E$3-47),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;"&amp;($E$3-47)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E55" s="29">
@@ -15417,7 +15417,7 @@
         <v/>
       </c>
       <c r="G55" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;="&amp;($E$3-47),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-47),'Данные'!$A:$A,"&lt;"&amp;($E$3-47)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H55" s="30">
@@ -15435,15 +15435,15 @@
         <v/>
       </c>
       <c r="B56" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;="&amp;($E$3-46),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;"&amp;($E$3-46)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C56" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;="&amp;($E$3-46),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;"&amp;($E$3-46)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D56" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;="&amp;($E$3-46),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;"&amp;($E$3-46)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E56" s="36">
@@ -15455,7 +15455,7 @@
         <v/>
       </c>
       <c r="G56" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;="&amp;($E$3-46),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-46),'Данные'!$A:$A,"&lt;"&amp;($E$3-46)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H56" s="37">
@@ -15473,15 +15473,15 @@
         <v/>
       </c>
       <c r="B57" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;="&amp;($E$3-45),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;"&amp;($E$3-45)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C57" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;="&amp;($E$3-45),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;"&amp;($E$3-45)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D57" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;="&amp;($E$3-45),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;"&amp;($E$3-45)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E57" s="29">
@@ -15493,7 +15493,7 @@
         <v/>
       </c>
       <c r="G57" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;="&amp;($E$3-45),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-45),'Данные'!$A:$A,"&lt;"&amp;($E$3-45)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H57" s="30">
@@ -15511,15 +15511,15 @@
         <v/>
       </c>
       <c r="B58" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;="&amp;($E$3-44),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;"&amp;($E$3-44)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C58" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;="&amp;($E$3-44),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;"&amp;($E$3-44)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D58" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;="&amp;($E$3-44),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;"&amp;($E$3-44)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E58" s="36">
@@ -15531,7 +15531,7 @@
         <v/>
       </c>
       <c r="G58" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;="&amp;($E$3-44),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-44),'Данные'!$A:$A,"&lt;"&amp;($E$3-44)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H58" s="37">
@@ -15549,15 +15549,15 @@
         <v/>
       </c>
       <c r="B59" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;="&amp;($E$3-43),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;"&amp;($E$3-43)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C59" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;="&amp;($E$3-43),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;"&amp;($E$3-43)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D59" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;="&amp;($E$3-43),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;"&amp;($E$3-43)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E59" s="29">
@@ -15569,7 +15569,7 @@
         <v/>
       </c>
       <c r="G59" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;="&amp;($E$3-43),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-43),'Данные'!$A:$A,"&lt;"&amp;($E$3-43)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H59" s="30">
@@ -15587,15 +15587,15 @@
         <v/>
       </c>
       <c r="B60" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;="&amp;($E$3-42),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;"&amp;($E$3-42)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C60" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;="&amp;($E$3-42),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;"&amp;($E$3-42)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D60" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;="&amp;($E$3-42),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;"&amp;($E$3-42)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E60" s="36">
@@ -15607,7 +15607,7 @@
         <v/>
       </c>
       <c r="G60" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;="&amp;($E$3-42),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-42),'Данные'!$A:$A,"&lt;"&amp;($E$3-42)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H60" s="37">
@@ -15625,15 +15625,15 @@
         <v/>
       </c>
       <c r="B61" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;="&amp;($E$3-41),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;"&amp;($E$3-41)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C61" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;="&amp;($E$3-41),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;"&amp;($E$3-41)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D61" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;="&amp;($E$3-41),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;"&amp;($E$3-41)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E61" s="29">
@@ -15645,7 +15645,7 @@
         <v/>
       </c>
       <c r="G61" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;="&amp;($E$3-41),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-41),'Данные'!$A:$A,"&lt;"&amp;($E$3-41)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H61" s="30">
@@ -15663,15 +15663,15 @@
         <v/>
       </c>
       <c r="B62" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;="&amp;($E$3-40),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;"&amp;($E$3-40)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C62" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;="&amp;($E$3-40),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;"&amp;($E$3-40)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D62" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;="&amp;($E$3-40),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;"&amp;($E$3-40)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E62" s="36">
@@ -15683,7 +15683,7 @@
         <v/>
       </c>
       <c r="G62" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;="&amp;($E$3-40),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-40),'Данные'!$A:$A,"&lt;"&amp;($E$3-40)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H62" s="37">
@@ -15701,15 +15701,15 @@
         <v/>
       </c>
       <c r="B63" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;="&amp;($E$3-39),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;"&amp;($E$3-39)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C63" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;="&amp;($E$3-39),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;"&amp;($E$3-39)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D63" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;="&amp;($E$3-39),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;"&amp;($E$3-39)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E63" s="29">
@@ -15721,7 +15721,7 @@
         <v/>
       </c>
       <c r="G63" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;="&amp;($E$3-39),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-39),'Данные'!$A:$A,"&lt;"&amp;($E$3-39)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H63" s="30">
@@ -15739,15 +15739,15 @@
         <v/>
       </c>
       <c r="B64" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;="&amp;($E$3-38),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;"&amp;($E$3-38)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C64" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;="&amp;($E$3-38),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;"&amp;($E$3-38)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D64" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;="&amp;($E$3-38),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;"&amp;($E$3-38)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E64" s="36">
@@ -15759,7 +15759,7 @@
         <v/>
       </c>
       <c r="G64" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;="&amp;($E$3-38),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-38),'Данные'!$A:$A,"&lt;"&amp;($E$3-38)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H64" s="37">
@@ -15777,15 +15777,15 @@
         <v/>
       </c>
       <c r="B65" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;="&amp;($E$3-37),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;"&amp;($E$3-37)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C65" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;="&amp;($E$3-37),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;"&amp;($E$3-37)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D65" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;="&amp;($E$3-37),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;"&amp;($E$3-37)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E65" s="29">
@@ -15797,7 +15797,7 @@
         <v/>
       </c>
       <c r="G65" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;="&amp;($E$3-37),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-37),'Данные'!$A:$A,"&lt;"&amp;($E$3-37)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H65" s="30">
@@ -15815,15 +15815,15 @@
         <v/>
       </c>
       <c r="B66" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;="&amp;($E$3-36),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;"&amp;($E$3-36)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C66" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;="&amp;($E$3-36),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;"&amp;($E$3-36)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D66" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;="&amp;($E$3-36),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;"&amp;($E$3-36)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E66" s="36">
@@ -15835,7 +15835,7 @@
         <v/>
       </c>
       <c r="G66" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;="&amp;($E$3-36),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-36),'Данные'!$A:$A,"&lt;"&amp;($E$3-36)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H66" s="37">
@@ -15853,15 +15853,15 @@
         <v/>
       </c>
       <c r="B67" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;="&amp;($E$3-35),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;"&amp;($E$3-35)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C67" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;="&amp;($E$3-35),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;"&amp;($E$3-35)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D67" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;="&amp;($E$3-35),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;"&amp;($E$3-35)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E67" s="29">
@@ -15873,7 +15873,7 @@
         <v/>
       </c>
       <c r="G67" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;="&amp;($E$3-35),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-35),'Данные'!$A:$A,"&lt;"&amp;($E$3-35)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H67" s="30">
@@ -15891,15 +15891,15 @@
         <v/>
       </c>
       <c r="B68" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;="&amp;($E$3-34),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;"&amp;($E$3-34)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C68" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;="&amp;($E$3-34),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;"&amp;($E$3-34)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D68" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;="&amp;($E$3-34),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;"&amp;($E$3-34)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E68" s="36">
@@ -15911,7 +15911,7 @@
         <v/>
       </c>
       <c r="G68" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;="&amp;($E$3-34),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-34),'Данные'!$A:$A,"&lt;"&amp;($E$3-34)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H68" s="37">
@@ -15929,15 +15929,15 @@
         <v/>
       </c>
       <c r="B69" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;="&amp;($E$3-33),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;"&amp;($E$3-33)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C69" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;="&amp;($E$3-33),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;"&amp;($E$3-33)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D69" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;="&amp;($E$3-33),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;"&amp;($E$3-33)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E69" s="29">
@@ -15949,7 +15949,7 @@
         <v/>
       </c>
       <c r="G69" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;="&amp;($E$3-33),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-33),'Данные'!$A:$A,"&lt;"&amp;($E$3-33)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H69" s="30">
@@ -15967,15 +15967,15 @@
         <v/>
       </c>
       <c r="B70" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;="&amp;($E$3-32),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;"&amp;($E$3-32)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C70" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;="&amp;($E$3-32),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;"&amp;($E$3-32)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D70" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;="&amp;($E$3-32),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;"&amp;($E$3-32)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E70" s="36">
@@ -15987,7 +15987,7 @@
         <v/>
       </c>
       <c r="G70" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;="&amp;($E$3-32),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-32),'Данные'!$A:$A,"&lt;"&amp;($E$3-32)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H70" s="37">
@@ -16005,15 +16005,15 @@
         <v/>
       </c>
       <c r="B71" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;="&amp;($E$3-31),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;"&amp;($E$3-31)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C71" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;="&amp;($E$3-31),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;"&amp;($E$3-31)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D71" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;="&amp;($E$3-31),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;"&amp;($E$3-31)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E71" s="29">
@@ -16025,7 +16025,7 @@
         <v/>
       </c>
       <c r="G71" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;="&amp;($E$3-31),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-31),'Данные'!$A:$A,"&lt;"&amp;($E$3-31)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H71" s="30">
@@ -16043,15 +16043,15 @@
         <v/>
       </c>
       <c r="B72" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;="&amp;($E$3-30),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;"&amp;($E$3-30)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C72" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;="&amp;($E$3-30),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;"&amp;($E$3-30)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D72" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;="&amp;($E$3-30),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;"&amp;($E$3-30)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E72" s="36">
@@ -16063,7 +16063,7 @@
         <v/>
       </c>
       <c r="G72" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;="&amp;($E$3-30),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-30),'Данные'!$A:$A,"&lt;"&amp;($E$3-30)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H72" s="37">
@@ -16081,15 +16081,15 @@
         <v/>
       </c>
       <c r="B73" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;="&amp;($E$3-29),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;"&amp;($E$3-29)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C73" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;="&amp;($E$3-29),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;"&amp;($E$3-29)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D73" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;="&amp;($E$3-29),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;"&amp;($E$3-29)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E73" s="29">
@@ -16101,7 +16101,7 @@
         <v/>
       </c>
       <c r="G73" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;="&amp;($E$3-29),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-29),'Данные'!$A:$A,"&lt;"&amp;($E$3-29)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H73" s="30">
@@ -16119,15 +16119,15 @@
         <v/>
       </c>
       <c r="B74" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;="&amp;($E$3-28),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;"&amp;($E$3-28)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C74" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;="&amp;($E$3-28),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;"&amp;($E$3-28)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D74" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;="&amp;($E$3-28),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;"&amp;($E$3-28)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E74" s="36">
@@ -16139,7 +16139,7 @@
         <v/>
       </c>
       <c r="G74" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;="&amp;($E$3-28),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-28),'Данные'!$A:$A,"&lt;"&amp;($E$3-28)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H74" s="37">
@@ -16157,15 +16157,15 @@
         <v/>
       </c>
       <c r="B75" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;="&amp;($E$3-27),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;"&amp;($E$3-27)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C75" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;="&amp;($E$3-27),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;"&amp;($E$3-27)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D75" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;="&amp;($E$3-27),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;"&amp;($E$3-27)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E75" s="29">
@@ -16177,7 +16177,7 @@
         <v/>
       </c>
       <c r="G75" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;="&amp;($E$3-27),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-27),'Данные'!$A:$A,"&lt;"&amp;($E$3-27)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H75" s="30">
@@ -16195,15 +16195,15 @@
         <v/>
       </c>
       <c r="B76" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;="&amp;($E$3-26),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;"&amp;($E$3-26)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C76" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;="&amp;($E$3-26),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;"&amp;($E$3-26)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D76" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;="&amp;($E$3-26),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;"&amp;($E$3-26)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E76" s="36">
@@ -16215,7 +16215,7 @@
         <v/>
       </c>
       <c r="G76" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;="&amp;($E$3-26),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-26),'Данные'!$A:$A,"&lt;"&amp;($E$3-26)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H76" s="37">
@@ -16233,15 +16233,15 @@
         <v/>
       </c>
       <c r="B77" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;="&amp;($E$3-25),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;"&amp;($E$3-25)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C77" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;="&amp;($E$3-25),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;"&amp;($E$3-25)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D77" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;="&amp;($E$3-25),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;"&amp;($E$3-25)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E77" s="29">
@@ -16253,7 +16253,7 @@
         <v/>
       </c>
       <c r="G77" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;="&amp;($E$3-25),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-25),'Данные'!$A:$A,"&lt;"&amp;($E$3-25)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H77" s="30">
@@ -16271,15 +16271,15 @@
         <v/>
       </c>
       <c r="B78" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;="&amp;($E$3-24),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;"&amp;($E$3-24)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C78" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;="&amp;($E$3-24),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;"&amp;($E$3-24)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D78" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;="&amp;($E$3-24),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;"&amp;($E$3-24)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E78" s="36">
@@ -16291,7 +16291,7 @@
         <v/>
       </c>
       <c r="G78" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;="&amp;($E$3-24),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-24),'Данные'!$A:$A,"&lt;"&amp;($E$3-24)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H78" s="37">
@@ -16309,15 +16309,15 @@
         <v/>
       </c>
       <c r="B79" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;="&amp;($E$3-23),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;"&amp;($E$3-23)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C79" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;="&amp;($E$3-23),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;"&amp;($E$3-23)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D79" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;="&amp;($E$3-23),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;"&amp;($E$3-23)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E79" s="29">
@@ -16329,7 +16329,7 @@
         <v/>
       </c>
       <c r="G79" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;="&amp;($E$3-23),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-23),'Данные'!$A:$A,"&lt;"&amp;($E$3-23)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H79" s="30">
@@ -16347,15 +16347,15 @@
         <v/>
       </c>
       <c r="B80" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;="&amp;($E$3-22),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;"&amp;($E$3-22)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C80" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;="&amp;($E$3-22),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;"&amp;($E$3-22)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D80" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;="&amp;($E$3-22),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;"&amp;($E$3-22)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E80" s="36">
@@ -16367,7 +16367,7 @@
         <v/>
       </c>
       <c r="G80" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;="&amp;($E$3-22),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-22),'Данные'!$A:$A,"&lt;"&amp;($E$3-22)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H80" s="37">
@@ -16385,15 +16385,15 @@
         <v/>
       </c>
       <c r="B81" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;="&amp;($E$3-21),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;"&amp;($E$3-21)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C81" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;="&amp;($E$3-21),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;"&amp;($E$3-21)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D81" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;="&amp;($E$3-21),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;"&amp;($E$3-21)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E81" s="29">
@@ -16405,7 +16405,7 @@
         <v/>
       </c>
       <c r="G81" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;="&amp;($E$3-21),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-21),'Данные'!$A:$A,"&lt;"&amp;($E$3-21)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H81" s="30">
@@ -16423,15 +16423,15 @@
         <v/>
       </c>
       <c r="B82" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;="&amp;($E$3-20),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;"&amp;($E$3-20)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C82" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;="&amp;($E$3-20),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;"&amp;($E$3-20)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D82" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;="&amp;($E$3-20),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;"&amp;($E$3-20)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E82" s="36">
@@ -16443,7 +16443,7 @@
         <v/>
       </c>
       <c r="G82" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;="&amp;($E$3-20),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-20),'Данные'!$A:$A,"&lt;"&amp;($E$3-20)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H82" s="37">
@@ -16461,15 +16461,15 @@
         <v/>
       </c>
       <c r="B83" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;="&amp;($E$3-19),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;"&amp;($E$3-19)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C83" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;="&amp;($E$3-19),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;"&amp;($E$3-19)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D83" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;="&amp;($E$3-19),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;"&amp;($E$3-19)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E83" s="29">
@@ -16481,7 +16481,7 @@
         <v/>
       </c>
       <c r="G83" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;="&amp;($E$3-19),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-19),'Данные'!$A:$A,"&lt;"&amp;($E$3-19)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H83" s="30">
@@ -16499,15 +16499,15 @@
         <v/>
       </c>
       <c r="B84" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;="&amp;($E$3-18),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;"&amp;($E$3-18)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C84" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;="&amp;($E$3-18),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;"&amp;($E$3-18)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D84" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;="&amp;($E$3-18),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;"&amp;($E$3-18)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E84" s="36">
@@ -16519,7 +16519,7 @@
         <v/>
       </c>
       <c r="G84" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;="&amp;($E$3-18),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-18),'Данные'!$A:$A,"&lt;"&amp;($E$3-18)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H84" s="37">
@@ -16537,15 +16537,15 @@
         <v/>
       </c>
       <c r="B85" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;="&amp;($E$3-17),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;"&amp;($E$3-17)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C85" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;="&amp;($E$3-17),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;"&amp;($E$3-17)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D85" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;="&amp;($E$3-17),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;"&amp;($E$3-17)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E85" s="29">
@@ -16557,7 +16557,7 @@
         <v/>
       </c>
       <c r="G85" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;="&amp;($E$3-17),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-17),'Данные'!$A:$A,"&lt;"&amp;($E$3-17)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H85" s="30">
@@ -16575,15 +16575,15 @@
         <v/>
       </c>
       <c r="B86" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;="&amp;($E$3-16),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;"&amp;($E$3-16)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C86" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;="&amp;($E$3-16),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;"&amp;($E$3-16)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D86" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;="&amp;($E$3-16),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;"&amp;($E$3-16)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E86" s="36">
@@ -16595,7 +16595,7 @@
         <v/>
       </c>
       <c r="G86" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;="&amp;($E$3-16),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-16),'Данные'!$A:$A,"&lt;"&amp;($E$3-16)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H86" s="37">
@@ -16613,15 +16613,15 @@
         <v/>
       </c>
       <c r="B87" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;="&amp;($E$3-15),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;"&amp;($E$3-15)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C87" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;="&amp;($E$3-15),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;"&amp;($E$3-15)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D87" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;="&amp;($E$3-15),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;"&amp;($E$3-15)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E87" s="29">
@@ -16633,7 +16633,7 @@
         <v/>
       </c>
       <c r="G87" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;="&amp;($E$3-15),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-15),'Данные'!$A:$A,"&lt;"&amp;($E$3-15)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H87" s="30">
@@ -16651,15 +16651,15 @@
         <v/>
       </c>
       <c r="B88" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;="&amp;($E$3-14),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;"&amp;($E$3-14)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C88" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;="&amp;($E$3-14),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;"&amp;($E$3-14)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D88" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;="&amp;($E$3-14),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;"&amp;($E$3-14)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E88" s="36">
@@ -16671,7 +16671,7 @@
         <v/>
       </c>
       <c r="G88" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;="&amp;($E$3-14),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-14),'Данные'!$A:$A,"&lt;"&amp;($E$3-14)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H88" s="37">
@@ -16689,15 +16689,15 @@
         <v/>
       </c>
       <c r="B89" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;="&amp;($E$3-13),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;"&amp;($E$3-13)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C89" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;="&amp;($E$3-13),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;"&amp;($E$3-13)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D89" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;="&amp;($E$3-13),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;"&amp;($E$3-13)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E89" s="29">
@@ -16709,7 +16709,7 @@
         <v/>
       </c>
       <c r="G89" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;="&amp;($E$3-13),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-13),'Данные'!$A:$A,"&lt;"&amp;($E$3-13)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H89" s="30">
@@ -16727,15 +16727,15 @@
         <v/>
       </c>
       <c r="B90" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;="&amp;($E$3-12),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;"&amp;($E$3-12)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C90" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;="&amp;($E$3-12),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;"&amp;($E$3-12)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D90" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;="&amp;($E$3-12),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;"&amp;($E$3-12)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E90" s="36">
@@ -16747,7 +16747,7 @@
         <v/>
       </c>
       <c r="G90" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;="&amp;($E$3-12),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-12),'Данные'!$A:$A,"&lt;"&amp;($E$3-12)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H90" s="37">
@@ -16765,15 +16765,15 @@
         <v/>
       </c>
       <c r="B91" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;="&amp;($E$3-11),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;"&amp;($E$3-11)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C91" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;="&amp;($E$3-11),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;"&amp;($E$3-11)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D91" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;="&amp;($E$3-11),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;"&amp;($E$3-11)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E91" s="29">
@@ -16785,7 +16785,7 @@
         <v/>
       </c>
       <c r="G91" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;="&amp;($E$3-11),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-11),'Данные'!$A:$A,"&lt;"&amp;($E$3-11)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H91" s="30">
@@ -16803,15 +16803,15 @@
         <v/>
       </c>
       <c r="B92" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;="&amp;($E$3-10),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;"&amp;($E$3-10)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C92" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;="&amp;($E$3-10),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;"&amp;($E$3-10)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D92" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;="&amp;($E$3-10),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;"&amp;($E$3-10)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E92" s="36">
@@ -16823,7 +16823,7 @@
         <v/>
       </c>
       <c r="G92" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;="&amp;($E$3-10),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-10),'Данные'!$A:$A,"&lt;"&amp;($E$3-10)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H92" s="37">
@@ -16841,15 +16841,15 @@
         <v/>
       </c>
       <c r="B93" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;="&amp;($E$3-9),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;"&amp;($E$3-9)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C93" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;="&amp;($E$3-9),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;"&amp;($E$3-9)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D93" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;="&amp;($E$3-9),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;"&amp;($E$3-9)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E93" s="29">
@@ -16861,7 +16861,7 @@
         <v/>
       </c>
       <c r="G93" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;="&amp;($E$3-9),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-9),'Данные'!$A:$A,"&lt;"&amp;($E$3-9)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H93" s="30">
@@ -16879,15 +16879,15 @@
         <v/>
       </c>
       <c r="B94" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;="&amp;($E$3-8),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;"&amp;($E$3-8)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C94" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;="&amp;($E$3-8),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;"&amp;($E$3-8)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D94" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;="&amp;($E$3-8),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;"&amp;($E$3-8)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E94" s="36">
@@ -16899,7 +16899,7 @@
         <v/>
       </c>
       <c r="G94" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;="&amp;($E$3-8),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-8),'Данные'!$A:$A,"&lt;"&amp;($E$3-8)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H94" s="37">
@@ -16917,15 +16917,15 @@
         <v/>
       </c>
       <c r="B95" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;="&amp;($E$3-7),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;"&amp;($E$3-7)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C95" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;="&amp;($E$3-7),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;"&amp;($E$3-7)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D95" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;="&amp;($E$3-7),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;"&amp;($E$3-7)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E95" s="29">
@@ -16937,7 +16937,7 @@
         <v/>
       </c>
       <c r="G95" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;="&amp;($E$3-7),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-7),'Данные'!$A:$A,"&lt;"&amp;($E$3-7)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H95" s="30">
@@ -16955,15 +16955,15 @@
         <v/>
       </c>
       <c r="B96" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;="&amp;($E$3-6),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;"&amp;($E$3-6)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C96" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;="&amp;($E$3-6),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;"&amp;($E$3-6)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D96" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;="&amp;($E$3-6),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;"&amp;($E$3-6)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E96" s="36">
@@ -16975,7 +16975,7 @@
         <v/>
       </c>
       <c r="G96" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;="&amp;($E$3-6),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-6),'Данные'!$A:$A,"&lt;"&amp;($E$3-6)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H96" s="37">
@@ -16993,15 +16993,15 @@
         <v/>
       </c>
       <c r="B97" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;="&amp;($E$3-5),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;"&amp;($E$3-5)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C97" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;="&amp;($E$3-5),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;"&amp;($E$3-5)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D97" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;="&amp;($E$3-5),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;"&amp;($E$3-5)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E97" s="29">
@@ -17013,7 +17013,7 @@
         <v/>
       </c>
       <c r="G97" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;="&amp;($E$3-5),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-5),'Данные'!$A:$A,"&lt;"&amp;($E$3-5)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H97" s="30">
@@ -17031,15 +17031,15 @@
         <v/>
       </c>
       <c r="B98" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;="&amp;($E$3-4),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;"&amp;($E$3-4)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C98" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;="&amp;($E$3-4),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;"&amp;($E$3-4)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D98" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;="&amp;($E$3-4),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;"&amp;($E$3-4)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E98" s="36">
@@ -17051,7 +17051,7 @@
         <v/>
       </c>
       <c r="G98" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;="&amp;($E$3-4),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-4),'Данные'!$A:$A,"&lt;"&amp;($E$3-4)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H98" s="37">
@@ -17069,15 +17069,15 @@
         <v/>
       </c>
       <c r="B99" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;="&amp;($E$3-3),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;"&amp;($E$3-3)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C99" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;="&amp;($E$3-3),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;"&amp;($E$3-3)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D99" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;="&amp;($E$3-3),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;"&amp;($E$3-3)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E99" s="29">
@@ -17089,7 +17089,7 @@
         <v/>
       </c>
       <c r="G99" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;="&amp;($E$3-3),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-3),'Данные'!$A:$A,"&lt;"&amp;($E$3-3)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H99" s="30">
@@ -17107,15 +17107,15 @@
         <v/>
       </c>
       <c r="B100" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;="&amp;($E$3-2),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;"&amp;($E$3-2)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C100" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;="&amp;($E$3-2),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;"&amp;($E$3-2)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D100" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;="&amp;($E$3-2),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;"&amp;($E$3-2)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E100" s="36">
@@ -17127,7 +17127,7 @@
         <v/>
       </c>
       <c r="G100" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;="&amp;($E$3-2),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-2),'Данные'!$A:$A,"&lt;"&amp;($E$3-2)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H100" s="37">
@@ -17145,15 +17145,15 @@
         <v/>
       </c>
       <c r="B101" s="27">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;="&amp;($E$3-1),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;"&amp;($E$3-1)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C101" s="28">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;="&amp;($E$3-1),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;"&amp;($E$3-1)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D101" s="28">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;="&amp;($E$3-1),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;"&amp;($E$3-1)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E101" s="29">
@@ -17165,7 +17165,7 @@
         <v/>
       </c>
       <c r="G101" s="28">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;="&amp;($E$3-1),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-1),'Данные'!$A:$A,"&lt;"&amp;($E$3-1)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H101" s="30">
@@ -17183,15 +17183,15 @@
         <v/>
       </c>
       <c r="B102" s="34">
-        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;="&amp;($E$3-0),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;"&amp;($E$3-0)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="C102" s="35">
-        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;="&amp;($E$3-0),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$D:$D,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;"&amp;($E$3-0)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="D102" s="35">
-        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;="&amp;($E$3-0),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$E:$E,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;"&amp;($E$3-0)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="E102" s="36">
@@ -17203,7 +17203,7 @@
         <v/>
       </c>
       <c r="G102" s="35">
-        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;="&amp;($E$3-0),'Данные'!$B:$B,$B$3)</f>
+        <f>SUMIFS('Данные'!$F:$F,'Данные'!$A:$A,"&gt;="&amp;($E$3-0),'Данные'!$A:$A,"&lt;"&amp;($E$3-0)+1,'Данные'!$B:$B,$B$3)</f>
         <v/>
       </c>
       <c r="H102" s="37">
@@ -17385,7 +17385,7 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>MAX('Данные'!$A:$A)</f>
+        <f>INT(MAX('Данные'!$A:$A))</f>
         <v/>
       </c>
       <c r="C7" s="4" t="inlineStr">

--- a/sova-report/sova-report.xlsx
+++ b/sova-report/sova-report.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="🦉 Сводная" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Сводная" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Направление 1" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Направление 2" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Направление 3" sheetId="4" state="visible" r:id="rId4"/>
@@ -459,7 +459,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'🦉 Сводная'!E19</f>
+              <f>'Сводная'!E19</f>
             </strRef>
           </tx>
           <spPr>
@@ -488,12 +488,12 @@
           </trendline>
           <cat>
             <numRef>
-              <f>'🦉 Сводная'!$A$20:$A$45</f>
+              <f>'Сводная'!$A$20:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'🦉 Сводная'!$E$20:$E$45</f>
+              <f>'Сводная'!$E$20:$E$45</f>
             </numRef>
           </val>
         </ser>
@@ -654,7 +654,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'🦉 Сводная'!E106</f>
+              <f>'Сводная'!E106</f>
             </strRef>
           </tx>
           <spPr>
@@ -683,12 +683,12 @@
           </trendline>
           <cat>
             <numRef>
-              <f>'🦉 Сводная'!$A$107:$A$118</f>
+              <f>'Сводная'!$A$107:$A$118</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'🦉 Сводная'!$E$107:$E$118</f>
+              <f>'Сводная'!$E$107:$E$118</f>
             </numRef>
           </val>
         </ser>
@@ -755,7 +755,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'🦉 Сводная'!B19</f>
+              <f>'Сводная'!B19</f>
             </strRef>
           </tx>
           <spPr>
@@ -776,12 +776,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'🦉 Сводная'!$A$20:$A$45</f>
+              <f>'Сводная'!$A$20:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'🦉 Сводная'!$B$20:$B$45</f>
+              <f>'Сводная'!$B$20:$B$45</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -791,7 +791,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'🦉 Сводная'!C19</f>
+              <f>'Сводная'!C19</f>
             </strRef>
           </tx>
           <spPr>
@@ -812,12 +812,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'🦉 Сводная'!$A$20:$A$45</f>
+              <f>'Сводная'!$A$20:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'🦉 Сводная'!$C$20:$C$45</f>
+              <f>'Сводная'!$C$20:$C$45</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -827,7 +827,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'🦉 Сводная'!D19</f>
+              <f>'Сводная'!D19</f>
             </strRef>
           </tx>
           <spPr>
@@ -848,12 +848,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'🦉 Сводная'!$A$20:$A$45</f>
+              <f>'Сводная'!$A$20:$A$45</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'🦉 Сводная'!$D$20:$D$45</f>
+              <f>'Сводная'!$D$20:$D$45</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -923,7 +923,7 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'🦉 Сводная'!B106</f>
+              <f>'Сводная'!B106</f>
             </strRef>
           </tx>
           <spPr>
@@ -944,12 +944,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'🦉 Сводная'!$A$107:$A$118</f>
+              <f>'Сводная'!$A$107:$A$118</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'🦉 Сводная'!$B$107:$B$118</f>
+              <f>'Сводная'!$B$107:$B$118</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -959,7 +959,7 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'🦉 Сводная'!C106</f>
+              <f>'Сводная'!C106</f>
             </strRef>
           </tx>
           <spPr>
@@ -980,12 +980,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'🦉 Сводная'!$A$107:$A$118</f>
+              <f>'Сводная'!$A$107:$A$118</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'🦉 Сводная'!$C$107:$C$118</f>
+              <f>'Сводная'!$C$107:$C$118</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -995,7 +995,7 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'🦉 Сводная'!D106</f>
+              <f>'Сводная'!D106</f>
             </strRef>
           </tx>
           <spPr>
@@ -1016,12 +1016,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'🦉 Сводная'!$A$107:$A$118</f>
+              <f>'Сводная'!$A$107:$A$118</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'🦉 Сводная'!$D$107:$D$118</f>
+              <f>'Сводная'!$D$107:$D$118</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2106,7 +2106,7 @@
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>🦉 Сова · Сводная по всем направлениям</t>
+          <t>Сова · Сводная по всем направлениям</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5663,7 +5663,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1">
-        <f>"🦉 Сова · "&amp;$B$3</f>
+        <f>"Сова · "&amp;$B$3</f>
         <v/>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9547,7 +9547,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1">
-        <f>"🦉 Сова · "&amp;$B$3</f>
+        <f>"Сова · "&amp;$B$3</f>
         <v/>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -13431,7 +13431,7 @@
   <sheetData>
     <row r="1" ht="34" customHeight="1">
       <c r="A1" s="1">
-        <f>"🦉 Сова · "&amp;$B$3</f>
+        <f>"Сова · "&amp;$B$3</f>
         <v/>
       </c>
       <c r="B1" s="2" t="n"/>

--- a/sova-report/sova-report.xlsx
+++ b/sova-report/sova-report.xlsx
@@ -17385,7 +17385,7 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>INT(MAX('Данные'!$A:$A))</f>
+        <f>IF(COUNT('Данные'!$A:$A),INT(MAX('Данные'!$A:$A)),TODAY()-1)</f>
         <v/>
       </c>
       <c r="C7" s="4" t="inlineStr">

--- a/sova-report/sova-report.xlsx
+++ b/sova-report/sova-report.xlsx
@@ -75,6 +75,11 @@
     </font>
     <font>
       <name val="Arial"/>
+      <color rgb="006B7280"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <b val="1"/>
       <color rgb="001F2430"/>
       <sz val="12"/>
@@ -90,11 +95,6 @@
       <b val="1"/>
       <color rgb="006B7280"/>
       <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <color rgb="006B7280"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -142,6 +142,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF6D6"/>
+        <bgColor rgb="00FFF6D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFFFFF"/>
         <bgColor rgb="00FFFFFF"/>
       </patternFill>
@@ -150,12 +156,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F4F6FA"/>
         <bgColor rgb="00F4F6FA"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF6D6"/>
-        <bgColor rgb="00FFF6D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -174,11 +174,6 @@
       <diagonal/>
     </border>
     <border>
-      <bottom style="thin">
-        <color rgb="00DFE3EB"/>
-      </bottom>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="00E0C46C"/>
       </left>
@@ -190,6 +185,11 @@
       </top>
       <bottom style="thin">
         <color rgb="00E0C46C"/>
+      </bottom>
+    </border>
+    <border>
+      <bottom style="thin">
+        <color rgb="00DFE3EB"/>
       </bottom>
     </border>
     <border>
@@ -217,105 +217,105 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="3" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="3" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="3" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="3" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="3" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="3" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="10" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="4" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="4" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="4" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -340,28 +340,28 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="170" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="4" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="2" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="4" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="2" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="2" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="2" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -5816,17 +5816,34 @@
         <f>'⚙ Настройки'!$B$7</f>
         <v/>
       </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Период с</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>по</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="n"/>
       <c r="M3" s="9" t="inlineStr">
         <is>
           <t>📈 По дням, последние 90</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="H4" s="10">
+        <f>IF(AND(ISNUMBER(H3),ISNUMBER(J3),H3&gt;J3),"⚠ Дата «с» позже даты «по»",IF(OR(ISNUMBER(H3),ISNUMBER(J3)),"Сравнение — с предыдущим периодом той же длины. Очистите поля, чтобы вернуть текущий месяц.","Пусто — текущий месяц. Дату выбирают двойным щелчком."))</f>
+        <v/>
+      </c>
+    </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Этот месяц против тех же дней прошлого</t>
-        </is>
+      <c r="A5" s="9">
+        <f>IF(OR(ISNUMBER($H$3),ISNUMBER($J$3)),"Выбранный период против предыдущего той же длины","Этот месяц против тех же дней прошлого")</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -5887,10 +5904,9 @@
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Этот месяц</t>
-        </is>
+      <c r="A7" s="12">
+        <f>IF(OR(ISNUMBER($H$3),ISNUMBER($J$3)),"Выбранный период","Этот месяц")</f>
+        <v/>
       </c>
       <c r="B7" s="13">
         <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$B$3)</f>
@@ -5925,19 +5941,18 @@
         <v/>
       </c>
       <c r="J7" s="18">
-        <f>DATE(YEAR($E$3),MONTH($E$3),1)</f>
+        <f>IF(ISNUMBER($H$3),$H$3,DATE(YEAR(K7),MONTH(K7),1))</f>
         <v/>
       </c>
       <c r="K7" s="18">
-        <f>$E$3</f>
+        <f>IF(ISNUMBER($J$3),$J$3,$E$3)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>Прошлый, те же дни</t>
-        </is>
+      <c r="A8" s="19">
+        <f>IF(OR(ISNUMBER($H$3),ISNUMBER($J$3)),"Предыдущий, той же длины","Прошлый, те же дни")</f>
+        <v/>
       </c>
       <c r="B8" s="20">
         <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;"&amp;$K$8+1,'Данные'!$B:$B,$B$3)</f>
@@ -5972,11 +5987,11 @@
         <v/>
       </c>
       <c r="J8" s="25">
-        <f>IF(FALSE,2*J7-K7-1,EDATE(J7,-1))</f>
+        <f>IF(OR(ISNUMBER($H$3),ISNUMBER($J$3)),2*J7-K7-1,EDATE(J7,-1))</f>
         <v/>
       </c>
       <c r="K8" s="25">
-        <f>IF(FALSE,J7-1,EDATE(K7,-1))</f>
+        <f>IF(OR(ISNUMBER($H$3),ISNUMBER($J$3)),J7-1,EDATE(K7,-1))</f>
         <v/>
       </c>
     </row>
@@ -9564,6 +9579,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="H3 J3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Период" prompt="Дата. Пусто — текущий месяц." type="date" operator="greaterThan">
+      <formula1>1</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -9700,17 +9720,34 @@
         <f>'⚙ Настройки'!$B$7</f>
         <v/>
       </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Период с</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>по</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="n"/>
       <c r="M3" s="9" t="inlineStr">
         <is>
           <t>📈 По дням, последние 90</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="H4" s="10">
+        <f>IF(AND(ISNUMBER(H3),ISNUMBER(J3),H3&gt;J3),"⚠ Дата «с» позже даты «по»",IF(OR(ISNUMBER(H3),ISNUMBER(J3)),"Сравнение — с предыдущим периодом той же длины. Очистите поля, чтобы вернуть текущий месяц.","Пусто — текущий месяц. Дату выбирают двойным щелчком."))</f>
+        <v/>
+      </c>
+    </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Этот месяц против тех же дней прошлого</t>
-        </is>
+      <c r="A5" s="9">
+        <f>IF(OR(ISNUMBER($H$3),ISNUMBER($J$3)),"Выбранный период против предыдущего той же длины","Этот месяц против тех же дней прошлого")</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -9771,10 +9808,9 @@
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Этот месяц</t>
-        </is>
+      <c r="A7" s="12">
+        <f>IF(OR(ISNUMBER($H$3),ISNUMBER($J$3)),"Выбранный период","Этот месяц")</f>
+        <v/>
       </c>
       <c r="B7" s="13">
         <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$B$3)</f>
@@ -9809,19 +9845,18 @@
         <v/>
       </c>
       <c r="J7" s="18">
-        <f>DATE(YEAR($E$3),MONTH($E$3),1)</f>
+        <f>IF(ISNUMBER($H$3),$H$3,DATE(YEAR(K7),MONTH(K7),1))</f>
         <v/>
       </c>
       <c r="K7" s="18">
-        <f>$E$3</f>
+        <f>IF(ISNUMBER($J$3),$J$3,$E$3)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>Прошлый, те же дни</t>
-        </is>
+      <c r="A8" s="19">
+        <f>IF(OR(ISNUMBER($H$3),ISNUMBER($J$3)),"Предыдущий, той же длины","Прошлый, те же дни")</f>
+        <v/>
       </c>
       <c r="B8" s="20">
         <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;"&amp;$K$8+1,'Данные'!$B:$B,$B$3)</f>
@@ -9856,11 +9891,11 @@
         <v/>
       </c>
       <c r="J8" s="25">
-        <f>IF(FALSE,2*J7-K7-1,EDATE(J7,-1))</f>
+        <f>IF(OR(ISNUMBER($H$3),ISNUMBER($J$3)),2*J7-K7-1,EDATE(J7,-1))</f>
         <v/>
       </c>
       <c r="K8" s="25">
-        <f>IF(FALSE,J7-1,EDATE(K7,-1))</f>
+        <f>IF(OR(ISNUMBER($H$3),ISNUMBER($J$3)),J7-1,EDATE(K7,-1))</f>
         <v/>
       </c>
     </row>
@@ -13448,6 +13483,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="H3 J3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Период" prompt="Дата. Пусто — текущий месяц." type="date" operator="greaterThan">
+      <formula1>1</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
@@ -13584,17 +13624,34 @@
         <f>'⚙ Настройки'!$B$7</f>
         <v/>
       </c>
+      <c r="G3" s="7" t="inlineStr">
+        <is>
+          <t>Период с</t>
+        </is>
+      </c>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="7" t="inlineStr">
+        <is>
+          <t>по</t>
+        </is>
+      </c>
+      <c r="J3" s="8" t="n"/>
       <c r="M3" s="9" t="inlineStr">
         <is>
           <t>📈 По дням, последние 90</t>
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="H4" s="10">
+        <f>IF(AND(ISNUMBER(H3),ISNUMBER(J3),H3&gt;J3),"⚠ Дата «с» позже даты «по»",IF(OR(ISNUMBER(H3),ISNUMBER(J3)),"Сравнение — с предыдущим периодом той же длины. Очистите поля, чтобы вернуть текущий месяц.","Пусто — текущий месяц. Дату выбирают двойным щелчком."))</f>
+        <v/>
+      </c>
+    </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>Этот месяц против тех же дней прошлого</t>
-        </is>
+      <c r="A5" s="9">
+        <f>IF(OR(ISNUMBER($H$3),ISNUMBER($J$3)),"Выбранный период против предыдущего той же длины","Этот месяц против тех же дней прошлого")</f>
+        <v/>
       </c>
     </row>
     <row r="6">
@@ -13655,10 +13712,9 @@
       </c>
     </row>
     <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Этот месяц</t>
-        </is>
+      <c r="A7" s="12">
+        <f>IF(OR(ISNUMBER($H$3),ISNUMBER($J$3)),"Выбранный период","Этот месяц")</f>
+        <v/>
       </c>
       <c r="B7" s="13">
         <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$7,'Данные'!$A:$A,"&lt;"&amp;$K$7+1,'Данные'!$B:$B,$B$3)</f>
@@ -13693,19 +13749,18 @@
         <v/>
       </c>
       <c r="J7" s="18">
-        <f>DATE(YEAR($E$3),MONTH($E$3),1)</f>
+        <f>IF(ISNUMBER($H$3),$H$3,DATE(YEAR(K7),MONTH(K7),1))</f>
         <v/>
       </c>
       <c r="K7" s="18">
-        <f>$E$3</f>
+        <f>IF(ISNUMBER($J$3),$J$3,$E$3)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="inlineStr">
-        <is>
-          <t>Прошлый, те же дни</t>
-        </is>
+      <c r="A8" s="19">
+        <f>IF(OR(ISNUMBER($H$3),ISNUMBER($J$3)),"Предыдущий, той же длины","Прошлый, те же дни")</f>
+        <v/>
       </c>
       <c r="B8" s="20">
         <f>SUMIFS('Данные'!$C:$C,'Данные'!$A:$A,"&gt;="&amp;$J$8,'Данные'!$A:$A,"&lt;"&amp;$K$8+1,'Данные'!$B:$B,$B$3)</f>
@@ -13740,11 +13795,11 @@
         <v/>
       </c>
       <c r="J8" s="25">
-        <f>IF(FALSE,2*J7-K7-1,EDATE(J7,-1))</f>
+        <f>IF(OR(ISNUMBER($H$3),ISNUMBER($J$3)),2*J7-K7-1,EDATE(J7,-1))</f>
         <v/>
       </c>
       <c r="K8" s="25">
-        <f>IF(FALSE,J7-1,EDATE(K7,-1))</f>
+        <f>IF(OR(ISNUMBER($H$3),ISNUMBER($J$3)),J7-1,EDATE(K7,-1))</f>
         <v/>
       </c>
     </row>
@@ -17332,6 +17387,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="H3 J3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" promptTitle="Период" prompt="Дата. Пусто — текущий месяц." type="date" operator="greaterThan">
+      <formula1>1</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>

--- a/sova-report/sova-report.xlsx
+++ b/sova-report/sova-report.xlsx
@@ -575,6 +575,507 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:t>Подписки по дням (пунктир — тренд)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Направление 2'!G12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1BAF7A"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="1BAF7A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <trendline>
+            <spPr>
+              <a:ln w="22000">
+                <a:solidFill>
+                  <a:srgbClr val="1F2A44"/>
+                </a:solidFill>
+                <a:prstDash val="dash"/>
+              </a:ln>
+            </spPr>
+            <trendlineType val="linear"/>
+            <dispRSqr val="0"/>
+            <dispEq val="0"/>
+          </trendline>
+          <cat>
+            <numRef>
+              <f>'Направление 2'!$A$13:$A$102</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Направление 2'!$G$13:$G$102</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="40"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart11.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Расход по дням, ₽ (пунктир — тренд)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Направление 2'!B12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <trendline>
+            <spPr>
+              <a:ln w="22000">
+                <a:solidFill>
+                  <a:srgbClr val="1F2A44"/>
+                </a:solidFill>
+                <a:prstDash val="dash"/>
+              </a:ln>
+            </spPr>
+            <trendlineType val="linear"/>
+            <dispRSqr val="0"/>
+            <dispEq val="0"/>
+          </trendline>
+          <cat>
+            <numRef>
+              <f>'Направление 2'!$A$13:$A$102</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Направление 2'!$B$13:$B$102</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="40"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart12.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Цена подписки по дням, ₽</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Направление 2'!H12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln w="22000">
+              <a:solidFill>
+                <a:srgbClr val="EB6834"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln>
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Направление 2'!$A$13:$A$102</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Направление 2'!$H$13:$H$102</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart13.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Подписки по дням (пунктир — тренд)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Направление 3'!G12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="1BAF7A"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="1BAF7A"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <trendline>
+            <spPr>
+              <a:ln w="22000">
+                <a:solidFill>
+                  <a:srgbClr val="1F2A44"/>
+                </a:solidFill>
+                <a:prstDash val="dash"/>
+              </a:ln>
+            </spPr>
+            <trendlineType val="linear"/>
+            <dispRSqr val="0"/>
+            <dispEq val="0"/>
+          </trendline>
+          <cat>
+            <numRef>
+              <f>'Направление 3'!$A$13:$A$102</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Направление 3'!$G$13:$G$102</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="40"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart14.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Расход по дням, ₽ (пунктир — тренд)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Направление 3'!B12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <trendline>
+            <spPr>
+              <a:ln w="22000">
+                <a:solidFill>
+                  <a:srgbClr val="1F2A44"/>
+                </a:solidFill>
+                <a:prstDash val="dash"/>
+              </a:ln>
+            </spPr>
+            <trendlineType val="linear"/>
+            <dispRSqr val="0"/>
+            <dispEq val="0"/>
+          </trendline>
+          <cat>
+            <numRef>
+              <f>'Направление 3'!$A$13:$A$102</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Направление 3'!$B$13:$B$102</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="40"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart15.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
               <a:t>Цена подписки по дням, ₽</a:t>
             </a:r>
           </a:p>
@@ -656,6 +1157,108 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Расход по неделям — вся клиника, ₽ (пунктир — тренд)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Сводная'!E77</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <trendline>
+            <spPr>
+              <a:ln w="22000">
+                <a:solidFill>
+                  <a:srgbClr val="1F2A44"/>
+                </a:solidFill>
+                <a:prstDash val="dash"/>
+              </a:ln>
+            </spPr>
+            <trendlineType val="linear"/>
+            <dispRSqr val="0"/>
+            <dispEq val="0"/>
+          </trendline>
+          <cat>
+            <numRef>
+              <f>'Сводная'!$A$78:$A$103</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Сводная'!$E$78:$E$103</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="40"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -757,7 +1360,109 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Расход по месяцам — вся клиника, ₽ (пунктир — тренд)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Сводная'!E136</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <trendline>
+            <spPr>
+              <a:ln w="22000">
+                <a:solidFill>
+                  <a:srgbClr val="1F2A44"/>
+                </a:solidFill>
+                <a:prstDash val="dash"/>
+              </a:ln>
+            </spPr>
+            <trendlineType val="linear"/>
+            <dispRSqr val="0"/>
+            <dispEq val="0"/>
+          </trendline>
+          <cat>
+            <numRef>
+              <f>'Сводная'!$A$137:$A$148</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Сводная'!$E$137:$E$148</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="40"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -925,7 +1630,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -1093,7 +1798,7 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -1195,7 +1900,109 @@
 </chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Расход по дням, ₽ (пунктир — тренд)</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Направление 1'!B12</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:solidFill>
+              <a:srgbClr val="2A78D6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:solidFill>
+                <a:srgbClr val="2A78D6"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <trendline>
+            <spPr>
+              <a:ln w="22000">
+                <a:solidFill>
+                  <a:srgbClr val="1F2A44"/>
+                </a:solidFill>
+                <a:prstDash val="dash"/>
+              </a:ln>
+            </spPr>
+            <trendlineType val="linear"/>
+            <dispRSqr val="0"/>
+            <dispEq val="0"/>
+          </trendline>
+          <cat>
+            <numRef>
+              <f>'Направление 1'!$A$13:$A$102</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Направление 1'!$B$13:$B$102</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="40"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
 <chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <style val="2"/>
   <chart>
@@ -1256,303 +2063,6 @@
         <axId val="10"/>
         <axId val="100"/>
       </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <numFmt formatCode="#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Подписки по дням (пунктир — тренд)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Направление 2'!G12</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="1BAF7A"/>
-            </a:solidFill>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="1BAF7A"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <trendline>
-            <spPr>
-              <a:ln w="22000">
-                <a:solidFill>
-                  <a:srgbClr val="1F2A44"/>
-                </a:solidFill>
-                <a:prstDash val="dash"/>
-              </a:ln>
-            </spPr>
-            <trendlineType val="linear"/>
-            <dispRSqr val="0"/>
-            <dispEq val="0"/>
-          </trendline>
-          <cat>
-            <numRef>
-              <f>'Направление 2'!$A$13:$A$102</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Направление 2'!$G$13:$G$102</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="40"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <numFmt formatCode="#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Цена подписки по дням, ₽</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Направление 2'!H12</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln w="22000">
-              <a:solidFill>
-                <a:srgbClr val="EB6834"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'Направление 2'!$A$13:$A$102</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Направление 2'!$H$13:$H$102</f>
-            </numRef>
-          </val>
-          <smooth val="0"/>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <delete val="0"/>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <numFmt formatCode="#,##0" sourceLinked="0"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <style val="2"/>
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>Подписки по дням (пунктир — тренд)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <barChart>
-        <barDir val="col"/>
-        <grouping val="clustered"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'Направление 3'!G12</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="1BAF7A"/>
-            </a:solidFill>
-            <a:ln>
-              <a:solidFill>
-                <a:srgbClr val="1BAF7A"/>
-              </a:solidFill>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <trendline>
-            <spPr>
-              <a:ln w="22000">
-                <a:solidFill>
-                  <a:srgbClr val="1F2A44"/>
-                </a:solidFill>
-                <a:prstDash val="dash"/>
-              </a:ln>
-            </spPr>
-            <trendlineType val="linear"/>
-            <dispRSqr val="0"/>
-            <dispEq val="0"/>
-          </trendline>
-          <cat>
-            <numRef>
-              <f>'Направление 3'!$A$13:$A$102</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Направление 3'!$G$13:$G$102</f>
-            </numRef>
-          </val>
-        </ser>
-        <gapWidth val="40"/>
-        <axId val="10"/>
-        <axId val="100"/>
-      </barChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -1675,6 +2185,50 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5328000" cy="2664000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId5"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>21</col>
+      <colOff>0</colOff>
+      <row>33</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5328000" cy="2664000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="6" name="Chart 6"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1719,6 +2273,28 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5328000" cy="2664000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1773,6 +2349,28 @@
     </graphicFrame>
     <clientData/>
   </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5328000" cy="2664000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
 </wsDr>
 </file>
 
@@ -1817,6 +2415,28 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>12</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5328000" cy="2664000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -2251,7 +2871,7 @@
       <c r="J3" s="8" t="n"/>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>📈 Тенденция подписок по неделям и месяцам (завершённые периоды)</t>
+          <t>📈 Подписки и расход по неделям и месяцам (завершённые периоды)</t>
         </is>
       </c>
     </row>
@@ -5830,7 +6450,7 @@
       <c r="J3" s="8" t="n"/>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>📈 По дням, последние 90</t>
+          <t>📈 Подписки и расход по дням, последние 90</t>
         </is>
       </c>
     </row>
@@ -9734,7 +10354,7 @@
       <c r="J3" s="8" t="n"/>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>📈 По дням, последние 90</t>
+          <t>📈 Подписки и расход по дням, последние 90</t>
         </is>
       </c>
     </row>
@@ -13638,7 +14258,7 @@
       <c r="J3" s="8" t="n"/>
       <c r="M3" s="9" t="inlineStr">
         <is>
-          <t>📈 По дням, последние 90</t>
+          <t>📈 Подписки и расход по дням, последние 90</t>
         </is>
       </c>
     </row>

--- a/sova-report/sova-report.xlsx
+++ b/sova-report/sova-report.xlsx
@@ -2121,9 +2121,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>21</col>
+      <col>12</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5328000" cy="2664000"/>
@@ -2145,7 +2145,7 @@
     <from>
       <col>12</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5328000" cy="2664000"/>
@@ -2165,9 +2165,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>21</col>
+      <col>12</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>48</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5328000" cy="2664000"/>
@@ -2189,7 +2189,7 @@
     <from>
       <col>12</col>
       <colOff>0</colOff>
-      <row>33</row>
+      <row>63</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5328000" cy="2664000"/>
@@ -2209,9 +2209,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>21</col>
+      <col>12</col>
       <colOff>0</colOff>
-      <row>33</row>
+      <row>78</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5328000" cy="2664000"/>
@@ -2258,9 +2258,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>21</col>
+      <col>12</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5328000" cy="2664000"/>
@@ -2282,7 +2282,7 @@
     <from>
       <col>12</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5328000" cy="2664000"/>
@@ -2329,9 +2329,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>21</col>
+      <col>12</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5328000" cy="2664000"/>
@@ -2353,7 +2353,7 @@
     <from>
       <col>12</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5328000" cy="2664000"/>
@@ -2400,9 +2400,9 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
-      <col>21</col>
+      <col>12</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>18</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5328000" cy="2664000"/>
@@ -2424,7 +2424,7 @@
     <from>
       <col>12</col>
       <colOff>0</colOff>
-      <row>18</row>
+      <row>33</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="5328000" cy="2664000"/>

--- a/sova-report/sova-report.xlsx
+++ b/sova-report/sova-report.xlsx
@@ -3370,7 +3370,7 @@
     </row>
     <row r="20">
       <c r="A20" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B20" s="31">
@@ -3393,7 +3393,7 @@
     </row>
     <row r="21">
       <c r="A21" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B21" s="38">
@@ -3419,7 +3419,7 @@
     </row>
     <row r="22">
       <c r="A22" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B22" s="31">
@@ -3445,7 +3445,7 @@
     </row>
     <row r="23">
       <c r="A23" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B23" s="38">
@@ -3471,7 +3471,7 @@
     </row>
     <row r="24">
       <c r="A24" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B24" s="31">
@@ -3497,7 +3497,7 @@
     </row>
     <row r="25">
       <c r="A25" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B25" s="38">
@@ -3523,7 +3523,7 @@
     </row>
     <row r="26">
       <c r="A26" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B26" s="31">
@@ -3549,7 +3549,7 @@
     </row>
     <row r="27">
       <c r="A27" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B27" s="38">
@@ -3575,7 +3575,7 @@
     </row>
     <row r="28">
       <c r="A28" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B28" s="31">
@@ -3601,7 +3601,7 @@
     </row>
     <row r="29">
       <c r="A29" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B29" s="38">
@@ -3627,7 +3627,7 @@
     </row>
     <row r="30">
       <c r="A30" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B30" s="31">
@@ -3653,7 +3653,7 @@
     </row>
     <row r="31">
       <c r="A31" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B31" s="38">
@@ -3679,7 +3679,7 @@
     </row>
     <row r="32">
       <c r="A32" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B32" s="31">
@@ -3705,7 +3705,7 @@
     </row>
     <row r="33">
       <c r="A33" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B33" s="38">
@@ -3731,7 +3731,7 @@
     </row>
     <row r="34">
       <c r="A34" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B34" s="31">
@@ -3757,7 +3757,7 @@
     </row>
     <row r="35">
       <c r="A35" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B35" s="38">
@@ -3783,7 +3783,7 @@
     </row>
     <row r="36">
       <c r="A36" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B36" s="31">
@@ -3809,7 +3809,7 @@
     </row>
     <row r="37">
       <c r="A37" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B37" s="38">
@@ -3835,7 +3835,7 @@
     </row>
     <row r="38">
       <c r="A38" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B38" s="31">
@@ -3861,7 +3861,7 @@
     </row>
     <row r="39">
       <c r="A39" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B39" s="38">
@@ -3887,7 +3887,7 @@
     </row>
     <row r="40">
       <c r="A40" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B40" s="31">
@@ -3913,7 +3913,7 @@
     </row>
     <row r="41">
       <c r="A41" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B41" s="38">
@@ -3939,7 +3939,7 @@
     </row>
     <row r="42">
       <c r="A42" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B42" s="31">
@@ -3965,7 +3965,7 @@
     </row>
     <row r="43">
       <c r="A43" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B43" s="38">
@@ -3991,7 +3991,7 @@
     </row>
     <row r="44">
       <c r="A44" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B44" s="31">
@@ -4017,7 +4017,7 @@
     </row>
     <row r="45">
       <c r="A45" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B45" s="38">
@@ -4074,7 +4074,7 @@
     </row>
     <row r="49">
       <c r="A49" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B49" s="33">
@@ -4096,7 +4096,7 @@
     </row>
     <row r="50">
       <c r="A50" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B50" s="40">
@@ -4118,7 +4118,7 @@
     </row>
     <row r="51">
       <c r="A51" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B51" s="33">
@@ -4140,7 +4140,7 @@
     </row>
     <row r="52">
       <c r="A52" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B52" s="40">
@@ -4162,7 +4162,7 @@
     </row>
     <row r="53">
       <c r="A53" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B53" s="33">
@@ -4184,7 +4184,7 @@
     </row>
     <row r="54">
       <c r="A54" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B54" s="40">
@@ -4206,7 +4206,7 @@
     </row>
     <row r="55">
       <c r="A55" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B55" s="33">
@@ -4228,7 +4228,7 @@
     </row>
     <row r="56">
       <c r="A56" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B56" s="40">
@@ -4250,7 +4250,7 @@
     </row>
     <row r="57">
       <c r="A57" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B57" s="33">
@@ -4272,7 +4272,7 @@
     </row>
     <row r="58">
       <c r="A58" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B58" s="40">
@@ -4294,7 +4294,7 @@
     </row>
     <row r="59">
       <c r="A59" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B59" s="33">
@@ -4316,7 +4316,7 @@
     </row>
     <row r="60">
       <c r="A60" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B60" s="40">
@@ -4338,7 +4338,7 @@
     </row>
     <row r="61">
       <c r="A61" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B61" s="33">
@@ -4360,7 +4360,7 @@
     </row>
     <row r="62">
       <c r="A62" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B62" s="40">
@@ -4382,7 +4382,7 @@
     </row>
     <row r="63">
       <c r="A63" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B63" s="33">
@@ -4404,7 +4404,7 @@
     </row>
     <row r="64">
       <c r="A64" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B64" s="40">
@@ -4426,7 +4426,7 @@
     </row>
     <row r="65">
       <c r="A65" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B65" s="33">
@@ -4448,7 +4448,7 @@
     </row>
     <row r="66">
       <c r="A66" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B66" s="40">
@@ -4470,7 +4470,7 @@
     </row>
     <row r="67">
       <c r="A67" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B67" s="33">
@@ -4492,7 +4492,7 @@
     </row>
     <row r="68">
       <c r="A68" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B68" s="40">
@@ -4514,7 +4514,7 @@
     </row>
     <row r="69">
       <c r="A69" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B69" s="33">
@@ -4536,7 +4536,7 @@
     </row>
     <row r="70">
       <c r="A70" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B70" s="40">
@@ -4558,7 +4558,7 @@
     </row>
     <row r="71">
       <c r="A71" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B71" s="33">
@@ -4580,7 +4580,7 @@
     </row>
     <row r="72">
       <c r="A72" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B72" s="40">
@@ -4602,7 +4602,7 @@
     </row>
     <row r="73">
       <c r="A73" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B73" s="33">
@@ -4624,7 +4624,7 @@
     </row>
     <row r="74">
       <c r="A74" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B74" s="40">
@@ -4677,7 +4677,7 @@
     </row>
     <row r="78">
       <c r="A78" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B78" s="30">
@@ -4699,7 +4699,7 @@
     </row>
     <row r="79">
       <c r="A79" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B79" s="37">
@@ -4721,7 +4721,7 @@
     </row>
     <row r="80">
       <c r="A80" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B80" s="30">
@@ -4743,7 +4743,7 @@
     </row>
     <row r="81">
       <c r="A81" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B81" s="37">
@@ -4765,7 +4765,7 @@
     </row>
     <row r="82">
       <c r="A82" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B82" s="30">
@@ -4787,7 +4787,7 @@
     </row>
     <row r="83">
       <c r="A83" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B83" s="37">
@@ -4809,7 +4809,7 @@
     </row>
     <row r="84">
       <c r="A84" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B84" s="30">
@@ -4831,7 +4831,7 @@
     </row>
     <row r="85">
       <c r="A85" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B85" s="37">
@@ -4853,7 +4853,7 @@
     </row>
     <row r="86">
       <c r="A86" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B86" s="30">
@@ -4875,7 +4875,7 @@
     </row>
     <row r="87">
       <c r="A87" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B87" s="37">
@@ -4897,7 +4897,7 @@
     </row>
     <row r="88">
       <c r="A88" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B88" s="30">
@@ -4919,7 +4919,7 @@
     </row>
     <row r="89">
       <c r="A89" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B89" s="37">
@@ -4941,7 +4941,7 @@
     </row>
     <row r="90">
       <c r="A90" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B90" s="30">
@@ -4963,7 +4963,7 @@
     </row>
     <row r="91">
       <c r="A91" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B91" s="37">
@@ -4985,7 +4985,7 @@
     </row>
     <row r="92">
       <c r="A92" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B92" s="30">
@@ -5007,7 +5007,7 @@
     </row>
     <row r="93">
       <c r="A93" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B93" s="37">
@@ -5029,7 +5029,7 @@
     </row>
     <row r="94">
       <c r="A94" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B94" s="30">
@@ -5051,7 +5051,7 @@
     </row>
     <row r="95">
       <c r="A95" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B95" s="37">
@@ -5073,7 +5073,7 @@
     </row>
     <row r="96">
       <c r="A96" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B96" s="30">
@@ -5095,7 +5095,7 @@
     </row>
     <row r="97">
       <c r="A97" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B97" s="37">
@@ -5117,7 +5117,7 @@
     </row>
     <row r="98">
       <c r="A98" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B98" s="30">
@@ -5139,7 +5139,7 @@
     </row>
     <row r="99">
       <c r="A99" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B99" s="37">
@@ -5161,7 +5161,7 @@
     </row>
     <row r="100">
       <c r="A100" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B100" s="30">
@@ -5183,7 +5183,7 @@
     </row>
     <row r="101">
       <c r="A101" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B101" s="37">
@@ -5205,7 +5205,7 @@
     </row>
     <row r="102">
       <c r="A102" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B102" s="30">
@@ -5227,7 +5227,7 @@
     </row>
     <row r="103">
       <c r="A103" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B103" s="37">
@@ -5299,7 +5299,7 @@
     </row>
     <row r="107">
       <c r="A107" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11))</f>
         <v/>
       </c>
       <c r="B107" s="31">
@@ -5322,7 +5322,7 @@
     </row>
     <row r="108">
       <c r="A108" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10))</f>
         <v/>
       </c>
       <c r="B108" s="38">
@@ -5348,7 +5348,7 @@
     </row>
     <row r="109">
       <c r="A109" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9))</f>
         <v/>
       </c>
       <c r="B109" s="31">
@@ -5374,7 +5374,7 @@
     </row>
     <row r="110">
       <c r="A110" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8))</f>
         <v/>
       </c>
       <c r="B110" s="38">
@@ -5400,7 +5400,7 @@
     </row>
     <row r="111">
       <c r="A111" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7))</f>
         <v/>
       </c>
       <c r="B111" s="31">
@@ -5426,7 +5426,7 @@
     </row>
     <row r="112">
       <c r="A112" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6))</f>
         <v/>
       </c>
       <c r="B112" s="38">
@@ -5452,7 +5452,7 @@
     </row>
     <row r="113">
       <c r="A113" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5))</f>
         <v/>
       </c>
       <c r="B113" s="31">
@@ -5478,7 +5478,7 @@
     </row>
     <row r="114">
       <c r="A114" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4))</f>
         <v/>
       </c>
       <c r="B114" s="38">
@@ -5504,7 +5504,7 @@
     </row>
     <row r="115">
       <c r="A115" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3))</f>
         <v/>
       </c>
       <c r="B115" s="31">
@@ -5530,7 +5530,7 @@
     </row>
     <row r="116">
       <c r="A116" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2))</f>
         <v/>
       </c>
       <c r="B116" s="38">
@@ -5556,7 +5556,7 @@
     </row>
     <row r="117">
       <c r="A117" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1))</f>
         <v/>
       </c>
       <c r="B117" s="31">
@@ -5582,7 +5582,7 @@
     </row>
     <row r="118">
       <c r="A118" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0))</f>
         <v/>
       </c>
       <c r="B118" s="38">
@@ -5639,7 +5639,7 @@
     </row>
     <row r="122">
       <c r="A122" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11))</f>
         <v/>
       </c>
       <c r="B122" s="33">
@@ -5661,7 +5661,7 @@
     </row>
     <row r="123">
       <c r="A123" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10))</f>
         <v/>
       </c>
       <c r="B123" s="40">
@@ -5683,7 +5683,7 @@
     </row>
     <row r="124">
       <c r="A124" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9))</f>
         <v/>
       </c>
       <c r="B124" s="33">
@@ -5705,7 +5705,7 @@
     </row>
     <row r="125">
       <c r="A125" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8))</f>
         <v/>
       </c>
       <c r="B125" s="40">
@@ -5727,7 +5727,7 @@
     </row>
     <row r="126">
       <c r="A126" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7))</f>
         <v/>
       </c>
       <c r="B126" s="33">
@@ -5749,7 +5749,7 @@
     </row>
     <row r="127">
       <c r="A127" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6))</f>
         <v/>
       </c>
       <c r="B127" s="40">
@@ -5771,7 +5771,7 @@
     </row>
     <row r="128">
       <c r="A128" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5))</f>
         <v/>
       </c>
       <c r="B128" s="33">
@@ -5793,7 +5793,7 @@
     </row>
     <row r="129">
       <c r="A129" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4))</f>
         <v/>
       </c>
       <c r="B129" s="40">
@@ -5815,7 +5815,7 @@
     </row>
     <row r="130">
       <c r="A130" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3))</f>
         <v/>
       </c>
       <c r="B130" s="33">
@@ -5837,7 +5837,7 @@
     </row>
     <row r="131">
       <c r="A131" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2))</f>
         <v/>
       </c>
       <c r="B131" s="40">
@@ -5859,7 +5859,7 @@
     </row>
     <row r="132">
       <c r="A132" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1))</f>
         <v/>
       </c>
       <c r="B132" s="33">
@@ -5881,7 +5881,7 @@
     </row>
     <row r="133">
       <c r="A133" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0))</f>
         <v/>
       </c>
       <c r="B133" s="40">
@@ -5934,7 +5934,7 @@
     </row>
     <row r="137">
       <c r="A137" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11))</f>
         <v/>
       </c>
       <c r="B137" s="30">
@@ -5956,7 +5956,7 @@
     </row>
     <row r="138">
       <c r="A138" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10))</f>
         <v/>
       </c>
       <c r="B138" s="37">
@@ -5978,7 +5978,7 @@
     </row>
     <row r="139">
       <c r="A139" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9))</f>
         <v/>
       </c>
       <c r="B139" s="30">
@@ -6000,7 +6000,7 @@
     </row>
     <row r="140">
       <c r="A140" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8))</f>
         <v/>
       </c>
       <c r="B140" s="37">
@@ -6022,7 +6022,7 @@
     </row>
     <row r="141">
       <c r="A141" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7))</f>
         <v/>
       </c>
       <c r="B141" s="30">
@@ -6044,7 +6044,7 @@
     </row>
     <row r="142">
       <c r="A142" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6))</f>
         <v/>
       </c>
       <c r="B142" s="37">
@@ -6066,7 +6066,7 @@
     </row>
     <row r="143">
       <c r="A143" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5))</f>
         <v/>
       </c>
       <c r="B143" s="30">
@@ -6088,7 +6088,7 @@
     </row>
     <row r="144">
       <c r="A144" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4))</f>
         <v/>
       </c>
       <c r="B144" s="37">
@@ -6110,7 +6110,7 @@
     </row>
     <row r="145">
       <c r="A145" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3))</f>
         <v/>
       </c>
       <c r="B145" s="30">
@@ -6132,7 +6132,7 @@
     </row>
     <row r="146">
       <c r="A146" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2))</f>
         <v/>
       </c>
       <c r="B146" s="37">
@@ -6154,7 +6154,7 @@
     </row>
     <row r="147">
       <c r="A147" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1))</f>
         <v/>
       </c>
       <c r="B147" s="30">
@@ -6176,7 +6176,7 @@
     </row>
     <row r="148">
       <c r="A148" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0))</f>
         <v/>
       </c>
       <c r="B148" s="37">
@@ -6726,7 +6726,7 @@
     </row>
     <row r="13">
       <c r="A13" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B13" s="30">
@@ -6764,7 +6764,7 @@
     </row>
     <row r="14">
       <c r="A14" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B14" s="37">
@@ -6802,7 +6802,7 @@
     </row>
     <row r="15">
       <c r="A15" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B15" s="30">
@@ -6840,7 +6840,7 @@
     </row>
     <row r="16">
       <c r="A16" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B16" s="37">
@@ -6878,7 +6878,7 @@
     </row>
     <row r="17">
       <c r="A17" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B17" s="30">
@@ -6916,7 +6916,7 @@
     </row>
     <row r="18">
       <c r="A18" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B18" s="37">
@@ -6954,7 +6954,7 @@
     </row>
     <row r="19">
       <c r="A19" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B19" s="30">
@@ -6992,7 +6992,7 @@
     </row>
     <row r="20">
       <c r="A20" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B20" s="37">
@@ -7030,7 +7030,7 @@
     </row>
     <row r="21">
       <c r="A21" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B21" s="30">
@@ -7068,7 +7068,7 @@
     </row>
     <row r="22">
       <c r="A22" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B22" s="37">
@@ -7106,7 +7106,7 @@
     </row>
     <row r="23">
       <c r="A23" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B23" s="30">
@@ -7144,7 +7144,7 @@
     </row>
     <row r="24">
       <c r="A24" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B24" s="37">
@@ -7182,7 +7182,7 @@
     </row>
     <row r="25">
       <c r="A25" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B25" s="30">
@@ -7220,7 +7220,7 @@
     </row>
     <row r="26">
       <c r="A26" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B26" s="37">
@@ -7258,7 +7258,7 @@
     </row>
     <row r="27">
       <c r="A27" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B27" s="30">
@@ -7296,7 +7296,7 @@
     </row>
     <row r="28">
       <c r="A28" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B28" s="37">
@@ -7334,7 +7334,7 @@
     </row>
     <row r="29">
       <c r="A29" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B29" s="30">
@@ -7372,7 +7372,7 @@
     </row>
     <row r="30">
       <c r="A30" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B30" s="37">
@@ -7410,7 +7410,7 @@
     </row>
     <row r="31">
       <c r="A31" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B31" s="30">
@@ -7448,7 +7448,7 @@
     </row>
     <row r="32">
       <c r="A32" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B32" s="37">
@@ -7486,7 +7486,7 @@
     </row>
     <row r="33">
       <c r="A33" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B33" s="30">
@@ -7524,7 +7524,7 @@
     </row>
     <row r="34">
       <c r="A34" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B34" s="37">
@@ -7562,7 +7562,7 @@
     </row>
     <row r="35">
       <c r="A35" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B35" s="30">
@@ -7600,7 +7600,7 @@
     </row>
     <row r="36">
       <c r="A36" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B36" s="37">
@@ -7638,7 +7638,7 @@
     </row>
     <row r="37">
       <c r="A37" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B37" s="30">
@@ -7676,7 +7676,7 @@
     </row>
     <row r="38">
       <c r="A38" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B38" s="37">
@@ -7807,7 +7807,7 @@
     </row>
     <row r="43">
       <c r="A43" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11))</f>
         <v/>
       </c>
       <c r="B43" s="30">
@@ -7845,7 +7845,7 @@
     </row>
     <row r="44">
       <c r="A44" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10))</f>
         <v/>
       </c>
       <c r="B44" s="37">
@@ -7883,7 +7883,7 @@
     </row>
     <row r="45">
       <c r="A45" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9))</f>
         <v/>
       </c>
       <c r="B45" s="30">
@@ -7921,7 +7921,7 @@
     </row>
     <row r="46">
       <c r="A46" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8))</f>
         <v/>
       </c>
       <c r="B46" s="37">
@@ -7959,7 +7959,7 @@
     </row>
     <row r="47">
       <c r="A47" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7))</f>
         <v/>
       </c>
       <c r="B47" s="30">
@@ -7997,7 +7997,7 @@
     </row>
     <row r="48">
       <c r="A48" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6))</f>
         <v/>
       </c>
       <c r="B48" s="37">
@@ -8035,7 +8035,7 @@
     </row>
     <row r="49">
       <c r="A49" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5))</f>
         <v/>
       </c>
       <c r="B49" s="30">
@@ -8073,7 +8073,7 @@
     </row>
     <row r="50">
       <c r="A50" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4))</f>
         <v/>
       </c>
       <c r="B50" s="37">
@@ -8111,7 +8111,7 @@
     </row>
     <row r="51">
       <c r="A51" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3))</f>
         <v/>
       </c>
       <c r="B51" s="30">
@@ -8149,7 +8149,7 @@
     </row>
     <row r="52">
       <c r="A52" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2))</f>
         <v/>
       </c>
       <c r="B52" s="37">
@@ -8187,7 +8187,7 @@
     </row>
     <row r="53">
       <c r="A53" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1))</f>
         <v/>
       </c>
       <c r="B53" s="30">
@@ -8225,7 +8225,7 @@
     </row>
     <row r="54">
       <c r="A54" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0))</f>
         <v/>
       </c>
       <c r="B54" s="37">
@@ -12359,7 +12359,7 @@
     </row>
     <row r="13">
       <c r="A13" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B13" s="30">
@@ -12397,7 +12397,7 @@
     </row>
     <row r="14">
       <c r="A14" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B14" s="37">
@@ -12435,7 +12435,7 @@
     </row>
     <row r="15">
       <c r="A15" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B15" s="30">
@@ -12473,7 +12473,7 @@
     </row>
     <row r="16">
       <c r="A16" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B16" s="37">
@@ -12511,7 +12511,7 @@
     </row>
     <row r="17">
       <c r="A17" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B17" s="30">
@@ -12549,7 +12549,7 @@
     </row>
     <row r="18">
       <c r="A18" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B18" s="37">
@@ -12587,7 +12587,7 @@
     </row>
     <row r="19">
       <c r="A19" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B19" s="30">
@@ -12625,7 +12625,7 @@
     </row>
     <row r="20">
       <c r="A20" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B20" s="37">
@@ -12663,7 +12663,7 @@
     </row>
     <row r="21">
       <c r="A21" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B21" s="30">
@@ -12701,7 +12701,7 @@
     </row>
     <row r="22">
       <c r="A22" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B22" s="37">
@@ -12739,7 +12739,7 @@
     </row>
     <row r="23">
       <c r="A23" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B23" s="30">
@@ -12777,7 +12777,7 @@
     </row>
     <row r="24">
       <c r="A24" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B24" s="37">
@@ -12815,7 +12815,7 @@
     </row>
     <row r="25">
       <c r="A25" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B25" s="30">
@@ -12853,7 +12853,7 @@
     </row>
     <row r="26">
       <c r="A26" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B26" s="37">
@@ -12891,7 +12891,7 @@
     </row>
     <row r="27">
       <c r="A27" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B27" s="30">
@@ -12929,7 +12929,7 @@
     </row>
     <row r="28">
       <c r="A28" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B28" s="37">
@@ -12967,7 +12967,7 @@
     </row>
     <row r="29">
       <c r="A29" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B29" s="30">
@@ -13005,7 +13005,7 @@
     </row>
     <row r="30">
       <c r="A30" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B30" s="37">
@@ -13043,7 +13043,7 @@
     </row>
     <row r="31">
       <c r="A31" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B31" s="30">
@@ -13081,7 +13081,7 @@
     </row>
     <row r="32">
       <c r="A32" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B32" s="37">
@@ -13119,7 +13119,7 @@
     </row>
     <row r="33">
       <c r="A33" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B33" s="30">
@@ -13157,7 +13157,7 @@
     </row>
     <row r="34">
       <c r="A34" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B34" s="37">
@@ -13195,7 +13195,7 @@
     </row>
     <row r="35">
       <c r="A35" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B35" s="30">
@@ -13233,7 +13233,7 @@
     </row>
     <row r="36">
       <c r="A36" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B36" s="37">
@@ -13271,7 +13271,7 @@
     </row>
     <row r="37">
       <c r="A37" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B37" s="30">
@@ -13309,7 +13309,7 @@
     </row>
     <row r="38">
       <c r="A38" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B38" s="37">
@@ -13440,7 +13440,7 @@
     </row>
     <row r="43">
       <c r="A43" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11))</f>
         <v/>
       </c>
       <c r="B43" s="30">
@@ -13478,7 +13478,7 @@
     </row>
     <row r="44">
       <c r="A44" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10))</f>
         <v/>
       </c>
       <c r="B44" s="37">
@@ -13516,7 +13516,7 @@
     </row>
     <row r="45">
       <c r="A45" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9))</f>
         <v/>
       </c>
       <c r="B45" s="30">
@@ -13554,7 +13554,7 @@
     </row>
     <row r="46">
       <c r="A46" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8))</f>
         <v/>
       </c>
       <c r="B46" s="37">
@@ -13592,7 +13592,7 @@
     </row>
     <row r="47">
       <c r="A47" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7))</f>
         <v/>
       </c>
       <c r="B47" s="30">
@@ -13630,7 +13630,7 @@
     </row>
     <row r="48">
       <c r="A48" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6))</f>
         <v/>
       </c>
       <c r="B48" s="37">
@@ -13668,7 +13668,7 @@
     </row>
     <row r="49">
       <c r="A49" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5))</f>
         <v/>
       </c>
       <c r="B49" s="30">
@@ -13706,7 +13706,7 @@
     </row>
     <row r="50">
       <c r="A50" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4))</f>
         <v/>
       </c>
       <c r="B50" s="37">
@@ -13744,7 +13744,7 @@
     </row>
     <row r="51">
       <c r="A51" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3))</f>
         <v/>
       </c>
       <c r="B51" s="30">
@@ -13782,7 +13782,7 @@
     </row>
     <row r="52">
       <c r="A52" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2))</f>
         <v/>
       </c>
       <c r="B52" s="37">
@@ -13820,7 +13820,7 @@
     </row>
     <row r="53">
       <c r="A53" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1))</f>
         <v/>
       </c>
       <c r="B53" s="30">
@@ -13858,7 +13858,7 @@
     </row>
     <row r="54">
       <c r="A54" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0))</f>
         <v/>
       </c>
       <c r="B54" s="37">
@@ -17992,7 +17992,7 @@
     </row>
     <row r="13">
       <c r="A13" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*25)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B13" s="30">
@@ -18030,7 +18030,7 @@
     </row>
     <row r="14">
       <c r="A14" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*24)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B14" s="37">
@@ -18068,7 +18068,7 @@
     </row>
     <row r="15">
       <c r="A15" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*23)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B15" s="30">
@@ -18106,7 +18106,7 @@
     </row>
     <row r="16">
       <c r="A16" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*22)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B16" s="37">
@@ -18144,7 +18144,7 @@
     </row>
     <row r="17">
       <c r="A17" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*21)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B17" s="30">
@@ -18182,7 +18182,7 @@
     </row>
     <row r="18">
       <c r="A18" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*20)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B18" s="37">
@@ -18220,7 +18220,7 @@
     </row>
     <row r="19">
       <c r="A19" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*19)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B19" s="30">
@@ -18258,7 +18258,7 @@
     </row>
     <row r="20">
       <c r="A20" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*18)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B20" s="37">
@@ -18296,7 +18296,7 @@
     </row>
     <row r="21">
       <c r="A21" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*17)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B21" s="30">
@@ -18334,7 +18334,7 @@
     </row>
     <row r="22">
       <c r="A22" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*16)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B22" s="37">
@@ -18372,7 +18372,7 @@
     </row>
     <row r="23">
       <c r="A23" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*15)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B23" s="30">
@@ -18410,7 +18410,7 @@
     </row>
     <row r="24">
       <c r="A24" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*14)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B24" s="37">
@@ -18448,7 +18448,7 @@
     </row>
     <row r="25">
       <c r="A25" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*13)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B25" s="30">
@@ -18486,7 +18486,7 @@
     </row>
     <row r="26">
       <c r="A26" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*12)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B26" s="37">
@@ -18524,7 +18524,7 @@
     </row>
     <row r="27">
       <c r="A27" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*11)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B27" s="30">
@@ -18562,7 +18562,7 @@
     </row>
     <row r="28">
       <c r="A28" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*10)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B28" s="37">
@@ -18600,7 +18600,7 @@
     </row>
     <row r="29">
       <c r="A29" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*9)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B29" s="30">
@@ -18638,7 +18638,7 @@
     </row>
     <row r="30">
       <c r="A30" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*8)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B30" s="37">
@@ -18676,7 +18676,7 @@
     </row>
     <row r="31">
       <c r="A31" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*7)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B31" s="30">
@@ -18714,7 +18714,7 @@
     </row>
     <row r="32">
       <c r="A32" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*6)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B32" s="37">
@@ -18752,7 +18752,7 @@
     </row>
     <row r="33">
       <c r="A33" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*5)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B33" s="30">
@@ -18790,7 +18790,7 @@
     </row>
     <row r="34">
       <c r="A34" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*4)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B34" s="37">
@@ -18828,7 +18828,7 @@
     </row>
     <row r="35">
       <c r="A35" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*3)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B35" s="30">
@@ -18866,7 +18866,7 @@
     </row>
     <row r="36">
       <c r="A36" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*2)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B36" s="37">
@@ -18904,7 +18904,7 @@
     </row>
     <row r="37">
       <c r="A37" s="29">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*1)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B37" s="30">
@@ -18942,7 +18942,7 @@
     </row>
     <row r="38">
       <c r="A38" s="36">
-        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6,"DD.MM")</f>
+        <f>TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0),"DD.MM")&amp;"–"&amp;TEXT((($E$3-WEEKDAY($E$3,2)+1-7*(WEEKDAY($E$3,2)&lt;7))-7*0)+6,"DD.MM.YYYY")</f>
         <v/>
       </c>
       <c r="B38" s="37">
@@ -19073,7 +19073,7 @@
     </row>
     <row r="43">
       <c r="A43" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-11))</f>
         <v/>
       </c>
       <c r="B43" s="30">
@@ -19111,7 +19111,7 @@
     </row>
     <row r="44">
       <c r="A44" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-10))</f>
         <v/>
       </c>
       <c r="B44" s="37">
@@ -19149,7 +19149,7 @@
     </row>
     <row r="45">
       <c r="A45" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-9))</f>
         <v/>
       </c>
       <c r="B45" s="30">
@@ -19187,7 +19187,7 @@
     </row>
     <row r="46">
       <c r="A46" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-8))</f>
         <v/>
       </c>
       <c r="B46" s="37">
@@ -19225,7 +19225,7 @@
     </row>
     <row r="47">
       <c r="A47" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-7))</f>
         <v/>
       </c>
       <c r="B47" s="30">
@@ -19263,7 +19263,7 @@
     </row>
     <row r="48">
       <c r="A48" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-6))</f>
         <v/>
       </c>
       <c r="B48" s="37">
@@ -19301,7 +19301,7 @@
     </row>
     <row r="49">
       <c r="A49" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-5))</f>
         <v/>
       </c>
       <c r="B49" s="30">
@@ -19339,7 +19339,7 @@
     </row>
     <row r="50">
       <c r="A50" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-4))</f>
         <v/>
       </c>
       <c r="B50" s="37">
@@ -19377,7 +19377,7 @@
     </row>
     <row r="51">
       <c r="A51" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-3))</f>
         <v/>
       </c>
       <c r="B51" s="30">
@@ -19415,7 +19415,7 @@
     </row>
     <row r="52">
       <c r="A52" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-2))</f>
         <v/>
       </c>
       <c r="B52" s="37">
@@ -19453,7 +19453,7 @@
     </row>
     <row r="53">
       <c r="A53" s="29">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),-1))</f>
         <v/>
       </c>
       <c r="B53" s="30">
@@ -19491,7 +19491,7 @@
     </row>
     <row r="54">
       <c r="A54" s="36">
-        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")</f>
+        <f>CHOOSE(MONTH(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0)),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(EDATE(EDATE(DATE(YEAR($E$3),MONTH($E$3),1),-($E$3&lt;EOMONTH($E$3,0))),0))</f>
         <v/>
       </c>
       <c r="B54" s="37">

--- a/sova-report/sova-report.xlsx
+++ b/sova-report/sova-report.xlsx
@@ -2898,7 +2898,7 @@
     </row>
     <row r="4">
       <c r="H4" s="11">
-        <f>IF(AND(ISNUMBER(H3),H3&gt;$E$3),"⚠ Дата «с» позже сегодняшней",IF(ISNUMBER(H3),"Сравнение — с предыдущим периодом той же длины. Очистите поле, чтобы считать с 1-го числа месяца.","«С» — вручную (двойной щелчок — календарь), пусто — с 1-го числа месяца. «По» — всегда сегодня."))</f>
+        <f>IF(AND(ISNUMBER(H3),H3&gt;$E$3),"⚠ Дата «с» позже вчерашней",IF(ISNUMBER(H3),"Сравнение — с предыдущим периодом той же длины. Очистите поле, чтобы считать с 1-го числа месяца.","«С» — вручную (двойной щелчок — календарь), пусто — с 1-го числа месяца. «По» — всегда вчера."))</f>
         <v/>
       </c>
     </row>
@@ -6519,7 +6519,7 @@
     </row>
     <row r="4">
       <c r="H4" s="11">
-        <f>IF(AND(ISNUMBER(H3),H3&gt;$E$3),"⚠ Дата «с» позже сегодняшней",IF(ISNUMBER(H3),"Сравнение — с предыдущим периодом той же длины. Очистите поле, чтобы считать с 1-го числа месяца.","«С» — вручную (двойной щелчок — календарь), пусто — с 1-го числа месяца. «По» — всегда сегодня."))</f>
+        <f>IF(AND(ISNUMBER(H3),H3&gt;$E$3),"⚠ Дата «с» позже вчерашней",IF(ISNUMBER(H3),"Сравнение — с предыдущим периодом той же длины. Очистите поле, чтобы считать с 1-го числа месяца.","«С» — вручную (двойной щелчок — календарь), пусто — с 1-го числа месяца. «По» — всегда вчера."))</f>
         <v/>
       </c>
     </row>
@@ -12716,7 +12716,7 @@
     </row>
     <row r="4">
       <c r="H4" s="11">
-        <f>IF(AND(ISNUMBER(H3),H3&gt;$E$3),"⚠ Дата «с» позже сегодняшней",IF(ISNUMBER(H3),"Сравнение — с предыдущим периодом той же длины. Очистите поле, чтобы считать с 1-го числа месяца.","«С» — вручную (двойной щелчок — календарь), пусто — с 1-го числа месяца. «По» — всегда сегодня."))</f>
+        <f>IF(AND(ISNUMBER(H3),H3&gt;$E$3),"⚠ Дата «с» позже вчерашней",IF(ISNUMBER(H3),"Сравнение — с предыдущим периодом той же длины. Очистите поле, чтобы считать с 1-го числа месяца.","«С» — вручную (двойной щелчок — календарь), пусто — с 1-го числа месяца. «По» — всегда вчера."))</f>
         <v/>
       </c>
     </row>
@@ -18913,7 +18913,7 @@
     </row>
     <row r="4">
       <c r="H4" s="11">
-        <f>IF(AND(ISNUMBER(H3),H3&gt;$E$3),"⚠ Дата «с» позже сегодняшней",IF(ISNUMBER(H3),"Сравнение — с предыдущим периодом той же длины. Очистите поле, чтобы считать с 1-го числа месяца.","«С» — вручную (двойной щелчок — календарь), пусто — с 1-го числа месяца. «По» — всегда сегодня."))</f>
+        <f>IF(AND(ISNUMBER(H3),H3&gt;$E$3),"⚠ Дата «с» позже вчерашней",IF(ISNUMBER(H3),"Сравнение — с предыдущим периодом той же длины. Очистите поле, чтобы считать с 1-го числа месяца.","«С» — вручную (двойной щелчок — календарь), пусто — с 1-го числа месяца. «По» — всегда вчера."))</f>
         <v/>
       </c>
     </row>
@@ -25051,12 +25051,12 @@
         </is>
       </c>
       <c r="B7" s="6">
-        <f>TODAY()</f>
+        <f>TODAY()-1</f>
         <v/>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>← всегда сегодня</t>
+          <t>← всегда вчера (последний полный день)</t>
         </is>
       </c>
     </row>
